--- a/uploads/giro.xlsx
+++ b/uploads/giro.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coralis\Eksport Implementasi\20251031\eksport\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coralis\Eksport Implementasi\20251114\Eksport\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="344">
   <si>
     <t>nomor_giro</t>
   </si>
@@ -54,334 +54,844 @@
     <t>ex: Cair, Belum Cair</t>
   </si>
   <si>
-    <t>051505</t>
-  </si>
-  <si>
-    <t>039726</t>
+    <t>201829</t>
+  </si>
+  <si>
+    <t>017071</t>
+  </si>
+  <si>
+    <t>BNI'46</t>
+  </si>
+  <si>
+    <t>Belum Cair</t>
+  </si>
+  <si>
+    <t>201846</t>
+  </si>
+  <si>
+    <t>201870</t>
+  </si>
+  <si>
+    <t>072546</t>
+  </si>
+  <si>
+    <t>239217</t>
+  </si>
+  <si>
+    <t>061611</t>
+  </si>
+  <si>
+    <t>BANK JABAR BANTEN</t>
+  </si>
+  <si>
+    <t>239218</t>
+  </si>
+  <si>
+    <t>502568</t>
+  </si>
+  <si>
+    <t>037981</t>
+  </si>
+  <si>
+    <t>BANK PANIN</t>
+  </si>
+  <si>
+    <t>502591</t>
+  </si>
+  <si>
+    <t>067039</t>
+  </si>
+  <si>
+    <t>502608</t>
+  </si>
+  <si>
+    <t>502618</t>
+  </si>
+  <si>
+    <t>502737</t>
+  </si>
+  <si>
+    <t>517238</t>
+  </si>
+  <si>
+    <t>000956</t>
+  </si>
+  <si>
+    <t>BANK JABAR</t>
+  </si>
+  <si>
+    <t>174003</t>
+  </si>
+  <si>
+    <t>013993</t>
+  </si>
+  <si>
+    <t>BANK MANDIRI</t>
+  </si>
+  <si>
+    <t>174004</t>
+  </si>
+  <si>
+    <t>174005</t>
+  </si>
+  <si>
+    <t>174006</t>
+  </si>
+  <si>
+    <t>369460</t>
+  </si>
+  <si>
+    <t>369461</t>
+  </si>
+  <si>
+    <t>369462</t>
+  </si>
+  <si>
+    <t>369463</t>
+  </si>
+  <si>
+    <t>369464</t>
+  </si>
+  <si>
+    <t>369465</t>
+  </si>
+  <si>
+    <t>046471</t>
+  </si>
+  <si>
+    <t>061065</t>
+  </si>
+  <si>
+    <t>BANK RAKYAT INDONESIA (PERSERO), Tbk.</t>
+  </si>
+  <si>
+    <t>716497</t>
+  </si>
+  <si>
+    <t>067099</t>
+  </si>
+  <si>
+    <t>716634</t>
+  </si>
+  <si>
+    <t>032723</t>
+  </si>
+  <si>
+    <t>052428</t>
+  </si>
+  <si>
+    <t>BANK DANAMON INDONESIA, PT. Tbk.</t>
+  </si>
+  <si>
+    <t>091063</t>
+  </si>
+  <si>
+    <t>053393</t>
+  </si>
+  <si>
+    <t>091066</t>
+  </si>
+  <si>
+    <t>105142</t>
+  </si>
+  <si>
+    <t>262630</t>
+  </si>
+  <si>
+    <t>042777</t>
+  </si>
+  <si>
+    <t>BANK INDEX SELINDO, PT.</t>
+  </si>
+  <si>
+    <t>328480</t>
+  </si>
+  <si>
+    <t>053463</t>
+  </si>
+  <si>
+    <t>328481</t>
+  </si>
+  <si>
+    <t>578612</t>
+  </si>
+  <si>
+    <t>040722</t>
+  </si>
+  <si>
+    <t>578613</t>
+  </si>
+  <si>
+    <t>626359</t>
+  </si>
+  <si>
+    <t>061077</t>
   </si>
   <si>
     <t>BANK CENTRAL ASIA</t>
   </si>
   <si>
-    <t>Belum Cair</t>
-  </si>
-  <si>
-    <t>201754</t>
-  </si>
-  <si>
-    <t>072546</t>
-  </si>
-  <si>
-    <t>BNI'46</t>
-  </si>
-  <si>
-    <t>239217</t>
-  </si>
-  <si>
-    <t>061611</t>
-  </si>
-  <si>
-    <t>BANK JABAR BANTEN</t>
-  </si>
-  <si>
-    <t>239218</t>
-  </si>
-  <si>
-    <t>257167</t>
-  </si>
-  <si>
-    <t>000956</t>
+    <t>725513</t>
+  </si>
+  <si>
+    <t>069474</t>
+  </si>
+  <si>
+    <t>BANK HANA</t>
+  </si>
+  <si>
+    <t>738878</t>
+  </si>
+  <si>
+    <t>BANK OCBC - INDONESIA, PT.</t>
+  </si>
+  <si>
+    <t>738879</t>
+  </si>
+  <si>
+    <t>738885</t>
+  </si>
+  <si>
+    <t>738887</t>
+  </si>
+  <si>
+    <t>738889</t>
+  </si>
+  <si>
+    <t>931669</t>
+  </si>
+  <si>
+    <t>065261</t>
+  </si>
+  <si>
+    <t>BANK SYARIAH INDONESIA</t>
+  </si>
+  <si>
+    <t>177397</t>
+  </si>
+  <si>
+    <t>013061</t>
+  </si>
+  <si>
+    <t>474289</t>
+  </si>
+  <si>
+    <t>003251</t>
+  </si>
+  <si>
+    <t>050006</t>
+  </si>
+  <si>
+    <t>042440</t>
+  </si>
+  <si>
+    <t>095316</t>
+  </si>
+  <si>
+    <t>042438</t>
+  </si>
+  <si>
+    <t>343605</t>
+  </si>
+  <si>
+    <t>030787</t>
+  </si>
+  <si>
+    <t>BANK MEGA</t>
+  </si>
+  <si>
+    <t>343612</t>
+  </si>
+  <si>
+    <t>392948</t>
+  </si>
+  <si>
+    <t>005647</t>
+  </si>
+  <si>
+    <t>BANK PERMATA, PT. Tbk.</t>
+  </si>
+  <si>
+    <t>518146</t>
+  </si>
+  <si>
+    <t>052835</t>
+  </si>
+  <si>
+    <t>518149</t>
+  </si>
+  <si>
+    <t>665434</t>
+  </si>
+  <si>
+    <t>000288</t>
+  </si>
+  <si>
+    <t>673303</t>
+  </si>
+  <si>
+    <t>673308</t>
+  </si>
+  <si>
+    <t>AGC 244752</t>
+  </si>
+  <si>
+    <t>006357</t>
   </si>
   <si>
     <t>BANK MAS, PT.</t>
   </si>
   <si>
-    <t>499725</t>
-  </si>
-  <si>
-    <t>067039</t>
-  </si>
-  <si>
-    <t>BANK PANIN</t>
-  </si>
-  <si>
-    <t>502545</t>
-  </si>
-  <si>
-    <t>037981</t>
-  </si>
-  <si>
-    <t>502591</t>
-  </si>
-  <si>
-    <t>517238</t>
-  </si>
-  <si>
-    <t>BANK JABAR</t>
-  </si>
-  <si>
-    <t>004666</t>
-  </si>
-  <si>
-    <t>014299</t>
+    <t>AN673290</t>
+  </si>
+  <si>
+    <t>BAG426131</t>
+  </si>
+  <si>
+    <t>051913</t>
+  </si>
+  <si>
+    <t>BANK CIMB NIAGA, PT.</t>
+  </si>
+  <si>
+    <t>BAG426229</t>
+  </si>
+  <si>
+    <t>BAG426311</t>
+  </si>
+  <si>
+    <t>EP 285497</t>
+  </si>
+  <si>
+    <t>006481</t>
+  </si>
+  <si>
+    <t>FB955185</t>
+  </si>
+  <si>
+    <t>046770</t>
+  </si>
+  <si>
+    <t>FB955199</t>
+  </si>
+  <si>
+    <t>GA 423712</t>
+  </si>
+  <si>
+    <t>006569</t>
+  </si>
+  <si>
+    <t>BANK CAPITAL INDONESIA, PT., Tbk.</t>
+  </si>
+  <si>
+    <t>013099</t>
+  </si>
+  <si>
+    <t>016726</t>
+  </si>
+  <si>
+    <t>0131231</t>
+  </si>
+  <si>
+    <t>021608</t>
+  </si>
+  <si>
+    <t>BANK MAYAPADA INTERNATIONAL, PT. Tbk.</t>
+  </si>
+  <si>
+    <t>013232</t>
+  </si>
+  <si>
+    <t>110953</t>
+  </si>
+  <si>
+    <t>072581</t>
+  </si>
+  <si>
+    <t>353862</t>
+  </si>
+  <si>
+    <t>000879</t>
+  </si>
+  <si>
+    <t>555465</t>
+  </si>
+  <si>
+    <t>064476</t>
+  </si>
+  <si>
+    <t>991270</t>
+  </si>
+  <si>
+    <t>072287</t>
+  </si>
+  <si>
+    <t>EC 993645</t>
+  </si>
+  <si>
+    <t>041928</t>
+  </si>
+  <si>
+    <t>EC 994011</t>
+  </si>
+  <si>
+    <t>055032</t>
+  </si>
+  <si>
+    <t>072047</t>
+  </si>
+  <si>
+    <t>063569</t>
+  </si>
+  <si>
+    <t>072055</t>
+  </si>
+  <si>
+    <t>727990</t>
+  </si>
+  <si>
+    <t>061391</t>
+  </si>
+  <si>
+    <t>028060</t>
+  </si>
+  <si>
+    <t>039651</t>
+  </si>
+  <si>
+    <t>028067</t>
+  </si>
+  <si>
+    <t>274740</t>
+  </si>
+  <si>
+    <t>031594</t>
+  </si>
+  <si>
+    <t>BANK VICTORIA INTERNATIONAL, PT., Tbk.</t>
+  </si>
+  <si>
+    <t>274742</t>
+  </si>
+  <si>
+    <t>274743</t>
+  </si>
+  <si>
+    <t>274744</t>
+  </si>
+  <si>
+    <t>274745</t>
+  </si>
+  <si>
+    <t>638026</t>
+  </si>
+  <si>
+    <t>053347</t>
+  </si>
+  <si>
+    <t>865632</t>
+  </si>
+  <si>
+    <t>032225</t>
+  </si>
+  <si>
+    <t>175346</t>
+  </si>
+  <si>
+    <t>004067</t>
+  </si>
+  <si>
+    <t>BANK WOORI INDONESIA, PT.</t>
+  </si>
+  <si>
+    <t>175381</t>
+  </si>
+  <si>
+    <t>176362</t>
+  </si>
+  <si>
+    <t>610913</t>
+  </si>
+  <si>
+    <t>063763</t>
+  </si>
+  <si>
+    <t>610920</t>
+  </si>
+  <si>
+    <t>70513</t>
+  </si>
+  <si>
+    <t>058132</t>
+  </si>
+  <si>
+    <t>955340</t>
+  </si>
+  <si>
+    <t>018727</t>
+  </si>
+  <si>
+    <t>955382</t>
+  </si>
+  <si>
+    <t>955383</t>
+  </si>
+  <si>
+    <t>003441</t>
+  </si>
+  <si>
+    <t>070541</t>
+  </si>
+  <si>
+    <t>003678</t>
+  </si>
+  <si>
+    <t>214299</t>
+  </si>
+  <si>
+    <t>051856</t>
+  </si>
+  <si>
+    <t>272359</t>
+  </si>
+  <si>
+    <t>280778</t>
+  </si>
+  <si>
+    <t>066399</t>
+  </si>
+  <si>
+    <t>280806</t>
+  </si>
+  <si>
+    <t>280816</t>
+  </si>
+  <si>
+    <t>363985</t>
+  </si>
+  <si>
+    <t>019316</t>
+  </si>
+  <si>
+    <t>453087</t>
+  </si>
+  <si>
+    <t>019267</t>
+  </si>
+  <si>
+    <t>476753</t>
+  </si>
+  <si>
+    <t>038729</t>
+  </si>
+  <si>
+    <t>PT. BANK MESTIKA DHARMA</t>
+  </si>
+  <si>
+    <t>481306</t>
+  </si>
+  <si>
+    <t>062514</t>
+  </si>
+  <si>
+    <t>496757</t>
+  </si>
+  <si>
+    <t>496758</t>
+  </si>
+  <si>
+    <t>496759</t>
+  </si>
+  <si>
+    <t>509201</t>
+  </si>
+  <si>
+    <t>019307</t>
+  </si>
+  <si>
+    <t>509202</t>
+  </si>
+  <si>
+    <t>509203</t>
+  </si>
+  <si>
+    <t>509204</t>
+  </si>
+  <si>
+    <t>509205</t>
+  </si>
+  <si>
+    <t>544679</t>
+  </si>
+  <si>
+    <t>039851</t>
+  </si>
+  <si>
+    <t>803272</t>
+  </si>
+  <si>
+    <t>019416</t>
+  </si>
+  <si>
+    <t>BANK SMBC INDONESIA</t>
+  </si>
+  <si>
+    <t>867011</t>
+  </si>
+  <si>
+    <t>050818</t>
+  </si>
+  <si>
+    <t>867012</t>
+  </si>
+  <si>
+    <t>934596</t>
+  </si>
+  <si>
+    <t>060925</t>
+  </si>
+  <si>
+    <t>934599</t>
+  </si>
+  <si>
+    <t>934600</t>
+  </si>
+  <si>
+    <t>001359</t>
+  </si>
+  <si>
+    <t>077041</t>
+  </si>
+  <si>
+    <t>PT. BANK NAGARI</t>
+  </si>
+  <si>
+    <t>534358</t>
+  </si>
+  <si>
+    <t>067329</t>
+  </si>
+  <si>
+    <t>534359</t>
+  </si>
+  <si>
+    <t>534651</t>
+  </si>
+  <si>
+    <t>534652</t>
+  </si>
+  <si>
+    <t>534653</t>
+  </si>
+  <si>
+    <t>534654</t>
+  </si>
+  <si>
+    <t>534655</t>
+  </si>
+  <si>
+    <t>005204</t>
+  </si>
+  <si>
+    <t>008302</t>
+  </si>
+  <si>
+    <t>031235</t>
+  </si>
+  <si>
+    <t>063371</t>
+  </si>
+  <si>
+    <t>031270</t>
+  </si>
+  <si>
+    <t>031333</t>
+  </si>
+  <si>
+    <t>247697</t>
+  </si>
+  <si>
+    <t>039234</t>
+  </si>
+  <si>
+    <t>247698</t>
+  </si>
+  <si>
+    <t>000111</t>
+  </si>
+  <si>
+    <t>031102</t>
   </si>
   <si>
     <t>BANK UOB INDONESIA, PT.</t>
   </si>
   <si>
-    <t>369459</t>
-  </si>
-  <si>
-    <t>013993</t>
-  </si>
-  <si>
-    <t>BANK MANDIRI</t>
-  </si>
-  <si>
-    <t>369460</t>
-  </si>
-  <si>
-    <t>369461</t>
-  </si>
-  <si>
-    <t>369462</t>
-  </si>
-  <si>
-    <t>369463</t>
-  </si>
-  <si>
-    <t>369464</t>
-  </si>
-  <si>
-    <t>369465</t>
-  </si>
-  <si>
-    <t>369478</t>
-  </si>
-  <si>
-    <t>080685</t>
-  </si>
-  <si>
-    <t>053393</t>
-  </si>
-  <si>
-    <t>BANK DANAMON INDONESIA, PT. Tbk.</t>
-  </si>
-  <si>
-    <t>080687</t>
-  </si>
-  <si>
-    <t>091027</t>
-  </si>
-  <si>
-    <t>262545</t>
-  </si>
-  <si>
-    <t>042777</t>
-  </si>
-  <si>
-    <t>578511</t>
-  </si>
-  <si>
-    <t>040722</t>
-  </si>
-  <si>
-    <t>578612</t>
-  </si>
-  <si>
-    <t>578613</t>
-  </si>
-  <si>
-    <t>626359</t>
-  </si>
-  <si>
-    <t>061077</t>
-  </si>
-  <si>
-    <t>725454</t>
-  </si>
-  <si>
-    <t>069474</t>
-  </si>
-  <si>
-    <t>BANK HANA</t>
-  </si>
-  <si>
-    <t>725455</t>
-  </si>
-  <si>
-    <t>931669</t>
-  </si>
-  <si>
-    <t>065261</t>
-  </si>
-  <si>
-    <t>BANK SYARIAH INDONESIA</t>
-  </si>
-  <si>
-    <t>964415</t>
-  </si>
-  <si>
-    <t>053463</t>
-  </si>
-  <si>
-    <t>964416</t>
-  </si>
-  <si>
-    <t>964417</t>
-  </si>
-  <si>
-    <t>964453</t>
-  </si>
-  <si>
-    <t>964454</t>
-  </si>
-  <si>
-    <t>185809</t>
-  </si>
-  <si>
-    <t>031572</t>
-  </si>
-  <si>
-    <t>488147</t>
-  </si>
-  <si>
-    <t>076052</t>
-  </si>
-  <si>
-    <t>BANK CIMB NIAGA, PT.</t>
-  </si>
-  <si>
-    <t>816391</t>
-  </si>
-  <si>
-    <t>003239</t>
-  </si>
-  <si>
-    <t>BANK MASPION INDONESIA, PT.</t>
-  </si>
-  <si>
-    <t>831678</t>
-  </si>
-  <si>
-    <t>056664</t>
-  </si>
-  <si>
-    <t>973437</t>
-  </si>
-  <si>
-    <t>003236</t>
-  </si>
-  <si>
-    <t>028034</t>
-  </si>
-  <si>
-    <t>039651</t>
-  </si>
-  <si>
-    <t>070531</t>
-  </si>
-  <si>
-    <t>003678</t>
-  </si>
-  <si>
-    <t>074739</t>
-  </si>
-  <si>
-    <t>005416</t>
-  </si>
-  <si>
-    <t>274727</t>
-  </si>
-  <si>
-    <t>031594</t>
-  </si>
-  <si>
-    <t>BANK VICTORIA INTERNATIONAL, PT., Tbk.</t>
-  </si>
-  <si>
-    <t>274728</t>
-  </si>
-  <si>
-    <t>274733</t>
-  </si>
-  <si>
-    <t>638026</t>
-  </si>
-  <si>
-    <t>053347</t>
-  </si>
-  <si>
-    <t>072604</t>
-  </si>
-  <si>
-    <t>018551</t>
+    <t>262355</t>
+  </si>
+  <si>
+    <t>040446</t>
+  </si>
+  <si>
+    <t>561845</t>
+  </si>
+  <si>
+    <t>061460</t>
+  </si>
+  <si>
+    <t>861392</t>
+  </si>
+  <si>
+    <t>003189</t>
+  </si>
+  <si>
+    <t>939864</t>
+  </si>
+  <si>
+    <t>012677</t>
+  </si>
+  <si>
+    <t>939865</t>
+  </si>
+  <si>
+    <t>10583667</t>
+  </si>
+  <si>
+    <t>020110</t>
+  </si>
+  <si>
+    <t>BANK CENTRADANA KAPUAS</t>
+  </si>
+  <si>
+    <t>GHC 716537</t>
+  </si>
+  <si>
+    <t>051938</t>
+  </si>
+  <si>
+    <t>045050</t>
+  </si>
+  <si>
+    <t>040518</t>
+  </si>
+  <si>
+    <t>047823</t>
+  </si>
+  <si>
+    <t>047824</t>
+  </si>
+  <si>
+    <t>054049</t>
+  </si>
+  <si>
+    <t>071313</t>
+  </si>
+  <si>
+    <t>119515</t>
+  </si>
+  <si>
+    <t>064639</t>
+  </si>
+  <si>
+    <t>348397</t>
+  </si>
+  <si>
+    <t>010146</t>
+  </si>
+  <si>
+    <t>444499</t>
+  </si>
+  <si>
+    <t>010091</t>
+  </si>
+  <si>
+    <t>618110</t>
+  </si>
+  <si>
+    <t>618114</t>
+  </si>
+  <si>
+    <t>765537</t>
+  </si>
+  <si>
+    <t>010204</t>
+  </si>
+  <si>
+    <t>BANK ARTHA GRAHA</t>
+  </si>
+  <si>
+    <t>765547</t>
+  </si>
+  <si>
+    <t>863654</t>
+  </si>
+  <si>
+    <t>863673</t>
+  </si>
+  <si>
+    <t>863674</t>
+  </si>
+  <si>
+    <t>BH 394318</t>
+  </si>
+  <si>
+    <t>017475</t>
+  </si>
+  <si>
+    <t>038367</t>
+  </si>
+  <si>
+    <t>065966</t>
+  </si>
+  <si>
+    <t>077799</t>
+  </si>
+  <si>
+    <t>032773</t>
+  </si>
+  <si>
+    <t>097531</t>
+  </si>
+  <si>
+    <t>236178</t>
+  </si>
+  <si>
+    <t>058113</t>
+  </si>
+  <si>
+    <t>290455</t>
+  </si>
+  <si>
+    <t>017884</t>
+  </si>
+  <si>
+    <t>315326</t>
+  </si>
+  <si>
+    <t>001644</t>
   </si>
   <si>
     <t>CIMB NIAGA</t>
   </si>
   <si>
-    <t>175322</t>
-  </si>
-  <si>
-    <t>004067</t>
-  </si>
-  <si>
-    <t>BANK WOORI INDONESIA, PT.</t>
-  </si>
-  <si>
-    <t>175330</t>
-  </si>
-  <si>
-    <t>175346</t>
-  </si>
-  <si>
-    <t>475658</t>
-  </si>
-  <si>
-    <t>004101</t>
-  </si>
-  <si>
-    <t>475671</t>
-  </si>
-  <si>
-    <t>610568</t>
-  </si>
-  <si>
-    <t>063763</t>
-  </si>
-  <si>
-    <t>610913</t>
-  </si>
-  <si>
-    <t>610920</t>
-  </si>
-  <si>
-    <t>927843</t>
-  </si>
-  <si>
-    <t>058132</t>
-  </si>
-  <si>
-    <t>928021</t>
-  </si>
-  <si>
-    <t>018611</t>
-  </si>
-  <si>
-    <t>946649</t>
-  </si>
-  <si>
-    <t>028340</t>
-  </si>
-  <si>
-    <t>946676</t>
-  </si>
-  <si>
-    <t>955330</t>
-  </si>
-  <si>
-    <t>018727</t>
+    <t>315536</t>
+  </si>
+  <si>
+    <t>017793</t>
+  </si>
+  <si>
+    <t>379325</t>
+  </si>
+  <si>
+    <t>066018</t>
+  </si>
+  <si>
+    <t>379340</t>
+  </si>
+  <si>
+    <t>560782</t>
+  </si>
+  <si>
+    <t>010867</t>
   </si>
   <si>
     <t>06272</t>
@@ -390,127 +900,157 @@
     <t>069718</t>
   </si>
   <si>
-    <t>0858</t>
+    <t>111347</t>
+  </si>
+  <si>
+    <t>011976</t>
+  </si>
+  <si>
+    <t>111348</t>
+  </si>
+  <si>
+    <t>111616</t>
+  </si>
+  <si>
+    <t>111617</t>
+  </si>
+  <si>
+    <t>111836</t>
+  </si>
+  <si>
+    <t>111837</t>
+  </si>
+  <si>
+    <t>111838</t>
+  </si>
+  <si>
+    <t>152532</t>
+  </si>
+  <si>
+    <t>037861</t>
+  </si>
+  <si>
+    <t>154837</t>
+  </si>
+  <si>
+    <t>038055</t>
+  </si>
+  <si>
+    <t>154838</t>
+  </si>
+  <si>
+    <t>154839</t>
+  </si>
+  <si>
+    <t>154840</t>
+  </si>
+  <si>
+    <t>159858</t>
+  </si>
+  <si>
+    <t>041826</t>
+  </si>
+  <si>
+    <t>170708</t>
   </si>
   <si>
     <t>011695</t>
   </si>
   <si>
-    <t>09444</t>
-  </si>
-  <si>
-    <t>027462</t>
-  </si>
-  <si>
-    <t>111018</t>
-  </si>
-  <si>
-    <t>011976</t>
-  </si>
-  <si>
-    <t>111345</t>
-  </si>
-  <si>
-    <t>111346</t>
-  </si>
-  <si>
-    <t>111347</t>
-  </si>
-  <si>
-    <t>111348</t>
-  </si>
-  <si>
-    <t>111616</t>
-  </si>
-  <si>
-    <t>111617</t>
-  </si>
-  <si>
-    <t>154836</t>
-  </si>
-  <si>
-    <t>038055</t>
-  </si>
-  <si>
-    <t>154837</t>
-  </si>
-  <si>
-    <t>154838</t>
-  </si>
-  <si>
-    <t>154839</t>
-  </si>
-  <si>
-    <t>154840</t>
-  </si>
-  <si>
-    <t>238554</t>
+    <t>170989</t>
+  </si>
+  <si>
+    <t>066499</t>
+  </si>
+  <si>
+    <t>238726</t>
   </si>
   <si>
     <t>032136</t>
   </si>
   <si>
-    <t>BANK INDEX SELINDO, PT.</t>
-  </si>
-  <si>
-    <t>238562</t>
-  </si>
-  <si>
-    <t>2387</t>
-  </si>
-  <si>
     <t>258965</t>
   </si>
   <si>
     <t>076766</t>
   </si>
   <si>
+    <t>26406</t>
+  </si>
+  <si>
     <t>265950</t>
   </si>
   <si>
     <t>076773</t>
   </si>
   <si>
+    <t>266090</t>
+  </si>
+  <si>
     <t>283163</t>
   </si>
   <si>
     <t>074324</t>
   </si>
   <si>
+    <t>283357</t>
+  </si>
+  <si>
     <t>58592</t>
   </si>
   <si>
     <t>053677</t>
   </si>
   <si>
-    <t>67713</t>
-  </si>
-  <si>
-    <t>036724</t>
-  </si>
-  <si>
-    <t>79326</t>
-  </si>
-  <si>
-    <t>001990</t>
-  </si>
-  <si>
-    <t>793319</t>
-  </si>
-  <si>
-    <t>974424</t>
-  </si>
-  <si>
-    <t>974425</t>
-  </si>
-  <si>
-    <t>997974</t>
+    <t>63696</t>
+  </si>
+  <si>
+    <t>038284</t>
+  </si>
+  <si>
+    <t>998024</t>
   </si>
   <si>
     <t>065920</t>
   </si>
   <si>
-    <t>997975</t>
+    <t>998025</t>
+  </si>
+  <si>
+    <t>AAP 528963</t>
+  </si>
+  <si>
+    <t>024994</t>
+  </si>
+  <si>
+    <t>GHC 231986</t>
+  </si>
+  <si>
+    <t>044734</t>
+  </si>
+  <si>
+    <t>BBA 871589</t>
+  </si>
+  <si>
+    <t>011149</t>
+  </si>
+  <si>
+    <t>BANK BUMI ARTA PT.</t>
+  </si>
+  <si>
+    <t>EC 277334</t>
+  </si>
+  <si>
+    <t>001851</t>
+  </si>
+  <si>
+    <t>GC 393667</t>
+  </si>
+  <si>
+    <t>001854</t>
+  </si>
+  <si>
+    <t>BANK MNC INTERNATIONAL TBK. PT</t>
   </si>
 </sst>
 </file>
@@ -800,7 +1340,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F201"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="16.7109375" customWidth="1"/>
@@ -856,13 +1396,13 @@
         <v>12</v>
       </c>
       <c r="C4" s="5">
-        <v>6918000</v>
+        <v>777000</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="6">
-        <v>45966</v>
+        <v>45976</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>14</v>
@@ -873,16 +1413,16 @@
         <v>15</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C5" s="5">
-        <v>6725000</v>
+        <v>1667000</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E5" s="6">
-        <v>45967</v>
+        <v>45983</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>14</v>
@@ -890,19 +1430,19 @@
     </row>
     <row r="6" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C6" s="5">
-        <v>21840000</v>
+        <v>1740000</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E6" s="6">
-        <v>44296</v>
+        <v>45979</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>14</v>
@@ -910,19 +1450,19 @@
     </row>
     <row r="7" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="5">
-        <v>40710000</v>
+        <v>21840000</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="6">
-        <v>44310</v>
+        <v>44296</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>14</v>
@@ -930,19 +1470,19 @@
     </row>
     <row r="8" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C8" s="5">
-        <v>2067000</v>
+        <v>40710000</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E8" s="6">
-        <v>45968</v>
+        <v>44310</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>14</v>
@@ -950,19 +1490,19 @@
     </row>
     <row r="9" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C9" s="5">
-        <v>2530000</v>
+        <v>5784200</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E9" s="6">
-        <v>45973</v>
+        <v>45986</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>14</v>
@@ -970,19 +1510,19 @@
     </row>
     <row r="10" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C10" s="5">
-        <v>2875200</v>
+        <v>5437000</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E10" s="6">
-        <v>45971</v>
+        <v>45975</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>14</v>
@@ -990,19 +1530,19 @@
     </row>
     <row r="11" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C11" s="5">
-        <v>5437000</v>
+        <v>4068500</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E11" s="6">
-        <v>45975</v>
+        <v>45992</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>14</v>
@@ -1010,19 +1550,19 @@
     </row>
     <row r="12" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C12" s="5">
-        <v>664300</v>
+        <v>4292300</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E12" s="6">
-        <v>45978</v>
+        <v>46000</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>14</v>
@@ -1030,19 +1570,19 @@
     </row>
     <row r="13" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C13" s="5">
-        <v>1831500</v>
+        <v>1217500</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E13" s="6">
-        <v>45962</v>
+        <v>45994</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>14</v>
@@ -1050,19 +1590,19 @@
     </row>
     <row r="14" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C14" s="5">
-        <v>15000000</v>
+        <v>664300</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E14" s="6">
-        <v>45971</v>
+        <v>45978</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>14</v>
@@ -1070,19 +1610,19 @@
     </row>
     <row r="15" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C15" s="5">
-        <v>14794000</v>
+        <v>12936000</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E15" s="6">
-        <v>45975</v>
+        <v>45989</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>14</v>
@@ -1090,19 +1630,19 @@
     </row>
     <row r="16" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C16" s="5">
-        <v>11400000</v>
+        <v>12500000</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E16" s="6">
-        <v>45979</v>
+        <v>46006</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>14</v>
@@ -1110,19 +1650,19 @@
     </row>
     <row r="17" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C17" s="5">
-        <v>11406000</v>
+        <v>12500000</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E17" s="6">
-        <v>45983</v>
+        <v>46010</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>14</v>
@@ -1130,19 +1670,19 @@
     </row>
     <row r="18" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C18" s="5">
-        <v>13600000</v>
+        <v>12072000</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E18" s="6">
-        <v>45992</v>
+        <v>46001</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>14</v>
@@ -1150,19 +1690,19 @@
     </row>
     <row r="19" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C19" s="5">
-        <v>13600000</v>
+        <v>14794000</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E19" s="6">
-        <v>45996</v>
+        <v>45975</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>14</v>
@@ -1170,19 +1710,19 @@
     </row>
     <row r="20" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C20" s="5">
-        <v>14188000</v>
+        <v>11400000</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E20" s="6">
-        <v>45999</v>
+        <v>45979</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>14</v>
@@ -1190,19 +1730,19 @@
     </row>
     <row r="21" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C21" s="5">
-        <v>14539000</v>
+        <v>11406000</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E21" s="6">
-        <v>45965</v>
+        <v>45983</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>14</v>
@@ -1210,19 +1750,19 @@
     </row>
     <row r="22" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C22" s="5">
-        <v>30966000</v>
+        <v>13600000</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E22" s="6">
-        <v>45967</v>
+        <v>45992</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>14</v>
@@ -1230,19 +1770,19 @@
     </row>
     <row r="23" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C23" s="5">
-        <v>5569000</v>
+        <v>13600000</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E23" s="6">
-        <v>45972</v>
+        <v>45996</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>14</v>
@@ -1250,19 +1790,19 @@
     </row>
     <row r="24" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C24" s="5">
-        <v>1072000</v>
+        <v>14188000</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E24" s="6">
-        <v>45973</v>
+        <v>45999</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>14</v>
@@ -1270,19 +1810,19 @@
     </row>
     <row r="25" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C25" s="5">
-        <v>10779200</v>
+        <v>42108750</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="E25" s="6">
-        <v>45964</v>
+        <v>45975</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>14</v>
@@ -1290,19 +1830,19 @@
     </row>
     <row r="26" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C26" s="5">
-        <v>4015400</v>
+        <v>285519683</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="E26" s="6">
-        <v>45965</v>
+        <v>45384</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>14</v>
@@ -1310,19 +1850,19 @@
     </row>
     <row r="27" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C27" s="5">
-        <v>2521000</v>
+        <v>255499245</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="E27" s="6">
-        <v>45976</v>
+        <v>45407</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>14</v>
@@ -1330,19 +1870,19 @@
     </row>
     <row r="28" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C28" s="5">
-        <v>1832600</v>
+        <v>4504970</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="E28" s="6">
-        <v>45990</v>
+        <v>45974</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>14</v>
@@ -1350,19 +1890,19 @@
     </row>
     <row r="29" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C29" s="5">
-        <v>145757371</v>
+        <v>5809000</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="E29" s="6">
-        <v>45986</v>
+        <v>45979</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>14</v>
@@ -1370,19 +1910,19 @@
     </row>
     <row r="30" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C30" s="5">
-        <v>52039200</v>
+        <v>12488000</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E30" s="6">
-        <v>45961</v>
+        <v>45982</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>14</v>
@@ -1390,19 +1930,19 @@
     </row>
     <row r="31" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C31" s="5">
-        <v>42333400</v>
+        <v>12457000</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E31" s="6">
-        <v>45967</v>
+        <v>45988</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>14</v>
@@ -1410,19 +1950,19 @@
     </row>
     <row r="32" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C32" s="5">
-        <v>150000000</v>
+        <v>11278700</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E32" s="6">
-        <v>45222</v>
+        <v>45976</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>14</v>
@@ -1430,19 +1970,19 @@
     </row>
     <row r="33" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C33" s="5">
-        <v>40720000</v>
+        <v>54761000</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E33" s="6">
-        <v>45965</v>
+        <v>45978</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>14</v>
@@ -1450,19 +1990,19 @@
     </row>
     <row r="34" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C34" s="5">
-        <v>51045000</v>
+        <v>22285000</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E34" s="6">
-        <v>45966</v>
+        <v>45980</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>14</v>
@@ -1470,19 +2010,19 @@
     </row>
     <row r="35" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C35" s="5">
-        <v>16207000</v>
+        <v>2521000</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="E35" s="6">
-        <v>45969</v>
+        <v>45976</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>14</v>
@@ -1490,19 +2030,19 @@
     </row>
     <row r="36" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C36" s="5">
-        <v>146832000</v>
+        <v>1832600</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="E36" s="6">
-        <v>45973</v>
+        <v>45990</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>14</v>
@@ -1510,19 +2050,19 @@
     </row>
     <row r="37" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C37" s="5">
-        <v>902000</v>
+        <v>145757371</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="E37" s="6">
-        <v>45974</v>
+        <v>45986</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>14</v>
@@ -1530,19 +2070,19 @@
     </row>
     <row r="38" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C38" s="5">
+        <v>133379900</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C38" s="5">
-        <v>1542900</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="E38" s="6">
-        <v>45961</v>
+        <v>45978</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>14</v>
@@ -1550,19 +2090,19 @@
     </row>
     <row r="39" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" s="5">
+        <v>7929100</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C39" s="5">
-        <v>358666</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>76</v>
-      </c>
       <c r="E39" s="6">
-        <v>45965</v>
+        <v>45989</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>14</v>
@@ -1570,19 +2110,19 @@
     </row>
     <row r="40" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C40" s="5">
-        <v>7190000</v>
+        <v>31015700</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E40" s="6">
-        <v>45966</v>
+        <v>45986</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>14</v>
@@ -1590,19 +2130,19 @@
     </row>
     <row r="41" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C41" s="5">
-        <v>14379900</v>
+        <v>31238700</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="E41" s="6">
-        <v>45964</v>
+        <v>45996</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>14</v>
@@ -1610,19 +2150,19 @@
     </row>
     <row r="42" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C42" s="5">
-        <v>18600000</v>
+        <v>2908300</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="E42" s="6">
-        <v>45966</v>
+        <v>45992</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>14</v>
@@ -1630,19 +2170,19 @@
     </row>
     <row r="43" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="C43" s="5">
-        <v>949050</v>
+        <v>8433300</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="E43" s="6">
-        <v>45964</v>
+        <v>45981</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>14</v>
@@ -1650,19 +2190,19 @@
     </row>
     <row r="44" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C44" s="5">
-        <v>16022100</v>
+        <v>150000000</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="E44" s="6">
-        <v>45965</v>
+        <v>45222</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>14</v>
@@ -1670,19 +2210,19 @@
     </row>
     <row r="45" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C45" s="5">
-        <v>18400000</v>
+        <v>2524000</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E45" s="6">
-        <v>45966</v>
+        <v>45982</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>14</v>
@@ -1690,19 +2230,19 @@
     </row>
     <row r="46" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C46" s="5">
-        <v>2869000</v>
+        <v>10865500</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="E46" s="6">
-        <v>45962</v>
+        <v>45976</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>14</v>
@@ -1710,19 +2250,19 @@
     </row>
     <row r="47" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C47" s="5">
-        <v>2869000</v>
+        <v>13410300</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="E47" s="6">
-        <v>45965</v>
+        <v>45982</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>14</v>
@@ -1730,19 +2270,19 @@
     </row>
     <row r="48" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C48" s="5">
-        <v>5278100</v>
+        <v>59392100</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="E48" s="6">
-        <v>45969</v>
+        <v>45982</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>14</v>
@@ -1750,19 +2290,19 @@
     </row>
     <row r="49" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C49" s="5">
-        <v>146086354</v>
+        <v>2800000</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="E49" s="6">
-        <v>45980</v>
+        <v>45978</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>14</v>
@@ -1770,19 +2310,19 @@
     </row>
     <row r="50" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C50" s="5">
-        <v>13609000</v>
+        <v>1100000</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E50" s="6">
-        <v>45960</v>
+        <v>45995</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>14</v>
@@ -1790,19 +2330,19 @@
     </row>
     <row r="51" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C51" s="5">
-        <v>35790500</v>
+        <v>16135400</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E51" s="6">
-        <v>45962</v>
+        <v>45974</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>14</v>
@@ -1810,19 +2350,19 @@
     </row>
     <row r="52" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C52" s="5">
-        <v>13068900</v>
+        <v>1263180</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="E52" s="6">
-        <v>45969</v>
+        <v>45982</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>14</v>
@@ -1830,19 +2370,19 @@
     </row>
     <row r="53" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C53" s="5">
-        <v>28394100</v>
+        <v>3038958</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="E53" s="6">
-        <v>45976</v>
+        <v>45983</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>14</v>
@@ -1850,19 +2390,19 @@
     </row>
     <row r="54" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C54" s="5">
-        <v>33115000</v>
+        <v>3187143</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E54" s="6">
-        <v>45962</v>
+        <v>45973</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>14</v>
@@ -1870,19 +2410,19 @@
     </row>
     <row r="55" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C55" s="5">
-        <v>12838000</v>
+        <v>17062464</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E55" s="6">
-        <v>45969</v>
+        <v>45997</v>
       </c>
       <c r="F55" s="5" t="s">
         <v>14</v>
@@ -1890,19 +2430,19 @@
     </row>
     <row r="56" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C56" s="5">
-        <v>18329700</v>
+        <v>1110000</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E56" s="6">
-        <v>45962</v>
+        <v>46001</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>14</v>
@@ -1910,19 +2450,19 @@
     </row>
     <row r="57" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C57" s="5">
-        <v>17794900</v>
+        <v>18926000</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="E57" s="6">
-        <v>45976</v>
+        <v>45826</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>14</v>
@@ -1930,19 +2470,19 @@
     </row>
     <row r="58" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C58" s="5">
-        <v>59272200</v>
+        <v>1148250</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="E58" s="6">
-        <v>46000</v>
+        <v>45991</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>14</v>
@@ -1950,19 +2490,19 @@
     </row>
     <row r="59" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C59" s="5">
-        <v>20369300</v>
+        <v>2384615</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="E59" s="6">
-        <v>45965</v>
+        <v>45977</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>14</v>
@@ -1970,19 +2510,19 @@
     </row>
     <row r="60" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C60" s="5">
-        <v>20151000</v>
+        <v>2286600</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="E60" s="6">
-        <v>45969</v>
+        <v>45980</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>14</v>
@@ -1990,19 +2530,19 @@
     </row>
     <row r="61" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="C61" s="5">
-        <v>1446000</v>
+        <v>1254300</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="E61" s="6">
-        <v>45971</v>
+        <v>45977</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>14</v>
@@ -2010,19 +2550,19 @@
     </row>
     <row r="62" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C62" s="5">
-        <v>8102000</v>
+        <v>6312800</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="E62" s="6">
-        <v>45964</v>
+        <v>45976</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>14</v>
@@ -2030,19 +2570,19 @@
     </row>
     <row r="63" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C63" s="5">
-        <v>122786000</v>
+        <v>15944040</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="E63" s="6">
-        <v>45969</v>
+        <v>45975</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>14</v>
@@ -2050,19 +2590,19 @@
     </row>
     <row r="64" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C64" s="5">
-        <v>4007900</v>
+        <v>13134671</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="E64" s="6">
-        <v>45976</v>
+        <v>45989</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>14</v>
@@ -2070,19 +2610,19 @@
     </row>
     <row r="65" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C65" s="5">
-        <v>1353600</v>
+        <v>10162000</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>13</v>
+        <v>120</v>
       </c>
       <c r="E65" s="6">
-        <v>45969</v>
+        <v>45987</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>14</v>
@@ -2090,19 +2630,19 @@
     </row>
     <row r="66" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C66" s="5">
-        <v>15744000</v>
+        <v>52787160</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E66" s="6">
-        <v>45968</v>
+        <v>45978</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>14</v>
@@ -2110,19 +2650,19 @@
     </row>
     <row r="67" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C67" s="5">
-        <v>8687000</v>
+        <v>9331000</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="E67" s="6">
-        <v>45969</v>
+        <v>45971</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>14</v>
@@ -2130,19 +2670,19 @@
     </row>
     <row r="68" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C68" s="5">
-        <v>9168000</v>
+        <v>15285500</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="E68" s="6">
-        <v>45963</v>
+        <v>45976</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>14</v>
@@ -2150,19 +2690,19 @@
     </row>
     <row r="69" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>128</v>
       </c>
       <c r="C69" s="5">
-        <v>9169000</v>
+        <v>31020120</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="E69" s="6">
-        <v>45965</v>
+        <v>45982</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>14</v>
@@ -2170,19 +2710,19 @@
     </row>
     <row r="70" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C70" s="5">
-        <v>7295000</v>
+        <v>12426277</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E70" s="6">
-        <v>45979</v>
+        <v>45976</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>14</v>
@@ -2190,19 +2730,19 @@
     </row>
     <row r="71" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B71" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B71" s="5" t="s">
-        <v>128</v>
-      </c>
       <c r="C71" s="5">
-        <v>7295000</v>
+        <v>108725300</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="E71" s="6">
-        <v>45980</v>
+        <v>45979</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>14</v>
@@ -2213,16 +2753,16 @@
         <v>133</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C72" s="5">
-        <v>8117000</v>
+        <v>1665000</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="E72" s="6">
-        <v>45990</v>
+        <v>45985</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>14</v>
@@ -2230,19 +2770,19 @@
     </row>
     <row r="73" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C73" s="5">
-        <v>12961000</v>
+        <v>2623548</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="E73" s="6">
-        <v>45976</v>
+        <v>45986</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>14</v>
@@ -2250,19 +2790,19 @@
     </row>
     <row r="74" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C74" s="5">
-        <v>71591700</v>
+        <v>2201605</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="E74" s="6">
-        <v>45969</v>
+        <v>45979</v>
       </c>
       <c r="F74" s="5" t="s">
         <v>14</v>
@@ -2270,19 +2810,19 @@
     </row>
     <row r="75" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C75" s="5">
-        <v>26350500</v>
+        <v>226898425</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="E75" s="6">
-        <v>45978</v>
+        <v>45975</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>14</v>
@@ -2290,19 +2830,19 @@
     </row>
     <row r="76" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C76" s="5">
-        <v>3164800</v>
+        <v>10703563</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="E76" s="6">
-        <v>45990</v>
+        <v>45982</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>14</v>
@@ -2310,19 +2850,19 @@
     </row>
     <row r="77" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C77" s="5">
-        <v>15564800</v>
+        <v>20765100</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="E77" s="6">
-        <v>46004</v>
+        <v>45975</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>14</v>
@@ -2330,19 +2870,19 @@
     </row>
     <row r="78" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C78" s="5">
-        <v>49116000</v>
+        <v>85501080</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="E78" s="6">
-        <v>46011</v>
+        <v>45975</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>14</v>
@@ -2350,19 +2890,19 @@
     </row>
     <row r="79" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C79" s="5">
-        <v>140011626</v>
+        <v>15406256</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>143</v>
+        <v>53</v>
       </c>
       <c r="E79" s="6">
-        <v>45962</v>
+        <v>45986</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>14</v>
@@ -2370,19 +2910,19 @@
     </row>
     <row r="80" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C80" s="5">
-        <v>200835560</v>
+        <v>3181300</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E80" s="6">
-        <v>45969</v>
+        <v>45999</v>
       </c>
       <c r="F80" s="5" t="s">
         <v>14</v>
@@ -2390,19 +2930,19 @@
     </row>
     <row r="81" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C81" s="5">
-        <v>49658070</v>
+        <v>7904200</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E81" s="6">
-        <v>45962</v>
+        <v>45976</v>
       </c>
       <c r="F81" s="5" t="s">
         <v>14</v>
@@ -2410,19 +2950,19 @@
     </row>
     <row r="82" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C82" s="5">
-        <v>1217000</v>
+        <v>7904200</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="E82" s="6">
-        <v>45976</v>
+        <v>45980</v>
       </c>
       <c r="F82" s="5" t="s">
         <v>14</v>
@@ -2430,19 +2970,19 @@
     </row>
     <row r="83" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B83" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B83" s="5" t="s">
+      <c r="C83" s="5">
+        <v>7904200</v>
+      </c>
+      <c r="D83" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="C83" s="5">
-        <v>437000</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>24</v>
-      </c>
       <c r="E83" s="6">
-        <v>45997</v>
+        <v>45982</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>14</v>
@@ -2450,19 +2990,19 @@
     </row>
     <row r="84" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C84" s="5">
-        <v>80425000</v>
+        <v>3181300</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
       <c r="E84" s="6">
-        <v>45980</v>
+        <v>45994</v>
       </c>
       <c r="F84" s="5" t="s">
         <v>14</v>
@@ -2470,19 +3010,19 @@
     </row>
     <row r="85" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C85" s="5">
-        <v>1030000</v>
+        <v>146086354</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E85" s="6">
-        <v>45991</v>
+        <v>45980</v>
       </c>
       <c r="F85" s="5" t="s">
         <v>14</v>
@@ -2490,19 +3030,19 @@
     </row>
     <row r="86" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C86" s="5">
-        <v>13708480</v>
+        <v>7053556</v>
       </c>
       <c r="D86" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E86" s="6">
-        <v>45964</v>
+        <v>45986</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>14</v>
@@ -2510,19 +3050,19 @@
     </row>
     <row r="87" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C87" s="5">
-        <v>3496500</v>
+        <v>28394100</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="E87" s="6">
-        <v>45958</v>
+        <v>45976</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>14</v>
@@ -2530,19 +3070,19 @@
     </row>
     <row r="88" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C88" s="5">
-        <v>4908983</v>
+        <v>22012300</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="E88" s="6">
-        <v>45950</v>
+        <v>45992</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>14</v>
@@ -2550,19 +3090,19 @@
     </row>
     <row r="89" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B89" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B89" s="5" t="s">
-        <v>128</v>
-      </c>
       <c r="C89" s="5">
-        <v>9341000</v>
+        <v>11336400</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="E89" s="6">
-        <v>45969</v>
+        <v>45983</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>14</v>
@@ -2570,19 +3110,19 @@
     </row>
     <row r="90" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="C90" s="5">
-        <v>9341000</v>
+        <v>17794900</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="E90" s="6">
-        <v>45972</v>
+        <v>45976</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>14</v>
@@ -2590,19 +3130,19 @@
     </row>
     <row r="91" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C91" s="5">
-        <v>38500000</v>
+        <v>59272200</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="E91" s="6">
-        <v>45962</v>
+        <v>46000</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>14</v>
@@ -2610,21 +3150,2201 @@
     </row>
     <row r="92" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C92" s="5">
-        <v>37765000</v>
+        <v>17089200</v>
       </c>
       <c r="D92" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E92" s="6">
+        <v>45982</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A93" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C93" s="5">
+        <v>7130000</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E93" s="6">
+        <v>45976</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A94" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C94" s="5">
+        <v>52220000</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E94" s="6">
+        <v>45989</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A95" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C95" s="5">
+        <v>34893000</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E95" s="6">
+        <v>45996</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A96" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C96" s="5">
+        <v>35500000</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E96" s="6">
+        <v>45987</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A97" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C97" s="5">
+        <v>17700000</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E97" s="6">
+        <v>45989</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A98" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C98" s="5">
+        <v>38479059</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E98" s="6">
+        <v>45980</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A99" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C99" s="5">
+        <v>23160869</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E99" s="6">
+        <v>46015</v>
+      </c>
+      <c r="F99" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A100" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C100" s="5">
+        <v>17127000</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E100" s="6">
+        <v>45982</v>
+      </c>
+      <c r="F100" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A101" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C101" s="5">
+        <v>109871000</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E101" s="6">
+        <v>46014</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A102" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C102" s="5">
+        <v>60913000</v>
+      </c>
+      <c r="D102" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E102" s="6">
+        <v>46017</v>
+      </c>
+      <c r="F102" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A103" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C103" s="5">
+        <v>5225200</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E103" s="6">
+        <v>45988</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A104" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C104" s="5">
+        <v>35000000</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E104" s="6">
+        <v>45980</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A105" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C105" s="5">
+        <v>53440500</v>
+      </c>
+      <c r="D105" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E105" s="6">
+        <v>45975</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A106" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C106" s="5">
+        <v>69050000</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E106" s="6">
+        <v>45979</v>
+      </c>
+      <c r="F106" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A107" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C107" s="5">
+        <v>50285000</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E107" s="6">
+        <v>45976</v>
+      </c>
+      <c r="F107" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A108" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C108" s="5">
+        <v>50285000</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E108" s="6">
+        <v>45981</v>
+      </c>
+      <c r="F108" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A109" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C109" s="5">
+        <v>50285000</v>
+      </c>
+      <c r="D109" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E109" s="6">
+        <v>45983</v>
+      </c>
+      <c r="F109" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A110" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C110" s="5">
+        <v>24642000</v>
+      </c>
+      <c r="D110" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E110" s="6">
+        <v>45982</v>
+      </c>
+      <c r="F110" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A111" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C111" s="5">
+        <v>19980000</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E111" s="6">
+        <v>45980</v>
+      </c>
+      <c r="F111" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A112" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C112" s="5">
+        <v>19480500</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E112" s="6">
+        <v>45981</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A113" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C113" s="5">
+        <v>35964000</v>
+      </c>
+      <c r="D113" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E113" s="6">
+        <v>45983</v>
+      </c>
+      <c r="F113" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A114" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C114" s="5">
+        <v>19092000</v>
+      </c>
+      <c r="D114" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="E114" s="6">
+        <v>45980</v>
+      </c>
+      <c r="F114" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A115" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C115" s="5">
+        <v>113935950</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E115" s="6">
+        <v>46000</v>
+      </c>
+      <c r="F115" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A116" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C116" s="5">
+        <v>12098813</v>
+      </c>
+      <c r="D116" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="E116" s="6">
+        <v>45973</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A117" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C117" s="5">
+        <v>69748368</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E117" s="6">
+        <v>45987</v>
+      </c>
+      <c r="F117" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A118" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C118" s="5">
+        <v>109105340</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E118" s="6">
+        <v>45981</v>
+      </c>
+      <c r="F118" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A119" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C119" s="5">
+        <v>9632000</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E119" s="6">
+        <v>46001</v>
+      </c>
+      <c r="F119" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A120" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C120" s="5">
+        <v>13193000</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E120" s="6">
+        <v>45980</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A121" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="C121" s="5">
+        <v>5636000</v>
+      </c>
+      <c r="D121" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E121" s="6">
+        <v>45990</v>
+      </c>
+      <c r="F121" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A122" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C122" s="5">
+        <v>7877800</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="E122" s="6">
+        <v>45978</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A123" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C123" s="5">
+        <v>49550900</v>
+      </c>
+      <c r="D123" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E123" s="6">
+        <v>45976</v>
+      </c>
+      <c r="F123" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A124" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C124" s="5">
+        <v>7990900</v>
+      </c>
+      <c r="D124" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E124" s="6">
+        <v>45985</v>
+      </c>
+      <c r="F124" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A125" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C125" s="5">
+        <v>3871100</v>
+      </c>
+      <c r="D125" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E125" s="6">
+        <v>45978</v>
+      </c>
+      <c r="F125" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A126" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C126" s="5">
+        <v>12367800</v>
+      </c>
+      <c r="D126" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E126" s="6">
+        <v>45984</v>
+      </c>
+      <c r="F126" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A127" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C127" s="5">
+        <v>10635600</v>
+      </c>
+      <c r="D127" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E127" s="6">
+        <v>45990</v>
+      </c>
+      <c r="F127" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A128" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C128" s="5">
+        <v>17489300</v>
+      </c>
+      <c r="D128" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E128" s="6">
+        <v>46008</v>
+      </c>
+      <c r="F128" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A129" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C129" s="5">
+        <v>40181000</v>
+      </c>
+      <c r="D129" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E129" s="6">
+        <v>45998</v>
+      </c>
+      <c r="F129" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A130" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C130" s="5">
+        <v>13990000</v>
+      </c>
+      <c r="D130" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E130" s="6">
+        <v>46007</v>
+      </c>
+      <c r="F130" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A131" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C131" s="5">
+        <v>42247300</v>
+      </c>
+      <c r="D131" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E131" s="6">
+        <v>45975</v>
+      </c>
+      <c r="F131" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A132" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C132" s="5">
+        <v>7849600</v>
+      </c>
+      <c r="D132" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E132" s="6">
+        <v>45975</v>
+      </c>
+      <c r="F132" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A133" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C133" s="5">
+        <v>3865900</v>
+      </c>
+      <c r="D133" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E133" s="6">
+        <v>45980</v>
+      </c>
+      <c r="F133" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A134" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C134" s="5">
+        <v>2220000</v>
+      </c>
+      <c r="D134" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E134" s="6">
+        <v>45976</v>
+      </c>
+      <c r="F134" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A135" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C135" s="5">
+        <v>2220000</v>
+      </c>
+      <c r="D135" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E135" s="6">
+        <v>45983</v>
+      </c>
+      <c r="F135" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A136" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C136" s="5">
+        <v>11430000</v>
+      </c>
+      <c r="D136" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="E136" s="6">
+        <v>45979</v>
+      </c>
+      <c r="F136" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A137" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C137" s="5">
+        <v>4297000</v>
+      </c>
+      <c r="D137" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E137" s="6">
+        <v>45981</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A138" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C138" s="5">
+        <v>63399800</v>
+      </c>
+      <c r="D138" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E138" s="6">
+        <v>45981</v>
+      </c>
+      <c r="F138" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A139" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C139" s="5">
+        <v>7507067</v>
+      </c>
+      <c r="D139" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E139" s="6">
+        <v>45974</v>
+      </c>
+      <c r="F139" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A140" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C140" s="5">
+        <v>25650300</v>
+      </c>
+      <c r="D140" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E140" s="6">
+        <v>45973</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A141" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C141" s="5">
+        <v>37011000</v>
+      </c>
+      <c r="D141" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E141" s="6">
+        <v>45975</v>
+      </c>
+      <c r="F141" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A142" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C142" s="5">
+        <v>1010100</v>
+      </c>
+      <c r="D142" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="E142" s="6">
+        <v>45982</v>
+      </c>
+      <c r="F142" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A143" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C143" s="5">
+        <v>18493664</v>
+      </c>
+      <c r="D143" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E143" s="6">
+        <v>45978</v>
+      </c>
+      <c r="F143" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A144" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C144" s="5">
+        <v>2645100</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E144" s="6">
+        <v>45980</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A145" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C145" s="5">
+        <v>8088000</v>
+      </c>
+      <c r="D145" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E145" s="6">
+        <v>45975</v>
+      </c>
+      <c r="F145" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A146" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C146" s="5">
+        <v>12472600</v>
+      </c>
+      <c r="D146" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E146" s="6">
+        <v>45976</v>
+      </c>
+      <c r="F146" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A147" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C147" s="5">
+        <v>2518500</v>
+      </c>
+      <c r="D147" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E147" s="6">
+        <v>45979</v>
+      </c>
+      <c r="F147" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A148" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C148" s="5">
+        <v>2251900</v>
+      </c>
+      <c r="D148" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E148" s="6">
+        <v>45989</v>
+      </c>
+      <c r="F148" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A149" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C149" s="5">
+        <v>2835000</v>
+      </c>
+      <c r="D149" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E149" s="6">
+        <v>45974</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A150" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C150" s="5">
+        <v>2077900</v>
+      </c>
+      <c r="D150" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E150" s="6">
+        <v>45995</v>
+      </c>
+      <c r="F150" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A151" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C151" s="5">
+        <v>3283300</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E151" s="6">
+        <v>45981</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A152" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C152" s="5">
+        <v>3322600</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E152" s="6">
+        <v>45986</v>
+      </c>
+      <c r="F152" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A153" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C153" s="5">
+        <v>1122900</v>
+      </c>
+      <c r="D153" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E153" s="6">
+        <v>45999</v>
+      </c>
+      <c r="F153" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A154" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C154" s="5">
+        <v>3639347</v>
+      </c>
+      <c r="D154" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E154" s="6">
+        <v>45996</v>
+      </c>
+      <c r="F154" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A155" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C155" s="5">
+        <v>3570194</v>
+      </c>
+      <c r="D155" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E155" s="6">
+        <v>46004</v>
+      </c>
+      <c r="F155" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A156" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C156" s="5">
+        <v>3153500</v>
+      </c>
+      <c r="D156" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E156" s="6">
+        <v>45976</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A157" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C157" s="5">
+        <v>12053400</v>
+      </c>
+      <c r="D157" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E157" s="6">
+        <v>45990</v>
+      </c>
+      <c r="F157" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A158" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C158" s="5">
+        <v>3153500</v>
+      </c>
+      <c r="D158" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E158" s="6">
+        <v>45994</v>
+      </c>
+      <c r="F158" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A159" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="C159" s="5">
+        <v>472850</v>
+      </c>
+      <c r="D159" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E159" s="6">
+        <v>45981</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A160" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="C160" s="5">
+        <v>17750500</v>
+      </c>
+      <c r="D160" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E160" s="6">
+        <v>45976</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A161" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C161" s="5">
+        <v>1698300</v>
+      </c>
+      <c r="D161" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E161" s="6">
+        <v>45979</v>
+      </c>
+      <c r="F161" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A162" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="C162" s="5">
+        <v>17636650</v>
+      </c>
+      <c r="D162" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E162" s="6">
+        <v>45990</v>
+      </c>
+      <c r="F162" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A163" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="C163" s="5">
+        <v>3470200</v>
+      </c>
+      <c r="D163" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E92" s="6">
-        <v>45966</v>
-      </c>
-      <c r="F92" s="5" t="s">
+      <c r="E163" s="6">
+        <v>45976</v>
+      </c>
+      <c r="F163" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A164" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="C164" s="5">
+        <v>11989000</v>
+      </c>
+      <c r="D164" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E164" s="6">
+        <v>45982</v>
+      </c>
+      <c r="F164" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A165" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="C165" s="5">
+        <v>4000630</v>
+      </c>
+      <c r="D165" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="E165" s="6">
+        <v>45981</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A166" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="C166" s="5">
+        <v>2998100</v>
+      </c>
+      <c r="D166" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E166" s="6">
+        <v>45974</v>
+      </c>
+      <c r="F166" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A167" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="C167" s="5">
+        <v>27723000</v>
+      </c>
+      <c r="D167" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E167" s="6">
+        <v>45979</v>
+      </c>
+      <c r="F167" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A168" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="C168" s="5">
+        <v>9916850</v>
+      </c>
+      <c r="D168" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E168" s="6">
+        <v>45986</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A169" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="C169" s="5">
+        <v>2902700</v>
+      </c>
+      <c r="D169" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E169" s="6">
+        <v>45976</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A170" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="C170" s="5">
+        <v>4007900</v>
+      </c>
+      <c r="D170" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E170" s="6">
+        <v>45976</v>
+      </c>
+      <c r="F170" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A171" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C171" s="5">
+        <v>7295000</v>
+      </c>
+      <c r="D171" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E171" s="6">
+        <v>45979</v>
+      </c>
+      <c r="F171" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A172" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C172" s="5">
+        <v>7295000</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E172" s="6">
+        <v>45980</v>
+      </c>
+      <c r="F172" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A173" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C173" s="5">
+        <v>8117000</v>
+      </c>
+      <c r="D173" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E173" s="6">
+        <v>45990</v>
+      </c>
+      <c r="F173" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A174" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C174" s="5">
+        <v>12961000</v>
+      </c>
+      <c r="D174" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E174" s="6">
+        <v>45976</v>
+      </c>
+      <c r="F174" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A175" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C175" s="5">
+        <v>11569000</v>
+      </c>
+      <c r="D175" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E175" s="6">
+        <v>45994</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A176" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C176" s="5">
+        <v>11074000</v>
+      </c>
+      <c r="D176" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E176" s="6">
+        <v>46002</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A177" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C177" s="5">
+        <v>7296000</v>
+      </c>
+      <c r="D177" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E177" s="6">
+        <v>45983</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A178" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="C178" s="5">
+        <v>3210000</v>
+      </c>
+      <c r="D178" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E178" s="6">
+        <v>45990</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A179" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C179" s="5">
+        <v>26350500</v>
+      </c>
+      <c r="D179" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E179" s="6">
+        <v>45978</v>
+      </c>
+      <c r="F179" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A180" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C180" s="5">
+        <v>3164800</v>
+      </c>
+      <c r="D180" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E180" s="6">
+        <v>45990</v>
+      </c>
+      <c r="F180" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A181" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C181" s="5">
+        <v>15564800</v>
+      </c>
+      <c r="D181" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E181" s="6">
+        <v>46004</v>
+      </c>
+      <c r="F181" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A182" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C182" s="5">
+        <v>49116000</v>
+      </c>
+      <c r="D182" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E182" s="6">
+        <v>46011</v>
+      </c>
+      <c r="F182" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A183" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="C183" s="5">
+        <v>57111290</v>
+      </c>
+      <c r="D183" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E183" s="6">
+        <v>45978</v>
+      </c>
+      <c r="F183" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A184" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C184" s="5">
+        <v>1004500</v>
+      </c>
+      <c r="D184" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E184" s="6">
+        <v>45979</v>
+      </c>
+      <c r="F184" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A185" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="C185" s="5">
+        <v>78000300</v>
+      </c>
+      <c r="D185" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E185" s="6">
+        <v>45978</v>
+      </c>
+      <c r="F185" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A186" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="C186" s="5">
+        <v>15694689</v>
+      </c>
+      <c r="D186" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E186" s="6">
+        <v>45976</v>
+      </c>
+      <c r="F186" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A187" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C187" s="5">
+        <v>1217000</v>
+      </c>
+      <c r="D187" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E187" s="6">
+        <v>45976</v>
+      </c>
+      <c r="F187" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A188" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="C188" s="5">
+        <v>2680000</v>
+      </c>
+      <c r="D188" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E188" s="6">
+        <v>45981</v>
+      </c>
+      <c r="F188" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A189" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C189" s="5">
+        <v>437000</v>
+      </c>
+      <c r="D189" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E189" s="6">
+        <v>45997</v>
+      </c>
+      <c r="F189" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A190" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C190" s="5">
+        <v>3225000</v>
+      </c>
+      <c r="D190" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E190" s="6">
+        <v>46004</v>
+      </c>
+      <c r="F190" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A191" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="C191" s="5">
+        <v>80425000</v>
+      </c>
+      <c r="D191" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E191" s="6">
+        <v>45980</v>
+      </c>
+      <c r="F191" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A192" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="C192" s="5">
+        <v>36419100</v>
+      </c>
+      <c r="D192" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E192" s="6">
+        <v>45995</v>
+      </c>
+      <c r="F192" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A193" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="C193" s="5">
+        <v>1030000</v>
+      </c>
+      <c r="D193" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E193" s="6">
+        <v>45991</v>
+      </c>
+      <c r="F193" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A194" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C194" s="5">
+        <v>16834900</v>
+      </c>
+      <c r="D194" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E194" s="6">
+        <v>45976</v>
+      </c>
+      <c r="F194" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A195" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C195" s="5">
+        <v>18266000</v>
+      </c>
+      <c r="D195" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E195" s="6">
+        <v>45980</v>
+      </c>
+      <c r="F195" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A196" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="C196" s="5">
+        <v>15327000</v>
+      </c>
+      <c r="D196" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E196" s="6">
+        <v>45989</v>
+      </c>
+      <c r="F196" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A197" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C197" s="5">
+        <v>1600342</v>
+      </c>
+      <c r="D197" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E197" s="6">
+        <v>45974</v>
+      </c>
+      <c r="F197" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A198" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="C198" s="5">
+        <v>3338000</v>
+      </c>
+      <c r="D198" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E198" s="6">
+        <v>45976</v>
+      </c>
+      <c r="F198" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A199" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="C199" s="5">
+        <v>13012000</v>
+      </c>
+      <c r="D199" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="E199" s="6">
+        <v>45980</v>
+      </c>
+      <c r="F199" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A200" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="C200" s="5">
+        <v>1364000</v>
+      </c>
+      <c r="D200" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E200" s="6">
+        <v>45979</v>
+      </c>
+      <c r="F200" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A201" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="C201" s="5">
+        <v>4309400</v>
+      </c>
+      <c r="D201" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="E201" s="6">
+        <v>45972</v>
+      </c>
+      <c r="F201" s="5" t="s">
         <v>14</v>
       </c>
     </row>

--- a/uploads/giro.xlsx
+++ b/uploads/giro.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coralis\Eksport Implementasi\20251114\Eksport\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coralis\20251202\fix\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7366BFBC-CBFC-4C9C-BD66-6360E235AA7A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12585"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Giro" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="329">
   <si>
     <t>nomor_giro</t>
   </si>
@@ -54,27 +55,45 @@
     <t>ex: Cair, Belum Cair</t>
   </si>
   <si>
-    <t>201829</t>
+    <t>051546</t>
+  </si>
+  <si>
+    <t>039726</t>
+  </si>
+  <si>
+    <t>BANK CENTRAL ASIA</t>
+  </si>
+  <si>
+    <t>Belum Cair</t>
+  </si>
+  <si>
+    <t>055333</t>
+  </si>
+  <si>
+    <t>001213</t>
+  </si>
+  <si>
+    <t>106583</t>
+  </si>
+  <si>
+    <t>034412</t>
+  </si>
+  <si>
+    <t>201958</t>
+  </si>
+  <si>
+    <t>072546</t>
+  </si>
+  <si>
+    <t>BNI'46</t>
+  </si>
+  <si>
+    <t>201979</t>
   </si>
   <si>
     <t>017071</t>
   </si>
   <si>
-    <t>BNI'46</t>
-  </si>
-  <si>
-    <t>Belum Cair</t>
-  </si>
-  <si>
-    <t>201846</t>
-  </si>
-  <si>
-    <t>201870</t>
-  </si>
-  <si>
-    <t>072546</t>
-  </si>
-  <si>
     <t>239217</t>
   </si>
   <si>
@@ -87,40 +106,43 @@
     <t>239218</t>
   </si>
   <si>
-    <t>502568</t>
+    <t>502618</t>
+  </si>
+  <si>
+    <t>067039</t>
+  </si>
+  <si>
+    <t>BANK PANIN</t>
+  </si>
+  <si>
+    <t>502737</t>
   </si>
   <si>
     <t>037981</t>
   </si>
   <si>
-    <t>BANK PANIN</t>
-  </si>
-  <si>
-    <t>502591</t>
-  </si>
-  <si>
-    <t>067039</t>
-  </si>
-  <si>
-    <t>502608</t>
-  </si>
-  <si>
-    <t>502618</t>
-  </si>
-  <si>
-    <t>502737</t>
-  </si>
-  <si>
-    <t>517238</t>
-  </si>
-  <si>
-    <t>000956</t>
-  </si>
-  <si>
-    <t>BANK JABAR</t>
-  </si>
-  <si>
-    <t>174003</t>
+    <t>502744</t>
+  </si>
+  <si>
+    <t>502812</t>
+  </si>
+  <si>
+    <t>829069</t>
+  </si>
+  <si>
+    <t>065300</t>
+  </si>
+  <si>
+    <t>BANK RAKYAT INDONESIA (PERSERO), Tbk.</t>
+  </si>
+  <si>
+    <t>006824</t>
+  </si>
+  <si>
+    <t>014270</t>
+  </si>
+  <si>
+    <t>174004</t>
   </si>
   <si>
     <t>013993</t>
@@ -129,40 +151,19 @@
     <t>BANK MANDIRI</t>
   </si>
   <si>
-    <t>174004</t>
-  </si>
-  <si>
     <t>174005</t>
   </si>
   <si>
     <t>174006</t>
   </si>
   <si>
-    <t>369460</t>
-  </si>
-  <si>
-    <t>369461</t>
-  </si>
-  <si>
-    <t>369462</t>
-  </si>
-  <si>
-    <t>369463</t>
-  </si>
-  <si>
-    <t>369464</t>
-  </si>
-  <si>
-    <t>369465</t>
-  </si>
-  <si>
-    <t>046471</t>
-  </si>
-  <si>
-    <t>061065</t>
-  </si>
-  <si>
-    <t>BANK RAKYAT INDONESIA (PERSERO), Tbk.</t>
+    <t>174027</t>
+  </si>
+  <si>
+    <t>147244</t>
+  </si>
+  <si>
+    <t>030419</t>
   </si>
   <si>
     <t>716497</t>
@@ -174,826 +175,775 @@
     <t>716634</t>
   </si>
   <si>
-    <t>032723</t>
-  </si>
-  <si>
-    <t>052428</t>
+    <t>116116</t>
+  </si>
+  <si>
+    <t>053393</t>
   </si>
   <si>
     <t>BANK DANAMON INDONESIA, PT. Tbk.</t>
   </si>
   <si>
-    <t>091063</t>
-  </si>
-  <si>
-    <t>053393</t>
-  </si>
-  <si>
-    <t>091066</t>
-  </si>
-  <si>
-    <t>105142</t>
-  </si>
-  <si>
-    <t>262630</t>
-  </si>
-  <si>
-    <t>042777</t>
+    <t>126488</t>
+  </si>
+  <si>
+    <t>053463</t>
+  </si>
+  <si>
+    <t>623154</t>
+  </si>
+  <si>
+    <t>626356</t>
+  </si>
+  <si>
+    <t>061077</t>
+  </si>
+  <si>
+    <t>626357</t>
+  </si>
+  <si>
+    <t>626360</t>
+  </si>
+  <si>
+    <t>725660</t>
+  </si>
+  <si>
+    <t>069474</t>
+  </si>
+  <si>
+    <t>BANK HANA</t>
+  </si>
+  <si>
+    <t>738885</t>
+  </si>
+  <si>
+    <t>BANK OCBC - INDONESIA, PT.</t>
+  </si>
+  <si>
+    <t>931669</t>
+  </si>
+  <si>
+    <t>065261</t>
+  </si>
+  <si>
+    <t>BANK SYARIAH INDONESIA</t>
+  </si>
+  <si>
+    <t>054420</t>
+  </si>
+  <si>
+    <t>012972</t>
+  </si>
+  <si>
+    <t>054421</t>
+  </si>
+  <si>
+    <t>477341</t>
+  </si>
+  <si>
+    <t>018947</t>
+  </si>
+  <si>
+    <t>816998</t>
+  </si>
+  <si>
+    <t>003239</t>
+  </si>
+  <si>
+    <t>BANK MASPION INDONESIA, PT.</t>
+  </si>
+  <si>
+    <t>973383</t>
+  </si>
+  <si>
+    <t>003236</t>
+  </si>
+  <si>
+    <t>033207</t>
+  </si>
+  <si>
+    <t>052835</t>
+  </si>
+  <si>
+    <t>217599</t>
+  </si>
+  <si>
+    <t>005647</t>
+  </si>
+  <si>
+    <t>BANK PERMATA, PT. Tbk.</t>
+  </si>
+  <si>
+    <t>343612</t>
+  </si>
+  <si>
+    <t>030787</t>
+  </si>
+  <si>
+    <t>BANK MEGA</t>
+  </si>
+  <si>
+    <t>343623</t>
+  </si>
+  <si>
+    <t>343629</t>
+  </si>
+  <si>
+    <t>673303</t>
+  </si>
+  <si>
+    <t>673308</t>
+  </si>
+  <si>
+    <t>673317</t>
+  </si>
+  <si>
+    <t>673322</t>
+  </si>
+  <si>
+    <t>AGC 244752</t>
+  </si>
+  <si>
+    <t>006357</t>
+  </si>
+  <si>
+    <t>BANK MAS, PT.</t>
+  </si>
+  <si>
+    <t>AN673290</t>
+  </si>
+  <si>
+    <t>BAG427068</t>
+  </si>
+  <si>
+    <t>051919</t>
+  </si>
+  <si>
+    <t>BANK CIMB NIAGA, PT.</t>
+  </si>
+  <si>
+    <t>BAG427251</t>
+  </si>
+  <si>
+    <t>051913</t>
+  </si>
+  <si>
+    <t>BAG427281</t>
+  </si>
+  <si>
+    <t>BAG427287</t>
+  </si>
+  <si>
+    <t>BAG427300</t>
+  </si>
+  <si>
+    <t>FC098849</t>
+  </si>
+  <si>
+    <t>046770</t>
+  </si>
+  <si>
+    <t>165115</t>
+  </si>
+  <si>
+    <t>015647</t>
+  </si>
+  <si>
+    <t>253726</t>
+  </si>
+  <si>
+    <t>EB 997773</t>
+  </si>
+  <si>
+    <t>008107</t>
+  </si>
+  <si>
+    <t>072086</t>
+  </si>
+  <si>
+    <t>063569</t>
+  </si>
+  <si>
+    <t>072132</t>
+  </si>
+  <si>
+    <t>072136</t>
+  </si>
+  <si>
+    <t>617932</t>
+  </si>
+  <si>
+    <t>023959</t>
+  </si>
+  <si>
+    <t>050853</t>
+  </si>
+  <si>
+    <t>039651</t>
+  </si>
+  <si>
+    <t>050865</t>
+  </si>
+  <si>
+    <t>053377</t>
+  </si>
+  <si>
+    <t>013878</t>
+  </si>
+  <si>
+    <t>274740</t>
+  </si>
+  <si>
+    <t>031594</t>
+  </si>
+  <si>
+    <t>BANK VICTORIA INTERNATIONAL, PT., Tbk.</t>
+  </si>
+  <si>
+    <t>274745</t>
+  </si>
+  <si>
+    <t>274756</t>
+  </si>
+  <si>
+    <t>274758</t>
+  </si>
+  <si>
+    <t>638029</t>
+  </si>
+  <si>
+    <t>053347</t>
+  </si>
+  <si>
+    <t>733962</t>
+  </si>
+  <si>
+    <t>013839</t>
+  </si>
+  <si>
+    <t>BANK SINAR MAS, PT.</t>
+  </si>
+  <si>
+    <t>733980</t>
+  </si>
+  <si>
+    <t>039331</t>
+  </si>
+  <si>
+    <t>175381</t>
+  </si>
+  <si>
+    <t>004067</t>
+  </si>
+  <si>
+    <t>BANK WOORI INDONESIA, PT.</t>
+  </si>
+  <si>
+    <t>175400</t>
+  </si>
+  <si>
+    <t>175416</t>
+  </si>
+  <si>
+    <t>270880</t>
+  </si>
+  <si>
+    <t>029265</t>
+  </si>
+  <si>
+    <t>270894</t>
+  </si>
+  <si>
+    <t>610920</t>
+  </si>
+  <si>
+    <t>063763</t>
+  </si>
+  <si>
+    <t>705453</t>
+  </si>
+  <si>
+    <t>018611</t>
+  </si>
+  <si>
+    <t>705596</t>
+  </si>
+  <si>
+    <t>058132</t>
+  </si>
+  <si>
+    <t>955383</t>
+  </si>
+  <si>
+    <t>018727</t>
+  </si>
+  <si>
+    <t>130752</t>
+  </si>
+  <si>
+    <t>033973</t>
+  </si>
+  <si>
+    <t>197006</t>
+  </si>
+  <si>
+    <t>066517</t>
+  </si>
+  <si>
+    <t>199508</t>
+  </si>
+  <si>
+    <t>023337</t>
+  </si>
+  <si>
+    <t>272359</t>
+  </si>
+  <si>
+    <t>051856</t>
+  </si>
+  <si>
+    <t>280806</t>
+  </si>
+  <si>
+    <t>066399</t>
+  </si>
+  <si>
+    <t>280816</t>
+  </si>
+  <si>
+    <t>381777</t>
+  </si>
+  <si>
+    <t>060925</t>
+  </si>
+  <si>
+    <t>381778</t>
+  </si>
+  <si>
+    <t>441424</t>
+  </si>
+  <si>
+    <t>059142</t>
+  </si>
+  <si>
+    <t>472876</t>
+  </si>
+  <si>
+    <t>019415</t>
+  </si>
+  <si>
+    <t>PT. BANK MESTIKA DHARMA</t>
+  </si>
+  <si>
+    <t>494701</t>
+  </si>
+  <si>
+    <t>052593</t>
+  </si>
+  <si>
+    <t>509222</t>
+  </si>
+  <si>
+    <t>019307</t>
+  </si>
+  <si>
+    <t>509223</t>
+  </si>
+  <si>
+    <t>509224</t>
+  </si>
+  <si>
+    <t>509225</t>
+  </si>
+  <si>
+    <t>509301</t>
+  </si>
+  <si>
+    <t>509302</t>
+  </si>
+  <si>
+    <t>509303</t>
+  </si>
+  <si>
+    <t>509304</t>
+  </si>
+  <si>
+    <t>527268</t>
+  </si>
+  <si>
+    <t>019383</t>
+  </si>
+  <si>
+    <t>544679</t>
+  </si>
+  <si>
+    <t>039851</t>
+  </si>
+  <si>
+    <t>803288</t>
+  </si>
+  <si>
+    <t>019416</t>
+  </si>
+  <si>
+    <t>BANK SMBC INDONESIA</t>
+  </si>
+  <si>
+    <t>934596</t>
+  </si>
+  <si>
+    <t>015333</t>
+  </si>
+  <si>
+    <t>000143</t>
+  </si>
+  <si>
+    <t>PT. BANK NAGARI</t>
+  </si>
+  <si>
+    <t>016050</t>
+  </si>
+  <si>
+    <t>007777</t>
+  </si>
+  <si>
+    <t>017991</t>
+  </si>
+  <si>
+    <t>209061</t>
+  </si>
+  <si>
+    <t>056474</t>
+  </si>
+  <si>
+    <t>209062</t>
+  </si>
+  <si>
+    <t>067329</t>
+  </si>
+  <si>
+    <t>209063</t>
+  </si>
+  <si>
+    <t>534654</t>
+  </si>
+  <si>
+    <t>534655</t>
+  </si>
+  <si>
+    <t>534690</t>
+  </si>
+  <si>
+    <t>534691</t>
+  </si>
+  <si>
+    <t>534692</t>
+  </si>
+  <si>
+    <t>534693</t>
+  </si>
+  <si>
+    <t>534694</t>
+  </si>
+  <si>
+    <t>005204</t>
+  </si>
+  <si>
+    <t>008302</t>
+  </si>
+  <si>
+    <t>BANK MAYAPADA INTERNATIONAL, PT. Tbk.</t>
+  </si>
+  <si>
+    <t>005210</t>
+  </si>
+  <si>
+    <t>005214</t>
+  </si>
+  <si>
+    <t>031181</t>
+  </si>
+  <si>
+    <t>063371</t>
+  </si>
+  <si>
+    <t>484548</t>
+  </si>
+  <si>
+    <t>039234</t>
+  </si>
+  <si>
+    <t>484555</t>
+  </si>
+  <si>
+    <t>484569</t>
+  </si>
+  <si>
+    <t>G 031157</t>
+  </si>
+  <si>
+    <t>262369</t>
+  </si>
+  <si>
+    <t>040446</t>
+  </si>
+  <si>
+    <t>932682</t>
+  </si>
+  <si>
+    <t>063928</t>
+  </si>
+  <si>
+    <t>932731</t>
+  </si>
+  <si>
+    <t>059272</t>
+  </si>
+  <si>
+    <t>GHC717656</t>
+  </si>
+  <si>
+    <t>000322</t>
+  </si>
+  <si>
+    <t>GHC717952</t>
+  </si>
+  <si>
+    <t>051938</t>
+  </si>
+  <si>
+    <t>DX 387255</t>
+  </si>
+  <si>
+    <t>070054</t>
+  </si>
+  <si>
+    <t>058141</t>
+  </si>
+  <si>
+    <t>027321</t>
+  </si>
+  <si>
+    <t>072947</t>
+  </si>
+  <si>
+    <t>040518</t>
+  </si>
+  <si>
+    <t>077985</t>
+  </si>
+  <si>
+    <t>077986</t>
+  </si>
+  <si>
+    <t>077987</t>
+  </si>
+  <si>
+    <t>346584</t>
+  </si>
+  <si>
+    <t>010146</t>
+  </si>
+  <si>
+    <t>346585</t>
+  </si>
+  <si>
+    <t>346600</t>
+  </si>
+  <si>
+    <t>348397</t>
+  </si>
+  <si>
+    <t>618114</t>
+  </si>
+  <si>
+    <t>010091</t>
+  </si>
+  <si>
+    <t>618167</t>
+  </si>
+  <si>
+    <t>618195</t>
+  </si>
+  <si>
+    <t>765513</t>
+  </si>
+  <si>
+    <t>010204</t>
+  </si>
+  <si>
+    <t>BANK ARTHA GRAHA</t>
+  </si>
+  <si>
+    <t>765537</t>
+  </si>
+  <si>
+    <t>765547</t>
+  </si>
+  <si>
+    <t>813082</t>
+  </si>
+  <si>
+    <t>057521</t>
+  </si>
+  <si>
+    <t>863674</t>
+  </si>
+  <si>
+    <t>BG 350687</t>
+  </si>
+  <si>
+    <t>017405</t>
+  </si>
+  <si>
+    <t>BH 394318</t>
+  </si>
+  <si>
+    <t>017475</t>
+  </si>
+  <si>
+    <t>BH 394347</t>
+  </si>
+  <si>
+    <t>BH 394399</t>
+  </si>
+  <si>
+    <t>077819</t>
+  </si>
+  <si>
+    <t>032773</t>
+  </si>
+  <si>
+    <t>097889</t>
+  </si>
+  <si>
+    <t>065966</t>
+  </si>
+  <si>
+    <t>236191</t>
+  </si>
+  <si>
+    <t>058113</t>
+  </si>
+  <si>
+    <t>562932</t>
+  </si>
+  <si>
+    <t>010867</t>
+  </si>
+  <si>
+    <t>8042577</t>
+  </si>
+  <si>
+    <t>010767</t>
+  </si>
+  <si>
+    <t>111836</t>
+  </si>
+  <si>
+    <t>011976</t>
+  </si>
+  <si>
+    <t>111837</t>
+  </si>
+  <si>
+    <t>112012</t>
+  </si>
+  <si>
+    <t>112307</t>
+  </si>
+  <si>
+    <t>112308</t>
+  </si>
+  <si>
+    <t>112309</t>
+  </si>
+  <si>
+    <t>112599</t>
+  </si>
+  <si>
+    <t>112660</t>
+  </si>
+  <si>
+    <t>112661</t>
+  </si>
+  <si>
+    <t>152543</t>
+  </si>
+  <si>
+    <t>037861</t>
+  </si>
+  <si>
+    <t>154839</t>
+  </si>
+  <si>
+    <t>038055</t>
+  </si>
+  <si>
+    <t>154840</t>
+  </si>
+  <si>
+    <t>170763</t>
+  </si>
+  <si>
+    <t>011695</t>
+  </si>
+  <si>
+    <t>217780</t>
+  </si>
+  <si>
+    <t>066499</t>
+  </si>
+  <si>
+    <t>219303</t>
+  </si>
+  <si>
+    <t>036724</t>
+  </si>
+  <si>
+    <t>238680</t>
+  </si>
+  <si>
+    <t>032136</t>
   </si>
   <si>
     <t>BANK INDEX SELINDO, PT.</t>
   </si>
   <si>
-    <t>328480</t>
-  </si>
-  <si>
-    <t>053463</t>
-  </si>
-  <si>
-    <t>328481</t>
-  </si>
-  <si>
-    <t>578612</t>
-  </si>
-  <si>
-    <t>040722</t>
-  </si>
-  <si>
-    <t>578613</t>
-  </si>
-  <si>
-    <t>626359</t>
-  </si>
-  <si>
-    <t>061077</t>
-  </si>
-  <si>
-    <t>BANK CENTRAL ASIA</t>
-  </si>
-  <si>
-    <t>725513</t>
-  </si>
-  <si>
-    <t>069474</t>
-  </si>
-  <si>
-    <t>BANK HANA</t>
-  </si>
-  <si>
-    <t>738878</t>
-  </si>
-  <si>
-    <t>BANK OCBC - INDONESIA, PT.</t>
-  </si>
-  <si>
-    <t>738879</t>
-  </si>
-  <si>
-    <t>738885</t>
-  </si>
-  <si>
-    <t>738887</t>
-  </si>
-  <si>
-    <t>738889</t>
-  </si>
-  <si>
-    <t>931669</t>
-  </si>
-  <si>
-    <t>065261</t>
-  </si>
-  <si>
-    <t>BANK SYARIAH INDONESIA</t>
-  </si>
-  <si>
-    <t>177397</t>
-  </si>
-  <si>
-    <t>013061</t>
-  </si>
-  <si>
-    <t>474289</t>
-  </si>
-  <si>
-    <t>003251</t>
-  </si>
-  <si>
-    <t>050006</t>
-  </si>
-  <si>
-    <t>042440</t>
-  </si>
-  <si>
-    <t>095316</t>
-  </si>
-  <si>
-    <t>042438</t>
-  </si>
-  <si>
-    <t>343605</t>
-  </si>
-  <si>
-    <t>030787</t>
-  </si>
-  <si>
-    <t>BANK MEGA</t>
-  </si>
-  <si>
-    <t>343612</t>
-  </si>
-  <si>
-    <t>392948</t>
-  </si>
-  <si>
-    <t>005647</t>
-  </si>
-  <si>
-    <t>BANK PERMATA, PT. Tbk.</t>
-  </si>
-  <si>
-    <t>518146</t>
-  </si>
-  <si>
-    <t>052835</t>
-  </si>
-  <si>
-    <t>518149</t>
-  </si>
-  <si>
-    <t>665434</t>
-  </si>
-  <si>
-    <t>000288</t>
-  </si>
-  <si>
-    <t>673303</t>
-  </si>
-  <si>
-    <t>673308</t>
-  </si>
-  <si>
-    <t>AGC 244752</t>
-  </si>
-  <si>
-    <t>006357</t>
-  </si>
-  <si>
-    <t>BANK MAS, PT.</t>
-  </si>
-  <si>
-    <t>AN673290</t>
-  </si>
-  <si>
-    <t>BAG426131</t>
-  </si>
-  <si>
-    <t>051913</t>
-  </si>
-  <si>
-    <t>BANK CIMB NIAGA, PT.</t>
-  </si>
-  <si>
-    <t>BAG426229</t>
-  </si>
-  <si>
-    <t>BAG426311</t>
-  </si>
-  <si>
-    <t>EP 285497</t>
-  </si>
-  <si>
-    <t>006481</t>
-  </si>
-  <si>
-    <t>FB955185</t>
-  </si>
-  <si>
-    <t>046770</t>
-  </si>
-  <si>
-    <t>FB955199</t>
-  </si>
-  <si>
-    <t>GA 423712</t>
-  </si>
-  <si>
-    <t>006569</t>
-  </si>
-  <si>
-    <t>BANK CAPITAL INDONESIA, PT., Tbk.</t>
-  </si>
-  <si>
-    <t>013099</t>
-  </si>
-  <si>
-    <t>016726</t>
-  </si>
-  <si>
-    <t>0131231</t>
-  </si>
-  <si>
-    <t>021608</t>
-  </si>
-  <si>
-    <t>BANK MAYAPADA INTERNATIONAL, PT. Tbk.</t>
-  </si>
-  <si>
-    <t>013232</t>
-  </si>
-  <si>
-    <t>110953</t>
-  </si>
-  <si>
-    <t>072581</t>
-  </si>
-  <si>
-    <t>353862</t>
-  </si>
-  <si>
-    <t>000879</t>
-  </si>
-  <si>
-    <t>555465</t>
-  </si>
-  <si>
-    <t>064476</t>
-  </si>
-  <si>
-    <t>991270</t>
-  </si>
-  <si>
-    <t>072287</t>
-  </si>
-  <si>
-    <t>EC 993645</t>
-  </si>
-  <si>
-    <t>041928</t>
-  </si>
-  <si>
-    <t>EC 994011</t>
-  </si>
-  <si>
-    <t>055032</t>
-  </si>
-  <si>
-    <t>072047</t>
-  </si>
-  <si>
-    <t>063569</t>
-  </si>
-  <si>
-    <t>072055</t>
-  </si>
-  <si>
-    <t>727990</t>
-  </si>
-  <si>
-    <t>061391</t>
-  </si>
-  <si>
-    <t>028060</t>
-  </si>
-  <si>
-    <t>039651</t>
-  </si>
-  <si>
-    <t>028067</t>
-  </si>
-  <si>
-    <t>274740</t>
-  </si>
-  <si>
-    <t>031594</t>
-  </si>
-  <si>
-    <t>BANK VICTORIA INTERNATIONAL, PT., Tbk.</t>
-  </si>
-  <si>
-    <t>274742</t>
-  </si>
-  <si>
-    <t>274743</t>
-  </si>
-  <si>
-    <t>274744</t>
-  </si>
-  <si>
-    <t>274745</t>
-  </si>
-  <si>
-    <t>638026</t>
-  </si>
-  <si>
-    <t>053347</t>
-  </si>
-  <si>
-    <t>865632</t>
-  </si>
-  <si>
-    <t>032225</t>
-  </si>
-  <si>
-    <t>175346</t>
-  </si>
-  <si>
-    <t>004067</t>
-  </si>
-  <si>
-    <t>BANK WOORI INDONESIA, PT.</t>
-  </si>
-  <si>
-    <t>175381</t>
-  </si>
-  <si>
-    <t>176362</t>
-  </si>
-  <si>
-    <t>610913</t>
-  </si>
-  <si>
-    <t>063763</t>
-  </si>
-  <si>
-    <t>610920</t>
-  </si>
-  <si>
-    <t>70513</t>
-  </si>
-  <si>
-    <t>058132</t>
-  </si>
-  <si>
-    <t>955340</t>
-  </si>
-  <si>
-    <t>018727</t>
-  </si>
-  <si>
-    <t>955382</t>
-  </si>
-  <si>
-    <t>955383</t>
-  </si>
-  <si>
-    <t>003441</t>
-  </si>
-  <si>
-    <t>070541</t>
-  </si>
-  <si>
-    <t>003678</t>
-  </si>
-  <si>
-    <t>214299</t>
-  </si>
-  <si>
-    <t>051856</t>
-  </si>
-  <si>
-    <t>272359</t>
-  </si>
-  <si>
-    <t>280778</t>
-  </si>
-  <si>
-    <t>066399</t>
-  </si>
-  <si>
-    <t>280806</t>
-  </si>
-  <si>
-    <t>280816</t>
-  </si>
-  <si>
-    <t>363985</t>
-  </si>
-  <si>
-    <t>019316</t>
-  </si>
-  <si>
-    <t>453087</t>
-  </si>
-  <si>
-    <t>019267</t>
-  </si>
-  <si>
-    <t>476753</t>
-  </si>
-  <si>
-    <t>038729</t>
-  </si>
-  <si>
-    <t>PT. BANK MESTIKA DHARMA</t>
-  </si>
-  <si>
-    <t>481306</t>
-  </si>
-  <si>
-    <t>062514</t>
-  </si>
-  <si>
-    <t>496757</t>
-  </si>
-  <si>
-    <t>496758</t>
-  </si>
-  <si>
-    <t>496759</t>
-  </si>
-  <si>
-    <t>509201</t>
-  </si>
-  <si>
-    <t>019307</t>
-  </si>
-  <si>
-    <t>509202</t>
-  </si>
-  <si>
-    <t>509203</t>
-  </si>
-  <si>
-    <t>509204</t>
-  </si>
-  <si>
-    <t>509205</t>
-  </si>
-  <si>
-    <t>544679</t>
-  </si>
-  <si>
-    <t>039851</t>
-  </si>
-  <si>
-    <t>803272</t>
-  </si>
-  <si>
-    <t>019416</t>
-  </si>
-  <si>
-    <t>BANK SMBC INDONESIA</t>
-  </si>
-  <si>
-    <t>867011</t>
-  </si>
-  <si>
-    <t>050818</t>
-  </si>
-  <si>
-    <t>867012</t>
-  </si>
-  <si>
-    <t>934596</t>
-  </si>
-  <si>
-    <t>060925</t>
-  </si>
-  <si>
-    <t>934599</t>
-  </si>
-  <si>
-    <t>934600</t>
-  </si>
-  <si>
-    <t>001359</t>
-  </si>
-  <si>
-    <t>077041</t>
-  </si>
-  <si>
-    <t>PT. BANK NAGARI</t>
-  </si>
-  <si>
-    <t>534358</t>
-  </si>
-  <si>
-    <t>067329</t>
-  </si>
-  <si>
-    <t>534359</t>
-  </si>
-  <si>
-    <t>534651</t>
-  </si>
-  <si>
-    <t>534652</t>
-  </si>
-  <si>
-    <t>534653</t>
-  </si>
-  <si>
-    <t>534654</t>
-  </si>
-  <si>
-    <t>534655</t>
-  </si>
-  <si>
-    <t>005204</t>
-  </si>
-  <si>
-    <t>008302</t>
-  </si>
-  <si>
-    <t>031235</t>
-  </si>
-  <si>
-    <t>063371</t>
-  </si>
-  <si>
-    <t>031270</t>
-  </si>
-  <si>
-    <t>031333</t>
-  </si>
-  <si>
-    <t>247697</t>
-  </si>
-  <si>
-    <t>039234</t>
-  </si>
-  <si>
-    <t>247698</t>
-  </si>
-  <si>
-    <t>000111</t>
-  </si>
-  <si>
-    <t>031102</t>
-  </si>
-  <si>
-    <t>BANK UOB INDONESIA, PT.</t>
-  </si>
-  <si>
-    <t>262355</t>
-  </si>
-  <si>
-    <t>040446</t>
-  </si>
-  <si>
-    <t>561845</t>
-  </si>
-  <si>
-    <t>061460</t>
-  </si>
-  <si>
-    <t>861392</t>
-  </si>
-  <si>
-    <t>003189</t>
-  </si>
-  <si>
-    <t>939864</t>
-  </si>
-  <si>
-    <t>012677</t>
-  </si>
-  <si>
-    <t>939865</t>
-  </si>
-  <si>
-    <t>10583667</t>
-  </si>
-  <si>
-    <t>020110</t>
-  </si>
-  <si>
-    <t>BANK CENTRADANA KAPUAS</t>
-  </si>
-  <si>
-    <t>GHC 716537</t>
-  </si>
-  <si>
-    <t>051938</t>
-  </si>
-  <si>
-    <t>045050</t>
-  </si>
-  <si>
-    <t>040518</t>
-  </si>
-  <si>
-    <t>047823</t>
-  </si>
-  <si>
-    <t>047824</t>
-  </si>
-  <si>
-    <t>054049</t>
-  </si>
-  <si>
-    <t>071313</t>
-  </si>
-  <si>
-    <t>119515</t>
-  </si>
-  <si>
-    <t>064639</t>
-  </si>
-  <si>
-    <t>348397</t>
-  </si>
-  <si>
-    <t>010146</t>
-  </si>
-  <si>
-    <t>444499</t>
-  </si>
-  <si>
-    <t>010091</t>
-  </si>
-  <si>
-    <t>618110</t>
-  </si>
-  <si>
-    <t>618114</t>
-  </si>
-  <si>
-    <t>765537</t>
-  </si>
-  <si>
-    <t>010204</t>
-  </si>
-  <si>
-    <t>BANK ARTHA GRAHA</t>
-  </si>
-  <si>
-    <t>765547</t>
-  </si>
-  <si>
-    <t>863654</t>
-  </si>
-  <si>
-    <t>863673</t>
-  </si>
-  <si>
-    <t>863674</t>
-  </si>
-  <si>
-    <t>BH 394318</t>
-  </si>
-  <si>
-    <t>017475</t>
-  </si>
-  <si>
-    <t>038367</t>
-  </si>
-  <si>
-    <t>065966</t>
-  </si>
-  <si>
-    <t>077799</t>
-  </si>
-  <si>
-    <t>032773</t>
-  </si>
-  <si>
-    <t>097531</t>
-  </si>
-  <si>
-    <t>236178</t>
-  </si>
-  <si>
-    <t>058113</t>
-  </si>
-  <si>
-    <t>290455</t>
-  </si>
-  <si>
-    <t>017884</t>
-  </si>
-  <si>
-    <t>315326</t>
-  </si>
-  <si>
-    <t>001644</t>
-  </si>
-  <si>
-    <t>CIMB NIAGA</t>
-  </si>
-  <si>
-    <t>315536</t>
-  </si>
-  <si>
-    <t>017793</t>
-  </si>
-  <si>
-    <t>379325</t>
-  </si>
-  <si>
-    <t>066018</t>
-  </si>
-  <si>
-    <t>379340</t>
-  </si>
-  <si>
-    <t>560782</t>
-  </si>
-  <si>
-    <t>010867</t>
-  </si>
-  <si>
-    <t>06272</t>
-  </si>
-  <si>
-    <t>069718</t>
-  </si>
-  <si>
-    <t>111347</t>
-  </si>
-  <si>
-    <t>011976</t>
-  </si>
-  <si>
-    <t>111348</t>
-  </si>
-  <si>
-    <t>111616</t>
-  </si>
-  <si>
-    <t>111617</t>
-  </si>
-  <si>
-    <t>111836</t>
-  </si>
-  <si>
-    <t>111837</t>
-  </si>
-  <si>
-    <t>111838</t>
-  </si>
-  <si>
-    <t>152532</t>
-  </si>
-  <si>
-    <t>037861</t>
-  </si>
-  <si>
-    <t>154837</t>
-  </si>
-  <si>
-    <t>038055</t>
-  </si>
-  <si>
-    <t>154838</t>
-  </si>
-  <si>
-    <t>154839</t>
-  </si>
-  <si>
-    <t>154840</t>
-  </si>
-  <si>
-    <t>159858</t>
-  </si>
-  <si>
-    <t>041826</t>
-  </si>
-  <si>
-    <t>170708</t>
-  </si>
-  <si>
-    <t>011695</t>
-  </si>
-  <si>
-    <t>170989</t>
-  </si>
-  <si>
-    <t>066499</t>
-  </si>
-  <si>
-    <t>238726</t>
-  </si>
-  <si>
-    <t>032136</t>
-  </si>
-  <si>
-    <t>258965</t>
+    <t>238682</t>
+  </si>
+  <si>
+    <t>265950</t>
+  </si>
+  <si>
+    <t>076773</t>
+  </si>
+  <si>
+    <t>266090</t>
   </si>
   <si>
     <t>076766</t>
   </si>
   <si>
-    <t>26406</t>
-  </si>
-  <si>
-    <t>265950</t>
-  </si>
-  <si>
-    <t>076773</t>
-  </si>
-  <si>
-    <t>266090</t>
-  </si>
-  <si>
-    <t>283163</t>
+    <t>266382</t>
+  </si>
+  <si>
+    <t>272880</t>
+  </si>
+  <si>
+    <t>274741</t>
+  </si>
+  <si>
+    <t>056852</t>
+  </si>
+  <si>
+    <t>283357</t>
   </si>
   <si>
     <t>074324</t>
   </si>
   <si>
-    <t>283357</t>
+    <t>293026</t>
   </si>
   <si>
     <t>58592</t>
@@ -1002,61 +952,67 @@
     <t>053677</t>
   </si>
   <si>
-    <t>63696</t>
-  </si>
-  <si>
-    <t>038284</t>
-  </si>
-  <si>
-    <t>998024</t>
+    <t>687783</t>
+  </si>
+  <si>
+    <t>066137</t>
+  </si>
+  <si>
+    <t>76128</t>
+  </si>
+  <si>
+    <t>027462</t>
+  </si>
+  <si>
+    <t>76129</t>
+  </si>
+  <si>
+    <t>978931</t>
+  </si>
+  <si>
+    <t>050679</t>
+  </si>
+  <si>
+    <t>998073</t>
   </si>
   <si>
     <t>065920</t>
   </si>
   <si>
-    <t>998025</t>
-  </si>
-  <si>
-    <t>AAP 528963</t>
+    <t>998074</t>
+  </si>
+  <si>
+    <t>AAP 528997</t>
   </si>
   <si>
     <t>024994</t>
   </si>
   <si>
-    <t>GHC 231986</t>
-  </si>
-  <si>
-    <t>044734</t>
-  </si>
-  <si>
-    <t>BBA 871589</t>
-  </si>
-  <si>
-    <t>011149</t>
-  </si>
-  <si>
-    <t>BANK BUMI ARTA PT.</t>
-  </si>
-  <si>
-    <t>EC 277334</t>
+    <t>EC 277485</t>
   </si>
   <si>
     <t>001851</t>
   </si>
   <si>
-    <t>GC 393667</t>
-  </si>
-  <si>
-    <t>001854</t>
-  </si>
-  <si>
-    <t>BANK MNC INTERNATIONAL TBK. PT</t>
+    <t>GB 066262</t>
+  </si>
+  <si>
+    <t>027558</t>
+  </si>
+  <si>
+    <t>BANK NATIONAL NOBU PT.</t>
+  </si>
+  <si>
+    <t>GB 892197</t>
+  </si>
+  <si>
+    <t>063878</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -1336,11 +1292,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F201"/>
+  <dimension ref="A1:F191"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="16.7109375" customWidth="1"/>
@@ -1396,13 +1352,13 @@
         <v>12</v>
       </c>
       <c r="C4" s="5">
-        <v>777000</v>
+        <v>6640000</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="6">
-        <v>45976</v>
+        <v>45994</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>14</v>
@@ -1413,16 +1369,16 @@
         <v>15</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C5" s="5">
-        <v>1667000</v>
+        <v>2671000</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="6">
-        <v>45983</v>
+        <v>45997</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>14</v>
@@ -1430,19 +1386,19 @@
     </row>
     <row r="6" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="5">
-        <v>1740000</v>
+        <v>30867100</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E6" s="6">
-        <v>45979</v>
+        <v>45999</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>14</v>
@@ -1450,19 +1406,19 @@
     </row>
     <row r="7" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="5">
-        <v>21840000</v>
+        <v>2334000</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" s="6">
-        <v>44296</v>
+        <v>45990</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>14</v>
@@ -1470,19 +1426,19 @@
     </row>
     <row r="8" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1828000</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="5">
-        <v>40710000</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="E8" s="6">
-        <v>44310</v>
+        <v>46007</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>14</v>
@@ -1490,19 +1446,19 @@
     </row>
     <row r="9" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9" s="5">
-        <v>5784200</v>
+        <v>21840000</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E9" s="6">
-        <v>45986</v>
+        <v>44296</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>14</v>
@@ -1510,19 +1466,19 @@
     </row>
     <row r="10" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="5">
+        <v>40710000</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="5">
-        <v>5437000</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>24</v>
-      </c>
       <c r="E10" s="6">
-        <v>45975</v>
+        <v>44310</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>14</v>
@@ -1530,19 +1486,19 @@
     </row>
     <row r="11" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C11" s="5">
-        <v>4068500</v>
+        <v>4292300</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E11" s="6">
-        <v>45992</v>
+        <v>46000</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>14</v>
@@ -1550,19 +1506,19 @@
     </row>
     <row r="12" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C12" s="5">
-        <v>4292300</v>
+        <v>1217500</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E12" s="6">
-        <v>46000</v>
+        <v>45994</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>14</v>
@@ -1570,19 +1526,19 @@
     </row>
     <row r="13" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C13" s="5">
-        <v>1217500</v>
+        <v>7766500</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E13" s="6">
-        <v>45994</v>
+        <v>46000</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>14</v>
@@ -1590,19 +1546,19 @@
     </row>
     <row r="14" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="5">
+        <v>3674800</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="5">
-        <v>664300</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="E14" s="6">
-        <v>45978</v>
+        <v>46006</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>14</v>
@@ -1610,19 +1566,19 @@
     </row>
     <row r="15" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C15" s="5">
-        <v>12936000</v>
+        <v>6840000</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E15" s="6">
-        <v>45989</v>
+        <v>45996</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>14</v>
@@ -1630,19 +1586,19 @@
     </row>
     <row r="16" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C16" s="5">
-        <v>12500000</v>
+        <v>42232000</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="E16" s="6">
-        <v>46006</v>
+        <v>46002</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>14</v>
@@ -1650,19 +1606,19 @@
     </row>
     <row r="17" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C17" s="5">
         <v>12500000</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E17" s="6">
-        <v>46010</v>
+        <v>46006</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>14</v>
@@ -1670,19 +1626,19 @@
     </row>
     <row r="18" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C18" s="5">
-        <v>12072000</v>
+        <v>12500000</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E18" s="6">
-        <v>46001</v>
+        <v>46010</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>14</v>
@@ -1690,19 +1646,19 @@
     </row>
     <row r="19" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C19" s="5">
-        <v>14794000</v>
+        <v>12072000</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E19" s="6">
-        <v>45975</v>
+        <v>46001</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>14</v>
@@ -1710,19 +1666,19 @@
     </row>
     <row r="20" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C20" s="5">
-        <v>11400000</v>
+        <v>23677000</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E20" s="6">
-        <v>45979</v>
+        <v>46020</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>14</v>
@@ -1730,19 +1686,19 @@
     </row>
     <row r="21" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C21" s="5">
-        <v>11406000</v>
+        <v>2097900</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E21" s="6">
-        <v>45983</v>
+        <v>45987</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>14</v>
@@ -1750,19 +1706,19 @@
     </row>
     <row r="22" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="C22" s="5">
-        <v>13600000</v>
+        <v>285519683</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E22" s="6">
-        <v>45992</v>
+        <v>45384</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>14</v>
@@ -1770,19 +1726,19 @@
     </row>
     <row r="23" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="C23" s="5">
-        <v>13600000</v>
+        <v>255499245</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E23" s="6">
-        <v>45996</v>
+        <v>45407</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>14</v>
@@ -1790,19 +1746,19 @@
     </row>
     <row r="24" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="C24" s="5">
-        <v>14188000</v>
+        <v>23751000</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="E24" s="6">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>14</v>
@@ -1810,19 +1766,19 @@
     </row>
     <row r="25" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C25" s="5">
-        <v>42108750</v>
+        <v>34537000</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E25" s="6">
-        <v>45975</v>
+        <v>45996</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>14</v>
@@ -1830,19 +1786,19 @@
     </row>
     <row r="26" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C26" s="5">
-        <v>285519683</v>
+        <v>7439000</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E26" s="6">
-        <v>45384</v>
+        <v>46002</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>14</v>
@@ -1850,19 +1806,19 @@
     </row>
     <row r="27" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C27" s="5">
-        <v>255499245</v>
+        <v>142239415</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="E27" s="6">
-        <v>45407</v>
+        <v>46007</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>14</v>
@@ -1870,19 +1826,19 @@
     </row>
     <row r="28" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C28" s="5">
-        <v>4504970</v>
+        <v>122652975</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="E28" s="6">
-        <v>45974</v>
+        <v>46009</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>14</v>
@@ -1890,19 +1846,19 @@
     </row>
     <row r="29" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C29" s="5">
-        <v>5809000</v>
+        <v>98921048</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="E29" s="6">
-        <v>45979</v>
+        <v>46000</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>14</v>
@@ -1910,19 +1866,19 @@
     </row>
     <row r="30" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C30" s="5">
-        <v>12488000</v>
+        <v>74057900</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E30" s="6">
-        <v>45982</v>
+        <v>46001</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>14</v>
@@ -1930,19 +1886,19 @@
     </row>
     <row r="31" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C31" s="5">
-        <v>12457000</v>
+        <v>31238700</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E31" s="6">
-        <v>45988</v>
+        <v>45996</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>14</v>
@@ -1950,19 +1906,19 @@
     </row>
     <row r="32" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C32" s="5">
-        <v>11278700</v>
+        <v>150000000</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E32" s="6">
-        <v>45976</v>
+        <v>45222</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>14</v>
@@ -1970,19 +1926,19 @@
     </row>
     <row r="33" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C33" s="5">
-        <v>54761000</v>
+        <v>36786900</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="E33" s="6">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>14</v>
@@ -1990,19 +1946,19 @@
     </row>
     <row r="34" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C34" s="5">
-        <v>22285000</v>
+        <v>15432600</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="E34" s="6">
-        <v>45980</v>
+        <v>45989</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>14</v>
@@ -2010,19 +1966,19 @@
     </row>
     <row r="35" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C35" s="5">
-        <v>2521000</v>
+        <v>5151500</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="E35" s="6">
-        <v>45976</v>
+        <v>46014</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>14</v>
@@ -2030,19 +1986,19 @@
     </row>
     <row r="36" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C36" s="5">
-        <v>1832600</v>
+        <v>5290000</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="E36" s="6">
-        <v>45990</v>
+        <v>45993</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>14</v>
@@ -2050,19 +2006,19 @@
     </row>
     <row r="37" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C37" s="5">
-        <v>145757371</v>
+        <v>12030000</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="E37" s="6">
-        <v>45986</v>
+        <v>45993</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>14</v>
@@ -2070,19 +2026,19 @@
     </row>
     <row r="38" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C38" s="5">
-        <v>133379900</v>
+        <v>1598400</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="E38" s="6">
-        <v>45978</v>
+        <v>46015</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>14</v>
@@ -2090,19 +2046,19 @@
     </row>
     <row r="39" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C39" s="5">
-        <v>7929100</v>
+        <v>14378700</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="E39" s="6">
-        <v>45989</v>
+        <v>46001</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>14</v>
@@ -2110,19 +2066,19 @@
     </row>
     <row r="40" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C40" s="5">
-        <v>31015700</v>
+        <v>1100000</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E40" s="6">
-        <v>45986</v>
+        <v>45995</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>14</v>
@@ -2130,19 +2086,19 @@
     </row>
     <row r="41" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C41" s="5">
-        <v>31238700</v>
+        <v>1600000</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E41" s="6">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>14</v>
@@ -2150,19 +2106,19 @@
     </row>
     <row r="42" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C42" s="5">
-        <v>2908300</v>
+        <v>1300000</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E42" s="6">
-        <v>45992</v>
+        <v>46017</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>14</v>
@@ -2170,19 +2126,19 @@
     </row>
     <row r="43" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C43" s="5">
-        <v>8433300</v>
+        <v>17062464</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="E43" s="6">
-        <v>45981</v>
+        <v>45997</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>14</v>
@@ -2190,19 +2146,19 @@
     </row>
     <row r="44" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>80</v>
       </c>
       <c r="C44" s="5">
-        <v>150000000</v>
+        <v>1110000</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="E44" s="6">
-        <v>45222</v>
+        <v>46001</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>14</v>
@@ -2210,19 +2166,19 @@
     </row>
     <row r="45" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C45" s="5">
-        <v>2524000</v>
+        <v>836940</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="E45" s="6">
-        <v>45982</v>
+        <v>46003</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>14</v>
@@ -2230,19 +2186,19 @@
     </row>
     <row r="46" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C46" s="5">
-        <v>10865500</v>
+        <v>1831500</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E46" s="6">
-        <v>45976</v>
+        <v>46013</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>14</v>
@@ -2250,19 +2206,19 @@
     </row>
     <row r="47" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C47" s="5">
-        <v>13410300</v>
+        <v>18926000</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="E47" s="6">
-        <v>45982</v>
+        <v>45826</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>14</v>
@@ -2270,19 +2226,19 @@
     </row>
     <row r="48" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C48" s="5">
-        <v>59392100</v>
+        <v>1148850</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="E48" s="6">
-        <v>45982</v>
+        <v>45991</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>14</v>
@@ -2290,19 +2246,19 @@
     </row>
     <row r="49" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C49" s="5">
-        <v>2800000</v>
+        <v>5121500</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E49" s="6">
-        <v>45978</v>
+        <v>45992</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>14</v>
@@ -2310,16 +2266,16 @@
     </row>
     <row r="50" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C50" s="5">
-        <v>1100000</v>
+        <v>1298700</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E50" s="6">
         <v>45995</v>
@@ -2330,19 +2286,19 @@
     </row>
     <row r="51" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C51" s="5">
-        <v>16135400</v>
+        <v>582750</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E51" s="6">
-        <v>45974</v>
+        <v>45994</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>14</v>
@@ -2350,19 +2306,19 @@
     </row>
     <row r="52" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C52" s="5">
-        <v>1263180</v>
+        <v>1781550</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="E52" s="6">
-        <v>45982</v>
+        <v>45993</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>14</v>
@@ -2370,19 +2326,19 @@
     </row>
     <row r="53" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C53" s="5">
+        <v>1798200</v>
+      </c>
+      <c r="D53" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B53" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C53" s="5">
-        <v>3038958</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>35</v>
-      </c>
       <c r="E53" s="6">
-        <v>45983</v>
+        <v>45997</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>14</v>
@@ -2390,19 +2346,19 @@
     </row>
     <row r="54" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C54" s="5">
-        <v>3187143</v>
+        <v>22176434</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="E54" s="6">
-        <v>45973</v>
+        <v>46000</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>14</v>
@@ -2410,19 +2366,19 @@
     </row>
     <row r="55" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C55" s="5">
-        <v>17062464</v>
+        <v>1831500</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="E55" s="6">
-        <v>45997</v>
+        <v>45994</v>
       </c>
       <c r="F55" s="5" t="s">
         <v>14</v>
@@ -2430,19 +2386,19 @@
     </row>
     <row r="56" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C56" s="5">
-        <v>1110000</v>
+        <v>999000</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="E56" s="6">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>14</v>
@@ -2450,19 +2406,19 @@
     </row>
     <row r="57" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C57" s="5">
-        <v>18926000</v>
+        <v>138945800</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="E57" s="6">
-        <v>45826</v>
+        <v>45996</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>14</v>
@@ -2470,19 +2426,19 @@
     </row>
     <row r="58" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="C58" s="5">
-        <v>1148250</v>
+        <v>8370607</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="E58" s="6">
-        <v>45991</v>
+        <v>45996</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>14</v>
@@ -2490,19 +2446,19 @@
     </row>
     <row r="59" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C59" s="5">
-        <v>2384615</v>
+        <v>17629073</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="E59" s="6">
-        <v>45977</v>
+        <v>46006</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>14</v>
@@ -2510,19 +2466,19 @@
     </row>
     <row r="60" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C60" s="5">
-        <v>2286600</v>
+        <v>42084540</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="E60" s="6">
-        <v>45980</v>
+        <v>46002</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>14</v>
@@ -2530,19 +2486,19 @@
     </row>
     <row r="61" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="C61" s="5">
-        <v>1254300</v>
+        <v>3866932</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="E61" s="6">
-        <v>45977</v>
+        <v>45993</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>14</v>
@@ -2550,19 +2506,19 @@
     </row>
     <row r="62" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C62" s="5">
-        <v>6312800</v>
+        <v>5180569</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="E62" s="6">
-        <v>45976</v>
+        <v>45995</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>14</v>
@@ -2570,19 +2526,19 @@
     </row>
     <row r="63" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C63" s="5">
-        <v>15944040</v>
+        <v>68413737</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="E63" s="6">
-        <v>45975</v>
+        <v>46006</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>14</v>
@@ -2590,19 +2546,19 @@
     </row>
     <row r="64" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="C64" s="5">
-        <v>13134671</v>
+        <v>6200000</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="E64" s="6">
-        <v>45989</v>
+        <v>45990</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>14</v>
@@ -2610,19 +2566,19 @@
     </row>
     <row r="65" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C65" s="5">
-        <v>10162000</v>
+        <v>3181300</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E65" s="6">
-        <v>45987</v>
+        <v>45999</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>14</v>
@@ -2630,19 +2586,19 @@
     </row>
     <row r="66" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C66" s="5">
-        <v>52787160</v>
+        <v>3181300</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>13</v>
+        <v>125</v>
       </c>
       <c r="E66" s="6">
-        <v>45978</v>
+        <v>45994</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>14</v>
@@ -2650,19 +2606,19 @@
     </row>
     <row r="67" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>124</v>
       </c>
       <c r="C67" s="5">
-        <v>9331000</v>
+        <v>3115215</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>125</v>
       </c>
       <c r="E67" s="6">
-        <v>45971</v>
+        <v>45993</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>14</v>
@@ -2670,19 +2626,19 @@
     </row>
     <row r="68" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>124</v>
       </c>
       <c r="C68" s="5">
-        <v>15285500</v>
+        <v>1143300</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>125</v>
       </c>
       <c r="E68" s="6">
-        <v>45976</v>
+        <v>45996</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>14</v>
@@ -2690,19 +2646,19 @@
     </row>
     <row r="69" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C69" s="5">
-        <v>31020120</v>
+        <v>18502159</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="E69" s="6">
-        <v>45982</v>
+        <v>46008</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>14</v>
@@ -2710,19 +2666,19 @@
     </row>
     <row r="70" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C70" s="5">
-        <v>12426277</v>
+        <v>3539000</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="E70" s="6">
-        <v>45976</v>
+        <v>45979</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>14</v>
@@ -2730,19 +2686,19 @@
     </row>
     <row r="71" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C71" s="5">
-        <v>108725300</v>
+        <v>7490260</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>69</v>
+        <v>133</v>
       </c>
       <c r="E71" s="6">
-        <v>45979</v>
+        <v>45996</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>14</v>
@@ -2750,19 +2706,19 @@
     </row>
     <row r="72" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C72" s="5">
-        <v>1665000</v>
+        <v>22012300</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>69</v>
+        <v>138</v>
       </c>
       <c r="E72" s="6">
-        <v>45985</v>
+        <v>45992</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>14</v>
@@ -2770,19 +2726,19 @@
     </row>
     <row r="73" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C73" s="5">
-        <v>2623548</v>
+        <v>16547600</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>69</v>
+        <v>138</v>
       </c>
       <c r="E73" s="6">
-        <v>45986</v>
+        <v>45997</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>14</v>
@@ -2790,19 +2746,19 @@
     </row>
     <row r="74" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B74" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="C74" s="5">
+        <v>18511500</v>
+      </c>
+      <c r="D74" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C74" s="5">
-        <v>2201605</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>69</v>
-      </c>
       <c r="E74" s="6">
-        <v>45979</v>
+        <v>46004</v>
       </c>
       <c r="F74" s="5" t="s">
         <v>14</v>
@@ -2810,19 +2766,19 @@
     </row>
     <row r="75" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C75" s="5">
-        <v>226898425</v>
+        <v>20091000</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="E75" s="6">
-        <v>45975</v>
+        <v>46001</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>14</v>
@@ -2830,19 +2786,19 @@
     </row>
     <row r="76" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C76" s="5">
-        <v>10703563</v>
+        <v>15591000</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="E76" s="6">
-        <v>45982</v>
+        <v>46009</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>14</v>
@@ -2850,19 +2806,19 @@
     </row>
     <row r="77" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C77" s="5">
-        <v>20765100</v>
+        <v>59272200</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="E77" s="6">
-        <v>45975</v>
+        <v>46000</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>14</v>
@@ -2870,19 +2826,19 @@
     </row>
     <row r="78" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C78" s="5">
-        <v>85501080</v>
+        <v>43448000</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="E78" s="6">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>14</v>
@@ -2890,19 +2846,19 @@
     </row>
     <row r="79" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C79" s="5">
-        <v>15406256</v>
+        <v>48291300</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="E79" s="6">
-        <v>45986</v>
+        <v>46009</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>14</v>
@@ -2910,19 +2866,19 @@
     </row>
     <row r="80" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C80" s="5">
-        <v>3181300</v>
+        <v>34893000</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>149</v>
+        <v>13</v>
       </c>
       <c r="E80" s="6">
-        <v>45999</v>
+        <v>45996</v>
       </c>
       <c r="F80" s="5" t="s">
         <v>14</v>
@@ -2930,19 +2886,19 @@
     </row>
     <row r="81" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C81" s="5">
-        <v>7904200</v>
+        <v>15086000</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="E81" s="6">
-        <v>45976</v>
+        <v>45997</v>
       </c>
       <c r="F81" s="5" t="s">
         <v>14</v>
@@ -2950,19 +2906,19 @@
     </row>
     <row r="82" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C82" s="5">
-        <v>7904200</v>
+        <v>19505000</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>149</v>
+        <v>42</v>
       </c>
       <c r="E82" s="6">
-        <v>45980</v>
+        <v>46022</v>
       </c>
       <c r="F82" s="5" t="s">
         <v>14</v>
@@ -2970,19 +2926,19 @@
     </row>
     <row r="83" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="C83" s="5">
-        <v>7904200</v>
+        <v>7795000</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>149</v>
+        <v>42</v>
       </c>
       <c r="E83" s="6">
-        <v>45982</v>
+        <v>46005</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>14</v>
@@ -2990,19 +2946,19 @@
     </row>
     <row r="84" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="C84" s="5">
-        <v>3181300</v>
+        <v>23160869</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>149</v>
+        <v>13</v>
       </c>
       <c r="E84" s="6">
-        <v>45994</v>
+        <v>46015</v>
       </c>
       <c r="F84" s="5" t="s">
         <v>14</v>
@@ -3010,19 +2966,19 @@
     </row>
     <row r="85" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C85" s="5">
-        <v>146086354</v>
+        <v>109871000</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="E85" s="6">
-        <v>45980</v>
+        <v>46014</v>
       </c>
       <c r="F85" s="5" t="s">
         <v>14</v>
@@ -3030,19 +2986,19 @@
     </row>
     <row r="86" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C86" s="5">
-        <v>7053556</v>
+        <v>60913000</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="E86" s="6">
-        <v>45986</v>
+        <v>46017</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>14</v>
@@ -3050,19 +3006,19 @@
     </row>
     <row r="87" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C87" s="5">
-        <v>28394100</v>
+        <v>10399000</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="E87" s="6">
-        <v>45976</v>
+        <v>46008</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>14</v>
@@ -3070,19 +3026,19 @@
     </row>
     <row r="88" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C88" s="5">
-        <v>22012300</v>
+        <v>7839000</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="E88" s="6">
-        <v>45992</v>
+        <v>46015</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>14</v>
@@ -3090,19 +3046,19 @@
     </row>
     <row r="89" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="C89" s="5">
-        <v>11336400</v>
+        <v>3653800</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="E89" s="6">
-        <v>45983</v>
+        <v>46026</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>14</v>
@@ -3110,19 +3066,19 @@
     </row>
     <row r="90" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C90" s="5">
-        <v>17794900</v>
+        <v>39757000</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="E90" s="6">
-        <v>45976</v>
+        <v>45994</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>14</v>
@@ -3130,19 +3086,19 @@
     </row>
     <row r="91" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="C91" s="5">
-        <v>59272200</v>
+        <v>8268100</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="E91" s="6">
-        <v>46000</v>
+        <v>45988</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>14</v>
@@ -3150,19 +3106,19 @@
     </row>
     <row r="92" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C92" s="5">
-        <v>17089200</v>
+        <v>9996000</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="E92" s="6">
-        <v>45982</v>
+        <v>45994</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>14</v>
@@ -3170,19 +3126,19 @@
     </row>
     <row r="93" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C93" s="5">
-        <v>7130000</v>
+        <v>34215750</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="E93" s="6">
-        <v>45976</v>
+        <v>46013</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>14</v>
@@ -3190,19 +3146,19 @@
     </row>
     <row r="94" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C94" s="5">
+        <v>27139500</v>
+      </c>
+      <c r="D94" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="B94" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="C94" s="5">
-        <v>52220000</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>69</v>
-      </c>
       <c r="E94" s="6">
-        <v>45989</v>
+        <v>46009</v>
       </c>
       <c r="F94" s="5" t="s">
         <v>14</v>
@@ -3210,19 +3166,19 @@
     </row>
     <row r="95" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C95" s="5">
-        <v>34893000</v>
+        <v>20646000</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="E95" s="6">
-        <v>45996</v>
+        <v>46008</v>
       </c>
       <c r="F95" s="5" t="s">
         <v>14</v>
@@ -3230,19 +3186,19 @@
     </row>
     <row r="96" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C96" s="5">
-        <v>35500000</v>
+        <v>19980000</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="E96" s="6">
-        <v>45987</v>
+        <v>46010</v>
       </c>
       <c r="F96" s="5" t="s">
         <v>14</v>
@@ -3250,19 +3206,19 @@
     </row>
     <row r="97" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B97" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B97" s="5" t="s">
-        <v>173</v>
-      </c>
       <c r="C97" s="5">
-        <v>17700000</v>
+        <v>19980000</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="E97" s="6">
-        <v>45989</v>
+        <v>46017</v>
       </c>
       <c r="F97" s="5" t="s">
         <v>14</v>
@@ -3270,19 +3226,19 @@
     </row>
     <row r="98" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C98" s="5">
-        <v>38479059</v>
+        <v>19980000</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="E98" s="6">
-        <v>45980</v>
+        <v>46014</v>
       </c>
       <c r="F98" s="5" t="s">
         <v>14</v>
@@ -3290,16 +3246,16 @@
     </row>
     <row r="99" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C99" s="5">
-        <v>23160869</v>
+        <v>19547100</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="E99" s="6">
         <v>46015</v>
@@ -3310,19 +3266,19 @@
     </row>
     <row r="100" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C100" s="5">
-        <v>17127000</v>
+        <v>31087000</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
       <c r="E100" s="6">
-        <v>45982</v>
+        <v>45990</v>
       </c>
       <c r="F100" s="5" t="s">
         <v>14</v>
@@ -3330,19 +3286,19 @@
     </row>
     <row r="101" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C101" s="5">
-        <v>109871000</v>
+        <v>113935950</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="E101" s="6">
-        <v>46014</v>
+        <v>46000</v>
       </c>
       <c r="F101" s="5" t="s">
         <v>14</v>
@@ -3350,19 +3306,19 @@
     </row>
     <row r="102" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="C102" s="5">
-        <v>60913000</v>
+        <v>11151878</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>47</v>
+        <v>188</v>
       </c>
       <c r="E102" s="6">
-        <v>46017</v>
+        <v>45989</v>
       </c>
       <c r="F102" s="5" t="s">
         <v>14</v>
@@ -3370,19 +3326,19 @@
     </row>
     <row r="103" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="C103" s="5">
-        <v>5225200</v>
+        <v>9632000</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E103" s="6">
-        <v>45988</v>
+        <v>46001</v>
       </c>
       <c r="F103" s="5" t="s">
         <v>14</v>
@@ -3390,19 +3346,19 @@
     </row>
     <row r="104" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="C104" s="5">
-        <v>35000000</v>
+        <v>5497495</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>35</v>
+        <v>192</v>
       </c>
       <c r="E104" s="6">
-        <v>45980</v>
+        <v>46013</v>
       </c>
       <c r="F104" s="5" t="s">
         <v>14</v>
@@ -3410,19 +3366,19 @@
     </row>
     <row r="105" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C105" s="5">
-        <v>53440500</v>
+        <v>2582415</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E105" s="6">
-        <v>45975</v>
+        <v>46013</v>
       </c>
       <c r="F105" s="5" t="s">
         <v>14</v>
@@ -3430,19 +3386,19 @@
     </row>
     <row r="106" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C106" s="5">
-        <v>69050000</v>
+        <v>771450</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="E106" s="6">
-        <v>45979</v>
+        <v>46002</v>
       </c>
       <c r="F106" s="5" t="s">
         <v>14</v>
@@ -3450,19 +3406,19 @@
     </row>
     <row r="107" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C107" s="5">
-        <v>50285000</v>
+        <v>7448500</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>188</v>
+        <v>37</v>
       </c>
       <c r="E107" s="6">
-        <v>45976</v>
+        <v>46002</v>
       </c>
       <c r="F107" s="5" t="s">
         <v>14</v>
@@ -3470,19 +3426,19 @@
     </row>
     <row r="108" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="C108" s="5">
-        <v>50285000</v>
+        <v>3714600</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>188</v>
+        <v>37</v>
       </c>
       <c r="E108" s="6">
-        <v>45981</v>
+        <v>46026</v>
       </c>
       <c r="F108" s="5" t="s">
         <v>14</v>
@@ -3490,19 +3446,19 @@
     </row>
     <row r="109" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="C109" s="5">
-        <v>50285000</v>
+        <v>7732800</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>188</v>
+        <v>37</v>
       </c>
       <c r="E109" s="6">
-        <v>45983</v>
+        <v>46041</v>
       </c>
       <c r="F109" s="5" t="s">
         <v>14</v>
@@ -3510,19 +3466,19 @@
     </row>
     <row r="110" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C110" s="5">
-        <v>24642000</v>
+        <v>17489300</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>188</v>
+        <v>37</v>
       </c>
       <c r="E110" s="6">
-        <v>45982</v>
+        <v>46008</v>
       </c>
       <c r="F110" s="5" t="s">
         <v>14</v>
@@ -3530,19 +3486,19 @@
     </row>
     <row r="111" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C111" s="5">
-        <v>19980000</v>
+        <v>40181000</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>188</v>
+        <v>37</v>
       </c>
       <c r="E111" s="6">
-        <v>45980</v>
+        <v>45998</v>
       </c>
       <c r="F111" s="5" t="s">
         <v>14</v>
@@ -3550,19 +3506,19 @@
     </row>
     <row r="112" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C112" s="5">
-        <v>19480500</v>
+        <v>1122300</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>188</v>
+        <v>37</v>
       </c>
       <c r="E112" s="6">
-        <v>45981</v>
+        <v>46000</v>
       </c>
       <c r="F112" s="5" t="s">
         <v>14</v>
@@ -3570,19 +3526,19 @@
     </row>
     <row r="113" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C113" s="5">
-        <v>35964000</v>
+        <v>41306100</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>188</v>
+        <v>37</v>
       </c>
       <c r="E113" s="6">
-        <v>45983</v>
+        <v>46006</v>
       </c>
       <c r="F113" s="5" t="s">
         <v>14</v>
@@ -3590,19 +3546,19 @@
     </row>
     <row r="114" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B114" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B114" s="5" t="s">
-        <v>195</v>
-      </c>
       <c r="C114" s="5">
-        <v>19092000</v>
+        <v>27795200</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>188</v>
+        <v>37</v>
       </c>
       <c r="E114" s="6">
-        <v>45980</v>
+        <v>46021</v>
       </c>
       <c r="F114" s="5" t="s">
         <v>14</v>
@@ -3610,19 +3566,19 @@
     </row>
     <row r="115" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C115" s="5">
-        <v>113935950</v>
+        <v>54567000</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>96</v>
+        <v>37</v>
       </c>
       <c r="E115" s="6">
-        <v>46000</v>
+        <v>46012</v>
       </c>
       <c r="F115" s="5" t="s">
         <v>14</v>
@@ -3630,19 +3586,19 @@
     </row>
     <row r="116" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C116" s="5">
-        <v>12098813</v>
+        <v>1359900</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>204</v>
+        <v>37</v>
       </c>
       <c r="E116" s="6">
-        <v>45973</v>
+        <v>46025</v>
       </c>
       <c r="F116" s="5" t="s">
         <v>14</v>
@@ -3650,19 +3606,19 @@
     </row>
     <row r="117" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C117" s="5">
-        <v>69748368</v>
+        <v>13990000</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>81</v>
+        <v>210</v>
       </c>
       <c r="E117" s="6">
-        <v>45987</v>
+        <v>46007</v>
       </c>
       <c r="F117" s="5" t="s">
         <v>14</v>
@@ -3670,19 +3626,19 @@
     </row>
     <row r="118" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C118" s="5">
-        <v>109105340</v>
+        <v>11190000</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>81</v>
+        <v>210</v>
       </c>
       <c r="E118" s="6">
-        <v>45981</v>
+        <v>46011</v>
       </c>
       <c r="F118" s="5" t="s">
         <v>14</v>
@@ -3690,19 +3646,19 @@
     </row>
     <row r="119" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>209</v>
       </c>
       <c r="C119" s="5">
-        <v>9632000</v>
+        <v>190353643</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>69</v>
+        <v>210</v>
       </c>
       <c r="E119" s="6">
-        <v>46001</v>
+        <v>46047</v>
       </c>
       <c r="F119" s="5" t="s">
         <v>14</v>
@@ -3710,19 +3666,19 @@
     </row>
     <row r="120" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C120" s="5">
-        <v>13193000</v>
+        <v>45771500</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="E120" s="6">
-        <v>45980</v>
+        <v>45996</v>
       </c>
       <c r="F120" s="5" t="s">
         <v>14</v>
@@ -3730,19 +3686,19 @@
     </row>
     <row r="121" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C121" s="5">
-        <v>5636000</v>
+        <v>1471000</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="E121" s="6">
-        <v>45990</v>
+        <v>45994</v>
       </c>
       <c r="F121" s="5" t="s">
         <v>14</v>
@@ -3750,19 +3706,19 @@
     </row>
     <row r="122" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C122" s="5">
-        <v>7877800</v>
+        <v>835000</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>214</v>
+        <v>30</v>
       </c>
       <c r="E122" s="6">
-        <v>45978</v>
+        <v>46004</v>
       </c>
       <c r="F122" s="5" t="s">
         <v>14</v>
@@ -3770,19 +3726,19 @@
     </row>
     <row r="123" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>216</v>
       </c>
       <c r="C123" s="5">
-        <v>49550900</v>
+        <v>1176000</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E123" s="6">
-        <v>45976</v>
+        <v>46003</v>
       </c>
       <c r="F123" s="5" t="s">
         <v>14</v>
@@ -3790,19 +3746,19 @@
     </row>
     <row r="124" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C124" s="5">
-        <v>7990900</v>
+        <v>246383600</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E124" s="6">
-        <v>45985</v>
+        <v>46003</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>14</v>
@@ -3810,19 +3766,19 @@
     </row>
     <row r="125" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C125" s="5">
-        <v>3871100</v>
+        <v>18181000</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="E125" s="6">
-        <v>45978</v>
+        <v>46002</v>
       </c>
       <c r="F125" s="5" t="s">
         <v>14</v>
@@ -3830,19 +3786,19 @@
     </row>
     <row r="126" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C126" s="5">
-        <v>12367800</v>
+        <v>4195800</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="E126" s="6">
-        <v>45984</v>
+        <v>45993</v>
       </c>
       <c r="F126" s="5" t="s">
         <v>14</v>
@@ -3850,19 +3806,19 @@
     </row>
     <row r="127" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="C127" s="5">
-        <v>10635600</v>
+        <v>3624308</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="E127" s="6">
-        <v>45990</v>
+        <v>45993</v>
       </c>
       <c r="F127" s="5" t="s">
         <v>14</v>
@@ -3870,19 +3826,19 @@
     </row>
     <row r="128" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="C128" s="5">
-        <v>17489300</v>
+        <v>12788410</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E128" s="6">
-        <v>46008</v>
+        <v>45991</v>
       </c>
       <c r="F128" s="5" t="s">
         <v>14</v>
@@ -3890,19 +3846,19 @@
     </row>
     <row r="129" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="C129" s="5">
-        <v>40181000</v>
+        <v>14962170</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E129" s="6">
-        <v>45998</v>
+        <v>46011</v>
       </c>
       <c r="F129" s="5" t="s">
         <v>14</v>
@@ -3910,19 +3866,19 @@
     </row>
     <row r="130" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C130" s="5">
-        <v>13990000</v>
+        <v>41692951</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>125</v>
+        <v>13</v>
       </c>
       <c r="E130" s="6">
-        <v>46007</v>
+        <v>45996</v>
       </c>
       <c r="F130" s="5" t="s">
         <v>14</v>
@@ -3930,19 +3886,19 @@
     </row>
     <row r="131" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="C131" s="5">
-        <v>42247300</v>
+        <v>18983775</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="E131" s="6">
-        <v>45975</v>
+        <v>45994</v>
       </c>
       <c r="F131" s="5" t="s">
         <v>14</v>
@@ -3950,19 +3906,19 @@
     </row>
     <row r="132" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="C132" s="5">
-        <v>7849600</v>
+        <v>5818600</v>
       </c>
       <c r="D132" s="5" t="s">
         <v>53</v>
       </c>
       <c r="E132" s="6">
-        <v>45975</v>
+        <v>45997</v>
       </c>
       <c r="F132" s="5" t="s">
         <v>14</v>
@@ -3970,19 +3926,19 @@
     </row>
     <row r="133" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="5" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="C133" s="5">
-        <v>3865900</v>
+        <v>3968200</v>
       </c>
       <c r="D133" s="5" t="s">
         <v>53</v>
       </c>
       <c r="E133" s="6">
-        <v>45980</v>
+        <v>46001</v>
       </c>
       <c r="F133" s="5" t="s">
         <v>14</v>
@@ -3990,19 +3946,19 @@
     </row>
     <row r="134" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="5" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C134" s="5">
-        <v>2220000</v>
+        <v>391900</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="E134" s="6">
-        <v>45976</v>
+        <v>46002</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>14</v>
@@ -4010,19 +3966,19 @@
     </row>
     <row r="135" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="5" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C135" s="5">
-        <v>2220000</v>
+        <v>2418100</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="E135" s="6">
-        <v>45983</v>
+        <v>46003</v>
       </c>
       <c r="F135" s="5" t="s">
         <v>14</v>
@@ -4030,19 +3986,19 @@
     </row>
     <row r="136" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="5" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C136" s="5">
-        <v>11430000</v>
+        <v>13478400</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>234</v>
+        <v>13</v>
       </c>
       <c r="E136" s="6">
-        <v>45979</v>
+        <v>45999</v>
       </c>
       <c r="F136" s="5" t="s">
         <v>14</v>
@@ -4050,19 +4006,19 @@
     </row>
     <row r="137" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="5" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C137" s="5">
-        <v>4297000</v>
+        <v>5216100</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="E137" s="6">
-        <v>45981</v>
+        <v>46002</v>
       </c>
       <c r="F137" s="5" t="s">
         <v>14</v>
@@ -4070,19 +4026,19 @@
     </row>
     <row r="138" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="5" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C138" s="5">
-        <v>63399800</v>
+        <v>5241400</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="E138" s="6">
-        <v>45981</v>
+        <v>46014</v>
       </c>
       <c r="F138" s="5" t="s">
         <v>14</v>
@@ -4090,19 +4046,19 @@
     </row>
     <row r="139" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="5" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>240</v>
       </c>
       <c r="C139" s="5">
-        <v>7507067</v>
+        <v>2077900</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>81</v>
+        <v>13</v>
       </c>
       <c r="E139" s="6">
-        <v>45974</v>
+        <v>45995</v>
       </c>
       <c r="F139" s="5" t="s">
         <v>14</v>
@@ -4110,19 +4066,19 @@
     </row>
     <row r="140" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="5" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C140" s="5">
-        <v>25650300</v>
+        <v>1122900</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>125</v>
+        <v>13</v>
       </c>
       <c r="E140" s="6">
-        <v>45973</v>
+        <v>45999</v>
       </c>
       <c r="F140" s="5" t="s">
         <v>14</v>
@@ -4130,19 +4086,19 @@
     </row>
     <row r="141" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="5" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C141" s="5">
-        <v>37011000</v>
+        <v>4409400</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>125</v>
+        <v>13</v>
       </c>
       <c r="E141" s="6">
-        <v>45975</v>
+        <v>45997</v>
       </c>
       <c r="F141" s="5" t="s">
         <v>14</v>
@@ -4150,19 +4106,19 @@
     </row>
     <row r="142" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="5" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>245</v>
       </c>
       <c r="C142" s="5">
-        <v>1010100</v>
+        <v>4415400</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>246</v>
+        <v>13</v>
       </c>
       <c r="E142" s="6">
-        <v>45982</v>
+        <v>46008</v>
       </c>
       <c r="F142" s="5" t="s">
         <v>14</v>
@@ -4170,19 +4126,19 @@
     </row>
     <row r="143" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C143" s="5">
-        <v>18493664</v>
+        <v>5737925</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>47</v>
+        <v>250</v>
       </c>
       <c r="E143" s="6">
-        <v>45978</v>
+        <v>46013</v>
       </c>
       <c r="F143" s="5" t="s">
         <v>14</v>
@@ -4190,19 +4146,19 @@
     </row>
     <row r="144" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B144" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="B144" s="5" t="s">
+      <c r="C144" s="5">
+        <v>3639347</v>
+      </c>
+      <c r="D144" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="C144" s="5">
-        <v>2645100</v>
-      </c>
-      <c r="D144" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="E144" s="6">
-        <v>45980</v>
+        <v>45996</v>
       </c>
       <c r="F144" s="5" t="s">
         <v>14</v>
@@ -4210,19 +4166,19 @@
     </row>
     <row r="145" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B145" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C145" s="5">
+        <v>3570194</v>
+      </c>
+      <c r="D145" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="C145" s="5">
-        <v>8088000</v>
-      </c>
-      <c r="D145" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="E145" s="6">
-        <v>45975</v>
+        <v>46004</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>14</v>
@@ -4230,19 +4186,19 @@
     </row>
     <row r="146" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C146" s="5">
-        <v>12472600</v>
+        <v>10003310</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>53</v>
+        <v>188</v>
       </c>
       <c r="E146" s="6">
-        <v>45976</v>
+        <v>46002</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>14</v>
@@ -4250,19 +4206,19 @@
     </row>
     <row r="147" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C147" s="5">
-        <v>2518500</v>
+        <v>3153500</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="E147" s="6">
-        <v>45979</v>
+        <v>45994</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>14</v>
@@ -4270,19 +4226,19 @@
     </row>
     <row r="148" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="C148" s="5">
-        <v>2251900</v>
+        <v>1660000</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="E148" s="6">
-        <v>45989</v>
+        <v>46003</v>
       </c>
       <c r="F148" s="5" t="s">
         <v>14</v>
@@ -4290,19 +4246,19 @@
     </row>
     <row r="149" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="5" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C149" s="5">
-        <v>2835000</v>
+        <v>472850</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E149" s="6">
-        <v>45974</v>
+        <v>45981</v>
       </c>
       <c r="F149" s="5" t="s">
         <v>14</v>
@@ -4310,19 +4266,19 @@
     </row>
     <row r="150" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="5" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C150" s="5">
-        <v>2077900</v>
+        <v>952700</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="E150" s="6">
-        <v>45995</v>
+        <v>46004</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>14</v>
@@ -4330,19 +4286,19 @@
     </row>
     <row r="151" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B151" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="B151" s="5" t="s">
-        <v>260</v>
-      </c>
       <c r="C151" s="5">
-        <v>3283300</v>
+        <v>1059800</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="E151" s="6">
-        <v>45981</v>
+        <v>46010</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>14</v>
@@ -4350,19 +4306,19 @@
     </row>
     <row r="152" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C152" s="5">
-        <v>3322600</v>
+        <v>1332000</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="E152" s="6">
-        <v>45986</v>
+        <v>45995</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>14</v>
@@ -4370,19 +4326,19 @@
     </row>
     <row r="153" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C153" s="5">
-        <v>1122900</v>
+        <v>41923100</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="E153" s="6">
-        <v>45999</v>
+        <v>46004</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>14</v>
@@ -4390,19 +4346,19 @@
     </row>
     <row r="154" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="5" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C154" s="5">
-        <v>3639347</v>
+        <v>1044500</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>265</v>
+        <v>21</v>
       </c>
       <c r="E154" s="6">
-        <v>45996</v>
+        <v>45993</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>14</v>
@@ -4410,16 +4366,16 @@
     </row>
     <row r="155" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C155" s="5">
-        <v>3570194</v>
+        <v>9915100</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>265</v>
+        <v>13</v>
       </c>
       <c r="E155" s="6">
         <v>46004</v>
@@ -4430,19 +4386,19 @@
     </row>
     <row r="156" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="C156" s="5">
-        <v>3153500</v>
+        <v>4544000</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>69</v>
+        <v>210</v>
       </c>
       <c r="E156" s="6">
-        <v>45976</v>
+        <v>45994</v>
       </c>
       <c r="F156" s="5" t="s">
         <v>14</v>
@@ -4450,19 +4406,19 @@
     </row>
     <row r="157" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A157" s="5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="C157" s="5">
-        <v>12053400</v>
+        <v>11569000</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="E157" s="6">
-        <v>45990</v>
+        <v>45994</v>
       </c>
       <c r="F157" s="5" t="s">
         <v>14</v>
@@ -4470,19 +4426,19 @@
     </row>
     <row r="158" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="5" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="C158" s="5">
-        <v>3153500</v>
+        <v>11074000</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="E158" s="6">
-        <v>45994</v>
+        <v>46002</v>
       </c>
       <c r="F158" s="5" t="s">
         <v>14</v>
@@ -4490,19 +4446,19 @@
     </row>
     <row r="159" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A159" s="5" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C159" s="5">
-        <v>472850</v>
+        <v>10000000</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E159" s="6">
-        <v>45981</v>
+        <v>46007</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>14</v>
@@ -4510,19 +4466,19 @@
     </row>
     <row r="160" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A160" s="5" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B160" s="5" t="s">
         <v>273</v>
       </c>
       <c r="C160" s="5">
-        <v>17750500</v>
+        <v>12949000</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="E160" s="6">
-        <v>45976</v>
+        <v>45999</v>
       </c>
       <c r="F160" s="5" t="s">
         <v>14</v>
@@ -4530,19 +4486,19 @@
     </row>
     <row r="161" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A161" s="5" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C161" s="5">
-        <v>1698300</v>
+        <v>7951000</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="E161" s="6">
-        <v>45979</v>
+        <v>46009</v>
       </c>
       <c r="F161" s="5" t="s">
         <v>14</v>
@@ -4550,19 +4506,19 @@
     </row>
     <row r="162" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A162" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B162" s="5" t="s">
         <v>273</v>
       </c>
       <c r="C162" s="5">
-        <v>17636650</v>
+        <v>7951000</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="E162" s="6">
-        <v>45990</v>
+        <v>46011</v>
       </c>
       <c r="F162" s="5" t="s">
         <v>14</v>
@@ -4570,19 +4526,19 @@
     </row>
     <row r="163" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A163" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C163" s="5">
-        <v>3470200</v>
+        <v>6242000</v>
       </c>
       <c r="D163" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E163" s="6">
-        <v>45976</v>
+        <v>46007</v>
       </c>
       <c r="F163" s="5" t="s">
         <v>14</v>
@@ -4590,19 +4546,19 @@
     </row>
     <row r="164" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A164" s="5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C164" s="5">
-        <v>11989000</v>
+        <v>9341000</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="E164" s="6">
-        <v>45982</v>
+        <v>46016</v>
       </c>
       <c r="F164" s="5" t="s">
         <v>14</v>
@@ -4613,16 +4569,16 @@
         <v>281</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="C165" s="5">
-        <v>4000630</v>
+        <v>9341000</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>283</v>
+        <v>13</v>
       </c>
       <c r="E165" s="6">
-        <v>45981</v>
+        <v>46021</v>
       </c>
       <c r="F165" s="5" t="s">
         <v>14</v>
@@ -4630,19 +4586,19 @@
     </row>
     <row r="166" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A166" s="5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C166" s="5">
-        <v>2998100</v>
+        <v>2140000</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>110</v>
+        <v>13</v>
       </c>
       <c r="E166" s="6">
-        <v>45974</v>
+        <v>45995</v>
       </c>
       <c r="F166" s="5" t="s">
         <v>14</v>
@@ -4650,19 +4606,19 @@
     </row>
     <row r="167" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A167" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C167" s="5">
-        <v>27723000</v>
+        <v>15564800</v>
       </c>
       <c r="D167" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E167" s="6">
-        <v>45979</v>
+        <v>46004</v>
       </c>
       <c r="F167" s="5" t="s">
         <v>14</v>
@@ -4670,19 +4626,19 @@
     </row>
     <row r="168" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A168" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C168" s="5">
-        <v>9916850</v>
+        <v>49116000</v>
       </c>
       <c r="D168" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E168" s="6">
-        <v>45986</v>
+        <v>46011</v>
       </c>
       <c r="F168" s="5" t="s">
         <v>14</v>
@@ -4690,19 +4646,19 @@
     </row>
     <row r="169" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A169" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C169" s="5">
-        <v>2902700</v>
+        <v>786000</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="E169" s="6">
-        <v>45976</v>
+        <v>45997</v>
       </c>
       <c r="F169" s="5" t="s">
         <v>14</v>
@@ -4710,19 +4666,19 @@
     </row>
     <row r="170" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A170" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C170" s="5">
-        <v>4007900</v>
+        <v>40787500</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="E170" s="6">
-        <v>45976</v>
+        <v>46009</v>
       </c>
       <c r="F170" s="5" t="s">
         <v>14</v>
@@ -4730,19 +4686,19 @@
     </row>
     <row r="171" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A171" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C171" s="5">
-        <v>7295000</v>
+        <v>5644616</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="E171" s="6">
-        <v>45979</v>
+        <v>46010</v>
       </c>
       <c r="F171" s="5" t="s">
         <v>14</v>
@@ -4750,19 +4706,19 @@
     </row>
     <row r="172" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A172" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B172" s="5" t="s">
         <v>294</v>
       </c>
       <c r="C172" s="5">
-        <v>7295000</v>
+        <v>87468710</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>69</v>
+        <v>295</v>
       </c>
       <c r="E172" s="6">
-        <v>45980</v>
+        <v>45997</v>
       </c>
       <c r="F172" s="5" t="s">
         <v>14</v>
@@ -4776,13 +4732,13 @@
         <v>294</v>
       </c>
       <c r="C173" s="5">
-        <v>8117000</v>
+        <v>25870770</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>69</v>
+        <v>295</v>
       </c>
       <c r="E173" s="6">
-        <v>45990</v>
+        <v>46004</v>
       </c>
       <c r="F173" s="5" t="s">
         <v>14</v>
@@ -4793,16 +4749,16 @@
         <v>297</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C174" s="5">
-        <v>12961000</v>
+        <v>437000</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="E174" s="6">
-        <v>45976</v>
+        <v>45997</v>
       </c>
       <c r="F174" s="5" t="s">
         <v>14</v>
@@ -4810,19 +4766,19 @@
     </row>
     <row r="175" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A175" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C175" s="5">
-        <v>11569000</v>
+        <v>3225000</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="E175" s="6">
-        <v>45994</v>
+        <v>46004</v>
       </c>
       <c r="F175" s="5" t="s">
         <v>14</v>
@@ -4830,19 +4786,19 @@
     </row>
     <row r="176" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A176" s="5" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C176" s="5">
-        <v>11074000</v>
+        <v>2481000</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="E176" s="6">
-        <v>46002</v>
+        <v>46018</v>
       </c>
       <c r="F176" s="5" t="s">
         <v>14</v>
@@ -4850,19 +4806,19 @@
     </row>
     <row r="177" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A177" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C177" s="5">
-        <v>7296000</v>
+        <v>1354200</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="E177" s="6">
-        <v>45983</v>
+        <v>46004</v>
       </c>
       <c r="F177" s="5" t="s">
         <v>14</v>
@@ -4870,19 +4826,19 @@
     </row>
     <row r="178" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A178" s="5" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C178" s="5">
-        <v>3210000</v>
+        <v>1495500</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="E178" s="6">
-        <v>45990</v>
+        <v>45995</v>
       </c>
       <c r="F178" s="5" t="s">
         <v>14</v>
@@ -4890,19 +4846,19 @@
     </row>
     <row r="179" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A179" s="5" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C179" s="5">
-        <v>26350500</v>
+        <v>36419100</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="E179" s="6">
-        <v>45978</v>
+        <v>45995</v>
       </c>
       <c r="F179" s="5" t="s">
         <v>14</v>
@@ -4910,19 +4866,19 @@
     </row>
     <row r="180" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A180" s="5" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C180" s="5">
-        <v>3164800</v>
+        <v>54381600</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="E180" s="6">
-        <v>45990</v>
+        <v>46015</v>
       </c>
       <c r="F180" s="5" t="s">
         <v>14</v>
@@ -4930,19 +4886,19 @@
     </row>
     <row r="181" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A181" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C181" s="5">
-        <v>15564800</v>
+        <v>1030000</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="E181" s="6">
-        <v>46004</v>
+        <v>45991</v>
       </c>
       <c r="F181" s="5" t="s">
         <v>14</v>
@@ -4950,19 +4906,19 @@
     </row>
     <row r="182" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A182" s="5" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="C182" s="5">
-        <v>49116000</v>
+        <v>19490000</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="E182" s="6">
-        <v>46011</v>
+        <v>45996</v>
       </c>
       <c r="F182" s="5" t="s">
         <v>14</v>
@@ -4970,19 +4926,19 @@
     </row>
     <row r="183" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A183" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C183" s="5">
-        <v>57111290</v>
+        <v>26014000</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="E183" s="6">
-        <v>45978</v>
+        <v>45995</v>
       </c>
       <c r="F183" s="5" t="s">
         <v>14</v>
@@ -4990,19 +4946,19 @@
     </row>
     <row r="184" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A184" s="5" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C184" s="5">
-        <v>1004500</v>
+        <v>10937000</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="E184" s="6">
-        <v>45979</v>
+        <v>46000</v>
       </c>
       <c r="F184" s="5" t="s">
         <v>14</v>
@@ -5010,19 +4966,19 @@
     </row>
     <row r="185" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A185" s="5" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C185" s="5">
-        <v>78000300</v>
+        <v>4824000</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="E185" s="6">
-        <v>45978</v>
+        <v>45992</v>
       </c>
       <c r="F185" s="5" t="s">
         <v>14</v>
@@ -5030,19 +4986,19 @@
     </row>
     <row r="186" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A186" s="5" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C186" s="5">
-        <v>15694689</v>
+        <v>13081000</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="E186" s="6">
-        <v>45976</v>
+        <v>45997</v>
       </c>
       <c r="F186" s="5" t="s">
         <v>14</v>
@@ -5050,19 +5006,19 @@
     </row>
     <row r="187" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A187" s="5" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C187" s="5">
-        <v>1217000</v>
+        <v>18641000</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="E187" s="6">
-        <v>45976</v>
+        <v>46007</v>
       </c>
       <c r="F187" s="5" t="s">
         <v>14</v>
@@ -5070,19 +5026,19 @@
     </row>
     <row r="188" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A188" s="5" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="C188" s="5">
-        <v>2680000</v>
+        <v>1212952</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E188" s="6">
-        <v>45981</v>
+        <v>45995</v>
       </c>
       <c r="F188" s="5" t="s">
         <v>14</v>
@@ -5090,19 +5046,19 @@
     </row>
     <row r="189" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A189" s="5" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C189" s="5">
-        <v>437000</v>
+        <v>2484000</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="E189" s="6">
-        <v>45997</v>
+        <v>45993</v>
       </c>
       <c r="F189" s="5" t="s">
         <v>14</v>
@@ -5110,19 +5066,19 @@
     </row>
     <row r="190" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A190" s="5" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C190" s="5">
-        <v>3225000</v>
+        <v>1082100</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>106</v>
+        <v>326</v>
       </c>
       <c r="E190" s="6">
-        <v>46004</v>
+        <v>45989</v>
       </c>
       <c r="F190" s="5" t="s">
         <v>14</v>
@@ -5130,221 +5086,21 @@
     </row>
     <row r="191" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A191" s="5" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C191" s="5">
-        <v>80425000</v>
+        <v>3666663</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="E191" s="6">
-        <v>45980</v>
+        <v>45994</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A192" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="B192" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="C192" s="5">
-        <v>36419100</v>
-      </c>
-      <c r="D192" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E192" s="6">
-        <v>45995</v>
-      </c>
-      <c r="F192" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A193" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="B193" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="C193" s="5">
-        <v>1030000</v>
-      </c>
-      <c r="D193" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E193" s="6">
-        <v>45991</v>
-      </c>
-      <c r="F193" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A194" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="B194" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="C194" s="5">
-        <v>16834900</v>
-      </c>
-      <c r="D194" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E194" s="6">
-        <v>45976</v>
-      </c>
-      <c r="F194" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A195" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="B195" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="C195" s="5">
-        <v>18266000</v>
-      </c>
-      <c r="D195" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E195" s="6">
-        <v>45980</v>
-      </c>
-      <c r="F195" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A196" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="B196" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="C196" s="5">
-        <v>15327000</v>
-      </c>
-      <c r="D196" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E196" s="6">
-        <v>45989</v>
-      </c>
-      <c r="F196" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A197" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="B197" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="C197" s="5">
-        <v>1600342</v>
-      </c>
-      <c r="D197" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E197" s="6">
-        <v>45974</v>
-      </c>
-      <c r="F197" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A198" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="B198" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="C198" s="5">
-        <v>3338000</v>
-      </c>
-      <c r="D198" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E198" s="6">
-        <v>45976</v>
-      </c>
-      <c r="F198" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A199" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="B199" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="C199" s="5">
-        <v>13012000</v>
-      </c>
-      <c r="D199" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="E199" s="6">
-        <v>45980</v>
-      </c>
-      <c r="F199" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A200" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="B200" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="C200" s="5">
-        <v>1364000</v>
-      </c>
-      <c r="D200" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E200" s="6">
-        <v>45979</v>
-      </c>
-      <c r="F200" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A201" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="B201" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="C201" s="5">
-        <v>4309400</v>
-      </c>
-      <c r="D201" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="E201" s="6">
-        <v>45972</v>
-      </c>
-      <c r="F201" s="5" t="s">
         <v>14</v>
       </c>
     </row>

--- a/uploads/giro.xlsx
+++ b/uploads/giro.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coralis\20251202\fix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coralis\Eksport Implementasi\20251215\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7366BFBC-CBFC-4C9C-BD66-6360E235AA7A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12585"/>
   </bookViews>
   <sheets>
     <sheet name="Giro" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="380">
   <si>
     <t>nomor_giro</t>
   </si>
@@ -55,157 +54,166 @@
     <t>ex: Cair, Belum Cair</t>
   </si>
   <si>
-    <t>051546</t>
-  </si>
-  <si>
-    <t>039726</t>
+    <t>201979</t>
+  </si>
+  <si>
+    <t>017071</t>
+  </si>
+  <si>
+    <t>BNI'46</t>
+  </si>
+  <si>
+    <t>Belum Cair</t>
+  </si>
+  <si>
+    <t>239217</t>
+  </si>
+  <si>
+    <t>061611</t>
+  </si>
+  <si>
+    <t>BANK JABAR BANTEN</t>
+  </si>
+  <si>
+    <t>239218</t>
+  </si>
+  <si>
+    <t>280783</t>
+  </si>
+  <si>
+    <t>072546</t>
+  </si>
+  <si>
+    <t>280851</t>
+  </si>
+  <si>
+    <t>502812</t>
+  </si>
+  <si>
+    <t>067039</t>
+  </si>
+  <si>
+    <t>BANK PANIN</t>
+  </si>
+  <si>
+    <t>517322</t>
+  </si>
+  <si>
+    <t>000956</t>
+  </si>
+  <si>
+    <t>BANK JABAR</t>
+  </si>
+  <si>
+    <t>599487</t>
+  </si>
+  <si>
+    <t>037981</t>
+  </si>
+  <si>
+    <t>599514</t>
+  </si>
+  <si>
+    <t>682094</t>
+  </si>
+  <si>
+    <t>008896</t>
+  </si>
+  <si>
+    <t>BANK OCBC - INDONESIA, PT.</t>
+  </si>
+  <si>
+    <t>174027</t>
+  </si>
+  <si>
+    <t>013993</t>
+  </si>
+  <si>
+    <t>BANK MANDIRI</t>
+  </si>
+  <si>
+    <t>174041</t>
+  </si>
+  <si>
+    <t>313678</t>
+  </si>
+  <si>
+    <t>062992</t>
+  </si>
+  <si>
+    <t>BANK MEGA</t>
+  </si>
+  <si>
+    <t>049231</t>
+  </si>
+  <si>
+    <t>040229</t>
+  </si>
+  <si>
+    <t>139557</t>
+  </si>
+  <si>
+    <t>064529</t>
+  </si>
+  <si>
+    <t>BANK RAKYAT INDONESIA (PERSERO), Tbk.</t>
+  </si>
+  <si>
+    <t>716497</t>
+  </si>
+  <si>
+    <t>067099</t>
+  </si>
+  <si>
+    <t>716634</t>
+  </si>
+  <si>
+    <t>742364</t>
+  </si>
+  <si>
+    <t>058003</t>
+  </si>
+  <si>
+    <t>119899</t>
+  </si>
+  <si>
+    <t>053393</t>
+  </si>
+  <si>
+    <t>BANK DANAMON INDONESIA, PT. Tbk.</t>
+  </si>
+  <si>
+    <t>121636</t>
+  </si>
+  <si>
+    <t>623155</t>
+  </si>
+  <si>
+    <t>053463</t>
+  </si>
+  <si>
+    <t>623247</t>
+  </si>
+  <si>
+    <t>623345</t>
+  </si>
+  <si>
+    <t>623346</t>
+  </si>
+  <si>
+    <t>626356</t>
+  </si>
+  <si>
+    <t>061077</t>
   </si>
   <si>
     <t>BANK CENTRAL ASIA</t>
   </si>
   <si>
-    <t>Belum Cair</t>
-  </si>
-  <si>
-    <t>055333</t>
-  </si>
-  <si>
-    <t>001213</t>
-  </si>
-  <si>
-    <t>106583</t>
-  </si>
-  <si>
-    <t>034412</t>
-  </si>
-  <si>
-    <t>201958</t>
-  </si>
-  <si>
-    <t>072546</t>
-  </si>
-  <si>
-    <t>BNI'46</t>
-  </si>
-  <si>
-    <t>201979</t>
-  </si>
-  <si>
-    <t>017071</t>
-  </si>
-  <si>
-    <t>239217</t>
-  </si>
-  <si>
-    <t>061611</t>
-  </si>
-  <si>
-    <t>BANK JABAR BANTEN</t>
-  </si>
-  <si>
-    <t>239218</t>
-  </si>
-  <si>
-    <t>502618</t>
-  </si>
-  <si>
-    <t>067039</t>
-  </si>
-  <si>
-    <t>BANK PANIN</t>
-  </si>
-  <si>
-    <t>502737</t>
-  </si>
-  <si>
-    <t>037981</t>
-  </si>
-  <si>
-    <t>502744</t>
-  </si>
-  <si>
-    <t>502812</t>
-  </si>
-  <si>
-    <t>829069</t>
-  </si>
-  <si>
-    <t>065300</t>
-  </si>
-  <si>
-    <t>BANK RAKYAT INDONESIA (PERSERO), Tbk.</t>
-  </si>
-  <si>
-    <t>006824</t>
-  </si>
-  <si>
-    <t>014270</t>
-  </si>
-  <si>
-    <t>174004</t>
-  </si>
-  <si>
-    <t>013993</t>
-  </si>
-  <si>
-    <t>BANK MANDIRI</t>
-  </si>
-  <si>
-    <t>174005</t>
-  </si>
-  <si>
-    <t>174006</t>
-  </si>
-  <si>
-    <t>174027</t>
-  </si>
-  <si>
-    <t>147244</t>
-  </si>
-  <si>
-    <t>030419</t>
-  </si>
-  <si>
-    <t>716497</t>
-  </si>
-  <si>
-    <t>067099</t>
-  </si>
-  <si>
-    <t>716634</t>
-  </si>
-  <si>
-    <t>116116</t>
-  </si>
-  <si>
-    <t>053393</t>
-  </si>
-  <si>
-    <t>BANK DANAMON INDONESIA, PT. Tbk.</t>
-  </si>
-  <si>
-    <t>126488</t>
-  </si>
-  <si>
-    <t>053463</t>
-  </si>
-  <si>
-    <t>623154</t>
-  </si>
-  <si>
-    <t>626356</t>
-  </si>
-  <si>
-    <t>061077</t>
-  </si>
-  <si>
     <t>626357</t>
   </si>
   <si>
-    <t>626360</t>
-  </si>
-  <si>
-    <t>725660</t>
+    <t>725260</t>
   </si>
   <si>
     <t>069474</t>
@@ -214,10 +222,16 @@
     <t>BANK HANA</t>
   </si>
   <si>
-    <t>738885</t>
-  </si>
-  <si>
-    <t>BANK OCBC - INDONESIA, PT.</t>
+    <t>738931</t>
+  </si>
+  <si>
+    <t>738939</t>
+  </si>
+  <si>
+    <t>738943</t>
+  </si>
+  <si>
+    <t>738944</t>
   </si>
   <si>
     <t>931669</t>
@@ -229,34 +243,40 @@
     <t>BANK SYARIAH INDONESIA</t>
   </si>
   <si>
-    <t>054420</t>
+    <t>054430</t>
   </si>
   <si>
     <t>012972</t>
   </si>
   <si>
-    <t>054421</t>
-  </si>
-  <si>
     <t>477341</t>
   </si>
   <si>
     <t>018947</t>
   </si>
   <si>
-    <t>816998</t>
-  </si>
-  <si>
-    <t>003239</t>
-  </si>
-  <si>
-    <t>BANK MASPION INDONESIA, PT.</t>
-  </si>
-  <si>
-    <t>973383</t>
-  </si>
-  <si>
-    <t>003236</t>
+    <t>627177</t>
+  </si>
+  <si>
+    <t>037172</t>
+  </si>
+  <si>
+    <t>BPD BALI</t>
+  </si>
+  <si>
+    <t>908165</t>
+  </si>
+  <si>
+    <t>003259</t>
+  </si>
+  <si>
+    <t>908166</t>
+  </si>
+  <si>
+    <t>953958</t>
+  </si>
+  <si>
+    <t>061263</t>
   </si>
   <si>
     <t>033207</t>
@@ -265,42 +285,69 @@
     <t>052835</t>
   </si>
   <si>
-    <t>217599</t>
+    <t>095717</t>
+  </si>
+  <si>
+    <t>042440</t>
+  </si>
+  <si>
+    <t>110220</t>
+  </si>
+  <si>
+    <t>007223</t>
+  </si>
+  <si>
+    <t>265850</t>
+  </si>
+  <si>
+    <t>006612</t>
+  </si>
+  <si>
+    <t>337176</t>
+  </si>
+  <si>
+    <t>071261</t>
+  </si>
+  <si>
+    <t>342307</t>
+  </si>
+  <si>
+    <t>006045</t>
+  </si>
+  <si>
+    <t>BANK PERMATA, PT. Tbk.</t>
+  </si>
+  <si>
+    <t>343629</t>
+  </si>
+  <si>
+    <t>030787</t>
+  </si>
+  <si>
+    <t>343637</t>
+  </si>
+  <si>
+    <t>642892</t>
   </si>
   <si>
     <t>005647</t>
   </si>
   <si>
-    <t>BANK PERMATA, PT. Tbk.</t>
-  </si>
-  <si>
-    <t>343612</t>
-  </si>
-  <si>
-    <t>030787</t>
-  </si>
-  <si>
-    <t>BANK MEGA</t>
-  </si>
-  <si>
-    <t>343623</t>
-  </si>
-  <si>
-    <t>343629</t>
-  </si>
-  <si>
-    <t>673303</t>
-  </si>
-  <si>
-    <t>673308</t>
-  </si>
-  <si>
     <t>673317</t>
   </si>
   <si>
     <t>673322</t>
   </si>
   <si>
+    <t>673366</t>
+  </si>
+  <si>
+    <t>673378</t>
+  </si>
+  <si>
+    <t>673387</t>
+  </si>
+  <si>
     <t>AGC 244752</t>
   </si>
   <si>
@@ -310,88 +357,154 @@
     <t>BANK MAS, PT.</t>
   </si>
   <si>
-    <t>AN673290</t>
-  </si>
-  <si>
-    <t>BAG427068</t>
-  </si>
-  <si>
-    <t>051919</t>
+    <t>BAG427170</t>
+  </si>
+  <si>
+    <t>051913</t>
   </si>
   <si>
     <t>BANK CIMB NIAGA, PT.</t>
   </si>
   <si>
-    <t>BAG427251</t>
-  </si>
-  <si>
-    <t>051913</t>
-  </si>
-  <si>
-    <t>BAG427281</t>
-  </si>
-  <si>
-    <t>BAG427287</t>
-  </si>
-  <si>
-    <t>BAG427300</t>
-  </si>
-  <si>
-    <t>FC098849</t>
+    <t>BAG427194</t>
+  </si>
+  <si>
+    <t>BAG427208</t>
+  </si>
+  <si>
+    <t>BAG427209</t>
+  </si>
+  <si>
+    <t>BR 597555</t>
+  </si>
+  <si>
+    <t>067128</t>
+  </si>
+  <si>
+    <t>FC098862</t>
   </si>
   <si>
     <t>046770</t>
   </si>
   <si>
-    <t>165115</t>
+    <t>FC098872</t>
+  </si>
+  <si>
+    <t>01132846</t>
+  </si>
+  <si>
+    <t>056151</t>
+  </si>
+  <si>
+    <t>BPD JAWA TENGAH</t>
+  </si>
+  <si>
+    <t>013333</t>
+  </si>
+  <si>
+    <t>021608</t>
+  </si>
+  <si>
+    <t>BANK MAYAPADA INTERNATIONAL, PT. Tbk.</t>
+  </si>
+  <si>
+    <t>055546</t>
+  </si>
+  <si>
+    <t>015933</t>
+  </si>
+  <si>
+    <t>BANK MAYBANK INDOCORP, PT.</t>
+  </si>
+  <si>
+    <t>206624</t>
+  </si>
+  <si>
+    <t>066109</t>
+  </si>
+  <si>
+    <t>253742</t>
   </si>
   <si>
     <t>015647</t>
   </si>
   <si>
-    <t>253726</t>
-  </si>
-  <si>
-    <t>EB 997773</t>
+    <t>287259</t>
+  </si>
+  <si>
+    <t>072581</t>
+  </si>
+  <si>
+    <t>959883</t>
+  </si>
+  <si>
+    <t>075056</t>
+  </si>
+  <si>
+    <t>BH 633115</t>
+  </si>
+  <si>
+    <t>008034</t>
+  </si>
+  <si>
+    <t>BR 574665</t>
+  </si>
+  <si>
+    <t>007996</t>
+  </si>
+  <si>
+    <t>EB 998468</t>
   </si>
   <si>
     <t>008107</t>
   </si>
   <si>
-    <t>072086</t>
+    <t>072132</t>
   </si>
   <si>
     <t>063569</t>
   </si>
   <si>
-    <t>072132</t>
-  </si>
-  <si>
-    <t>072136</t>
-  </si>
-  <si>
-    <t>617932</t>
+    <t>072146</t>
+  </si>
+  <si>
+    <t>111920</t>
+  </si>
+  <si>
+    <t>037558</t>
+  </si>
+  <si>
+    <t>398652</t>
+  </si>
+  <si>
+    <t>008575</t>
+  </si>
+  <si>
+    <t>617962</t>
   </si>
   <si>
     <t>023959</t>
   </si>
   <si>
-    <t>050853</t>
+    <t>050828</t>
   </si>
   <si>
     <t>039651</t>
   </si>
   <si>
+    <t>050837</t>
+  </si>
+  <si>
     <t>050865</t>
   </si>
   <si>
-    <t>053377</t>
-  </si>
-  <si>
-    <t>013878</t>
-  </si>
-  <si>
-    <t>274740</t>
+    <t>116902</t>
+  </si>
+  <si>
+    <t>027724</t>
+  </si>
+  <si>
+    <t>274764</t>
   </si>
   <si>
     <t>031594</t>
@@ -400,13 +513,19 @@
     <t>BANK VICTORIA INTERNATIONAL, PT., Tbk.</t>
   </si>
   <si>
-    <t>274745</t>
-  </si>
-  <si>
-    <t>274756</t>
-  </si>
-  <si>
-    <t>274758</t>
+    <t>274765</t>
+  </si>
+  <si>
+    <t>274766</t>
+  </si>
+  <si>
+    <t>274767</t>
+  </si>
+  <si>
+    <t>274768</t>
+  </si>
+  <si>
+    <t>274769</t>
   </si>
   <si>
     <t>638029</t>
@@ -415,7 +534,10 @@
     <t>053347</t>
   </si>
   <si>
-    <t>733962</t>
+    <t>638033</t>
+  </si>
+  <si>
+    <t>733974</t>
   </si>
   <si>
     <t>013839</t>
@@ -424,13 +546,19 @@
     <t>BANK SINAR MAS, PT.</t>
   </si>
   <si>
-    <t>733980</t>
-  </si>
-  <si>
-    <t>039331</t>
-  </si>
-  <si>
-    <t>175381</t>
+    <t>85479182</t>
+  </si>
+  <si>
+    <t>072306</t>
+  </si>
+  <si>
+    <t>018551</t>
+  </si>
+  <si>
+    <t>CIMB NIAGA</t>
+  </si>
+  <si>
+    <t>175416</t>
   </si>
   <si>
     <t>004067</t>
@@ -439,46 +567,58 @@
     <t>BANK WOORI INDONESIA, PT.</t>
   </si>
   <si>
-    <t>175400</t>
-  </si>
-  <si>
-    <t>175416</t>
-  </si>
-  <si>
-    <t>270880</t>
+    <t>175431</t>
+  </si>
+  <si>
+    <t>175446</t>
+  </si>
+  <si>
+    <t>270894</t>
   </si>
   <si>
     <t>029265</t>
   </si>
   <si>
-    <t>270894</t>
-  </si>
-  <si>
-    <t>610920</t>
-  </si>
-  <si>
-    <t>063763</t>
-  </si>
-  <si>
-    <t>705453</t>
+    <t>604900</t>
+  </si>
+  <si>
+    <t>004101</t>
+  </si>
+  <si>
+    <t>705596</t>
+  </si>
+  <si>
+    <t>058132</t>
+  </si>
+  <si>
+    <t>705698</t>
   </si>
   <si>
     <t>018611</t>
   </si>
   <si>
-    <t>705596</t>
-  </si>
-  <si>
-    <t>058132</t>
-  </si>
-  <si>
-    <t>955383</t>
+    <t>958987</t>
+  </si>
+  <si>
+    <t>028340</t>
+  </si>
+  <si>
+    <t>958988</t>
+  </si>
+  <si>
+    <t>962148</t>
   </si>
   <si>
     <t>018727</t>
   </si>
   <si>
-    <t>130752</t>
+    <t>036773</t>
+  </si>
+  <si>
+    <t>019466</t>
+  </si>
+  <si>
+    <t>130862</t>
   </si>
   <si>
     <t>033973</t>
@@ -496,12 +636,21 @@
     <t>023337</t>
   </si>
   <si>
+    <t>244871</t>
+  </si>
+  <si>
+    <t>064511</t>
+  </si>
+  <si>
     <t>272359</t>
   </si>
   <si>
     <t>051856</t>
   </si>
   <si>
+    <t>272375</t>
+  </si>
+  <si>
     <t>280806</t>
   </si>
   <si>
@@ -511,6 +660,12 @@
     <t>280816</t>
   </si>
   <si>
+    <t>280828</t>
+  </si>
+  <si>
+    <t>280840</t>
+  </si>
+  <si>
     <t>381777</t>
   </si>
   <si>
@@ -520,13 +675,25 @@
     <t>381778</t>
   </si>
   <si>
+    <t>381782</t>
+  </si>
+  <si>
+    <t>381783</t>
+  </si>
+  <si>
     <t>441424</t>
   </si>
   <si>
     <t>059142</t>
   </si>
   <si>
-    <t>472876</t>
+    <t>453090</t>
+  </si>
+  <si>
+    <t>019267</t>
+  </si>
+  <si>
+    <t>473119</t>
   </si>
   <si>
     <t>019415</t>
@@ -535,21 +702,51 @@
     <t>PT. BANK MESTIKA DHARMA</t>
   </si>
   <si>
-    <t>494701</t>
+    <t>494713</t>
   </si>
   <si>
     <t>052593</t>
   </si>
   <si>
-    <t>509222</t>
+    <t>496792</t>
+  </si>
+  <si>
+    <t>019742</t>
+  </si>
+  <si>
+    <t>496793</t>
+  </si>
+  <si>
+    <t>062514</t>
+  </si>
+  <si>
+    <t>496794</t>
+  </si>
+  <si>
+    <t>496795</t>
+  </si>
+  <si>
+    <t>496796</t>
+  </si>
+  <si>
+    <t>500402</t>
+  </si>
+  <si>
+    <t>500403</t>
+  </si>
+  <si>
+    <t>508807</t>
+  </si>
+  <si>
+    <t>053773</t>
+  </si>
+  <si>
+    <t>509223</t>
   </si>
   <si>
     <t>019307</t>
   </si>
   <si>
-    <t>509223</t>
-  </si>
-  <si>
     <t>509224</t>
   </si>
   <si>
@@ -568,19 +765,19 @@
     <t>509304</t>
   </si>
   <si>
-    <t>527268</t>
-  </si>
-  <si>
-    <t>019383</t>
-  </si>
-  <si>
-    <t>544679</t>
+    <t>758214</t>
   </si>
   <si>
     <t>039851</t>
   </si>
   <si>
-    <t>803288</t>
+    <t>768039</t>
+  </si>
+  <si>
+    <t>070541</t>
+  </si>
+  <si>
+    <t>803300</t>
   </si>
   <si>
     <t>019416</t>
@@ -589,7 +786,10 @@
     <t>BANK SMBC INDONESIA</t>
   </si>
   <si>
-    <t>934596</t>
+    <t>931502</t>
+  </si>
+  <si>
+    <t>050818</t>
   </si>
   <si>
     <t>015333</t>
@@ -607,13 +807,7 @@
     <t>007777</t>
   </si>
   <si>
-    <t>017991</t>
-  </si>
-  <si>
-    <t>209061</t>
-  </si>
-  <si>
-    <t>056474</t>
+    <t>018444</t>
   </si>
   <si>
     <t>209062</t>
@@ -628,12 +822,6 @@
     <t>534654</t>
   </si>
   <si>
-    <t>534655</t>
-  </si>
-  <si>
-    <t>534690</t>
-  </si>
-  <si>
     <t>534691</t>
   </si>
   <si>
@@ -652,58 +840,67 @@
     <t>008302</t>
   </si>
   <si>
-    <t>BANK MAYAPADA INTERNATIONAL, PT. Tbk.</t>
-  </si>
-  <si>
     <t>005210</t>
   </si>
   <si>
     <t>005214</t>
   </si>
   <si>
-    <t>031181</t>
+    <t>031136</t>
   </si>
   <si>
     <t>063371</t>
   </si>
   <si>
-    <t>484548</t>
+    <t>031143</t>
+  </si>
+  <si>
+    <t>031149</t>
+  </si>
+  <si>
+    <t>343017</t>
+  </si>
+  <si>
+    <t>008536</t>
+  </si>
+  <si>
+    <t>484555</t>
   </si>
   <si>
     <t>039234</t>
   </si>
   <si>
-    <t>484555</t>
-  </si>
-  <si>
-    <t>484569</t>
-  </si>
-  <si>
-    <t>G 031157</t>
-  </si>
-  <si>
-    <t>262369</t>
-  </si>
-  <si>
-    <t>040446</t>
-  </si>
-  <si>
-    <t>932682</t>
-  </si>
-  <si>
-    <t>063928</t>
-  </si>
-  <si>
-    <t>932731</t>
-  </si>
-  <si>
-    <t>059272</t>
-  </si>
-  <si>
-    <t>GHC717656</t>
-  </si>
-  <si>
-    <t>000322</t>
+    <t>484651</t>
+  </si>
+  <si>
+    <t>485265</t>
+  </si>
+  <si>
+    <t>053208</t>
+  </si>
+  <si>
+    <t>BR 370441</t>
+  </si>
+  <si>
+    <t>029855</t>
+  </si>
+  <si>
+    <t>038804</t>
+  </si>
+  <si>
+    <t>012761</t>
+  </si>
+  <si>
+    <t>860908</t>
+  </si>
+  <si>
+    <t>003189</t>
+  </si>
+  <si>
+    <t>940018</t>
+  </si>
+  <si>
+    <t>012677</t>
   </si>
   <si>
     <t>GHC717952</t>
@@ -712,58 +909,52 @@
     <t>051938</t>
   </si>
   <si>
-    <t>DX 387255</t>
-  </si>
-  <si>
-    <t>070054</t>
-  </si>
-  <si>
-    <t>058141</t>
+    <t>GHC718995</t>
+  </si>
+  <si>
+    <t>BT 387990</t>
+  </si>
+  <si>
+    <t>077082</t>
+  </si>
+  <si>
+    <t>083976</t>
+  </si>
+  <si>
+    <t>040518</t>
+  </si>
+  <si>
+    <t>083977</t>
+  </si>
+  <si>
+    <t>224804</t>
   </si>
   <si>
     <t>027321</t>
   </si>
   <si>
-    <t>072947</t>
-  </si>
-  <si>
-    <t>040518</t>
-  </si>
-  <si>
-    <t>077985</t>
-  </si>
-  <si>
-    <t>077986</t>
-  </si>
-  <si>
-    <t>077987</t>
-  </si>
-  <si>
-    <t>346584</t>
+    <t>346600</t>
   </si>
   <si>
     <t>010146</t>
   </si>
   <si>
-    <t>346585</t>
-  </si>
-  <si>
-    <t>346600</t>
-  </si>
-  <si>
-    <t>348397</t>
-  </si>
-  <si>
-    <t>618114</t>
+    <t>399476</t>
+  </si>
+  <si>
+    <t>399477</t>
+  </si>
+  <si>
+    <t>618195</t>
   </si>
   <si>
     <t>010091</t>
   </si>
   <si>
-    <t>618167</t>
-  </si>
-  <si>
-    <t>618195</t>
+    <t>618259</t>
+  </si>
+  <si>
+    <t>618270</t>
   </si>
   <si>
     <t>765513</t>
@@ -775,27 +966,9 @@
     <t>BANK ARTHA GRAHA</t>
   </si>
   <si>
-    <t>765537</t>
-  </si>
-  <si>
     <t>765547</t>
   </si>
   <si>
-    <t>813082</t>
-  </si>
-  <si>
-    <t>057521</t>
-  </si>
-  <si>
-    <t>863674</t>
-  </si>
-  <si>
-    <t>BG 350687</t>
-  </si>
-  <si>
-    <t>017405</t>
-  </si>
-  <si>
     <t>BH 394318</t>
   </si>
   <si>
@@ -808,51 +981,48 @@
     <t>BH 394399</t>
   </si>
   <si>
-    <t>077819</t>
+    <t>BH 394444</t>
+  </si>
+  <si>
+    <t>077840</t>
   </si>
   <si>
     <t>032773</t>
   </si>
   <si>
-    <t>097889</t>
-  </si>
-  <si>
-    <t>065966</t>
-  </si>
-  <si>
-    <t>236191</t>
-  </si>
-  <si>
-    <t>058113</t>
-  </si>
-  <si>
-    <t>562932</t>
+    <t>290843</t>
+  </si>
+  <si>
+    <t>017884</t>
+  </si>
+  <si>
+    <t>315835</t>
+  </si>
+  <si>
+    <t>017793</t>
+  </si>
+  <si>
+    <t>379445</t>
+  </si>
+  <si>
+    <t>066018</t>
+  </si>
+  <si>
+    <t>563007</t>
   </si>
   <si>
     <t>010867</t>
   </si>
   <si>
-    <t>8042577</t>
-  </si>
-  <si>
-    <t>010767</t>
-  </si>
-  <si>
-    <t>111836</t>
+    <t>563008</t>
+  </si>
+  <si>
+    <t>112012</t>
   </si>
   <si>
     <t>011976</t>
   </si>
   <si>
-    <t>111837</t>
-  </si>
-  <si>
-    <t>112012</t>
-  </si>
-  <si>
-    <t>112307</t>
-  </si>
-  <si>
     <t>112308</t>
   </si>
   <si>
@@ -868,25 +1038,40 @@
     <t>112661</t>
   </si>
   <si>
-    <t>152543</t>
-  </si>
-  <si>
-    <t>037861</t>
-  </si>
-  <si>
-    <t>154839</t>
+    <t>112929</t>
+  </si>
+  <si>
+    <t>112930</t>
+  </si>
+  <si>
+    <t>112931</t>
+  </si>
+  <si>
+    <t>113377</t>
+  </si>
+  <si>
+    <t>113378</t>
+  </si>
+  <si>
+    <t>154840</t>
   </si>
   <si>
     <t>038055</t>
   </si>
   <si>
-    <t>154840</t>
-  </si>
-  <si>
-    <t>170763</t>
-  </si>
-  <si>
-    <t>011695</t>
+    <t>188773</t>
+  </si>
+  <si>
+    <t>072047</t>
+  </si>
+  <si>
+    <t>BPD JAWA TIMUR</t>
+  </si>
+  <si>
+    <t>206021</t>
+  </si>
+  <si>
+    <t>066137</t>
   </si>
   <si>
     <t>217780</t>
@@ -901,7 +1086,31 @@
     <t>036724</t>
   </si>
   <si>
-    <t>238680</t>
+    <t>219315</t>
+  </si>
+  <si>
+    <t>22202</t>
+  </si>
+  <si>
+    <t>222023</t>
+  </si>
+  <si>
+    <t>222024</t>
+  </si>
+  <si>
+    <t>225567</t>
+  </si>
+  <si>
+    <t>065920</t>
+  </si>
+  <si>
+    <t>225568</t>
+  </si>
+  <si>
+    <t>225588</t>
+  </si>
+  <si>
+    <t>238673</t>
   </si>
   <si>
     <t>032136</t>
@@ -913,10 +1122,10 @@
     <t>238682</t>
   </si>
   <si>
-    <t>265950</t>
-  </si>
-  <si>
-    <t>076773</t>
+    <t>263253</t>
+  </si>
+  <si>
+    <t>041826</t>
   </si>
   <si>
     <t>266090</t>
@@ -928,91 +1137,34 @@
     <t>266382</t>
   </si>
   <si>
-    <t>272880</t>
-  </si>
-  <si>
-    <t>274741</t>
-  </si>
-  <si>
-    <t>056852</t>
-  </si>
-  <si>
-    <t>283357</t>
+    <t>293026</t>
   </si>
   <si>
     <t>074324</t>
   </si>
   <si>
-    <t>293026</t>
-  </si>
-  <si>
-    <t>58592</t>
-  </si>
-  <si>
-    <t>053677</t>
-  </si>
-  <si>
-    <t>687783</t>
-  </si>
-  <si>
-    <t>066137</t>
-  </si>
-  <si>
-    <t>76128</t>
-  </si>
-  <si>
-    <t>027462</t>
-  </si>
-  <si>
-    <t>76129</t>
-  </si>
-  <si>
-    <t>978931</t>
-  </si>
-  <si>
-    <t>050679</t>
-  </si>
-  <si>
-    <t>998073</t>
-  </si>
-  <si>
-    <t>065920</t>
+    <t>293082</t>
+  </si>
+  <si>
+    <t>63764</t>
+  </si>
+  <si>
+    <t>038284</t>
   </si>
   <si>
     <t>998074</t>
   </si>
   <si>
-    <t>AAP 528997</t>
-  </si>
-  <si>
-    <t>024994</t>
-  </si>
-  <si>
-    <t>EC 277485</t>
-  </si>
-  <si>
-    <t>001851</t>
-  </si>
-  <si>
-    <t>GB 066262</t>
-  </si>
-  <si>
-    <t>027558</t>
-  </si>
-  <si>
-    <t>BANK NATIONAL NOBU PT.</t>
-  </si>
-  <si>
-    <t>GB 892197</t>
-  </si>
-  <si>
-    <t>063878</t>
+    <t>FC 082913</t>
+  </si>
+  <si>
+    <t>047451</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -1292,11 +1444,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F191"/>
+  <dimension ref="A1:F222"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="16.7109375" customWidth="1"/>
@@ -1352,13 +1504,13 @@
         <v>12</v>
       </c>
       <c r="C4" s="5">
-        <v>6640000</v>
+        <v>1828000</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="6">
-        <v>45994</v>
+        <v>46007</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>14</v>
@@ -1372,13 +1524,13 @@
         <v>16</v>
       </c>
       <c r="C5" s="5">
-        <v>2671000</v>
+        <v>21840000</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E5" s="6">
-        <v>45997</v>
+        <v>44296</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>14</v>
@@ -1386,19 +1538,19 @@
     </row>
     <row r="6" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="5">
+        <v>40710000</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="5">
-        <v>30867100</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>13</v>
-      </c>
       <c r="E6" s="6">
-        <v>45999</v>
+        <v>44310</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>14</v>
@@ -1412,13 +1564,13 @@
         <v>20</v>
       </c>
       <c r="C7" s="5">
-        <v>2334000</v>
+        <v>3557000</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E7" s="6">
-        <v>45990</v>
+        <v>46018</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>14</v>
@@ -1426,19 +1578,19 @@
     </row>
     <row r="8" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C8" s="5">
-        <v>1828000</v>
+        <v>1294000</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E8" s="6">
-        <v>46007</v>
+        <v>46011</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>14</v>
@@ -1446,19 +1598,19 @@
     </row>
     <row r="9" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="5">
+        <v>3674800</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="5">
-        <v>21840000</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="E9" s="6">
-        <v>44296</v>
+        <v>46006</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>14</v>
@@ -1466,19 +1618,19 @@
     </row>
     <row r="10" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1899900</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="5">
-        <v>40710000</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="E10" s="6">
-        <v>44310</v>
+        <v>46017</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>14</v>
@@ -1492,13 +1644,13 @@
         <v>29</v>
       </c>
       <c r="C11" s="5">
-        <v>4292300</v>
+        <v>1010700</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E11" s="6">
-        <v>46000</v>
+        <v>46013</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>14</v>
@@ -1506,19 +1658,19 @@
     </row>
     <row r="12" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C12" s="5">
-        <v>1217500</v>
+        <v>2887000</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E12" s="6">
-        <v>45994</v>
+        <v>46023</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>14</v>
@@ -1526,19 +1678,19 @@
     </row>
     <row r="13" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C13" s="5">
-        <v>7766500</v>
+        <v>6690093</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E13" s="6">
-        <v>46000</v>
+        <v>46006</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>14</v>
@@ -1549,16 +1701,16 @@
         <v>34</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C14" s="5">
-        <v>3674800</v>
+        <v>23677000</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E14" s="6">
-        <v>46006</v>
+        <v>46020</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>14</v>
@@ -1566,19 +1718,19 @@
     </row>
     <row r="15" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5">
+        <v>13454000</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="5">
-        <v>6840000</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>37</v>
-      </c>
       <c r="E15" s="6">
-        <v>45996</v>
+        <v>46009</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>14</v>
@@ -1592,13 +1744,13 @@
         <v>39</v>
       </c>
       <c r="C16" s="5">
-        <v>42232000</v>
+        <v>11200000</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E16" s="6">
-        <v>46002</v>
+        <v>46009</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>14</v>
@@ -1606,19 +1758,19 @@
     </row>
     <row r="17" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C17" s="5">
-        <v>12500000</v>
+        <v>5265373</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E17" s="6">
-        <v>46006</v>
+        <v>46003</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>14</v>
@@ -1629,16 +1781,16 @@
         <v>43</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C18" s="5">
-        <v>12500000</v>
+        <v>7727995</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E18" s="6">
-        <v>46010</v>
+        <v>46004</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>14</v>
@@ -1646,19 +1798,19 @@
     </row>
     <row r="19" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C19" s="5">
-        <v>12072000</v>
+        <v>285519683</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E19" s="6">
-        <v>46001</v>
+        <v>45384</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>14</v>
@@ -1666,19 +1818,19 @@
     </row>
     <row r="20" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="5">
+        <v>255499245</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="5">
-        <v>23677000</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>42</v>
-      </c>
       <c r="E20" s="6">
-        <v>46020</v>
+        <v>45407</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>14</v>
@@ -1686,19 +1838,19 @@
     </row>
     <row r="21" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C21" s="5">
-        <v>2097900</v>
+        <v>1009991</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E21" s="6">
-        <v>45987</v>
+        <v>46003</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>14</v>
@@ -1706,19 +1858,19 @@
     </row>
     <row r="22" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C22" s="5">
-        <v>285519683</v>
+        <v>9230000</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E22" s="6">
-        <v>45384</v>
+        <v>46009</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>14</v>
@@ -1726,19 +1878,19 @@
     </row>
     <row r="23" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C23" s="5">
-        <v>255499245</v>
+        <v>12309000</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E23" s="6">
-        <v>45407</v>
+        <v>46010</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>14</v>
@@ -1746,19 +1898,19 @@
     </row>
     <row r="24" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C24" s="5">
-        <v>23751000</v>
+        <v>55265000</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="E24" s="6">
-        <v>46001</v>
+        <v>46004</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>14</v>
@@ -1766,19 +1918,19 @@
     </row>
     <row r="25" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C25" s="5">
-        <v>34537000</v>
+        <v>63187000</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E25" s="6">
-        <v>45996</v>
+        <v>46008</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>14</v>
@@ -1786,19 +1938,19 @@
     </row>
     <row r="26" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>55</v>
-      </c>
       <c r="C26" s="5">
-        <v>7439000</v>
+        <v>14350000</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E26" s="6">
-        <v>46002</v>
+        <v>46004</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>14</v>
@@ -1806,19 +1958,19 @@
     </row>
     <row r="27" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C27" s="5">
-        <v>142239415</v>
+        <v>68095000</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E27" s="6">
-        <v>46007</v>
+        <v>46015</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>14</v>
@@ -1826,19 +1978,19 @@
     </row>
     <row r="28" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C28" s="5">
-        <v>122652975</v>
+        <v>142239415</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="E28" s="6">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>14</v>
@@ -1846,19 +1998,19 @@
     </row>
     <row r="29" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C29" s="5">
-        <v>98921048</v>
+        <v>122652975</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="E29" s="6">
-        <v>46000</v>
+        <v>46009</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>14</v>
@@ -1866,19 +2018,19 @@
     </row>
     <row r="30" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C30" s="5">
-        <v>74057900</v>
+        <v>73467800</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E30" s="6">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>14</v>
@@ -1886,19 +2038,19 @@
     </row>
     <row r="31" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C31" s="5">
-        <v>31238700</v>
+        <v>26111600</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="E31" s="6">
-        <v>45996</v>
+        <v>46013</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>14</v>
@@ -1906,19 +2058,19 @@
     </row>
     <row r="32" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C32" s="5">
-        <v>150000000</v>
+        <v>14513600</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="E32" s="6">
-        <v>45222</v>
+        <v>46015</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>14</v>
@@ -1929,16 +2081,16 @@
         <v>69</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C33" s="5">
-        <v>36786900</v>
+        <v>45690200</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E33" s="6">
-        <v>45979</v>
+        <v>46021</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>14</v>
@@ -1946,19 +2098,19 @@
     </row>
     <row r="34" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C34" s="5">
-        <v>15432600</v>
+        <v>44674400</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E34" s="6">
-        <v>45989</v>
+        <v>46017</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>14</v>
@@ -1966,19 +2118,19 @@
     </row>
     <row r="35" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="C35" s="5">
+        <v>150000000</v>
+      </c>
+      <c r="D35" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C35" s="5">
-        <v>5151500</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>42</v>
-      </c>
       <c r="E35" s="6">
-        <v>46014</v>
+        <v>45222</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>14</v>
@@ -1992,13 +2144,13 @@
         <v>75</v>
       </c>
       <c r="C36" s="5">
-        <v>5290000</v>
+        <v>13760700</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="E36" s="6">
-        <v>45993</v>
+        <v>46008</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>14</v>
@@ -2006,19 +2158,19 @@
     </row>
     <row r="37" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>78</v>
-      </c>
       <c r="C37" s="5">
-        <v>12030000</v>
+        <v>5151500</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E37" s="6">
-        <v>45993</v>
+        <v>46014</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>14</v>
@@ -2026,19 +2178,19 @@
     </row>
     <row r="38" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="C38" s="5">
+        <v>2444197</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C38" s="5">
-        <v>1598400</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>42</v>
-      </c>
       <c r="E38" s="6">
-        <v>46015</v>
+        <v>45999</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>14</v>
@@ -2052,13 +2204,13 @@
         <v>82</v>
       </c>
       <c r="C39" s="5">
-        <v>14378700</v>
+        <v>7820100</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="E39" s="6">
-        <v>46001</v>
+        <v>46011</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>14</v>
@@ -2066,19 +2218,19 @@
     </row>
     <row r="40" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C40" s="5">
-        <v>1100000</v>
+        <v>10417600</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="E40" s="6">
-        <v>45995</v>
+        <v>46016</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>14</v>
@@ -2086,19 +2238,19 @@
     </row>
     <row r="41" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>85</v>
       </c>
       <c r="C41" s="5">
-        <v>1600000</v>
+        <v>89148500</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E41" s="6">
-        <v>46000</v>
+        <v>46006</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>14</v>
@@ -2106,19 +2258,19 @@
     </row>
     <row r="42" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C42" s="5">
-        <v>1300000</v>
+        <v>1598400</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="E42" s="6">
-        <v>46017</v>
+        <v>46015</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>14</v>
@@ -2126,19 +2278,19 @@
     </row>
     <row r="43" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>80</v>
-      </c>
       <c r="C43" s="5">
-        <v>17062464</v>
+        <v>6192400</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E43" s="6">
-        <v>45997</v>
+        <v>46003</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>14</v>
@@ -2149,16 +2301,16 @@
         <v>90</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C44" s="5">
-        <v>1110000</v>
+        <v>3779500</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="E44" s="6">
-        <v>46001</v>
+        <v>46004</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>14</v>
@@ -2166,19 +2318,19 @@
     </row>
     <row r="45" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C45" s="5">
-        <v>836940</v>
+        <v>5050141</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="E45" s="6">
-        <v>46003</v>
+        <v>46004</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>14</v>
@@ -2186,19 +2338,19 @@
     </row>
     <row r="46" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C46" s="5">
-        <v>1831500</v>
+        <v>7492000</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="E46" s="6">
-        <v>46013</v>
+        <v>46016</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>14</v>
@@ -2206,19 +2358,19 @@
     </row>
     <row r="47" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C47" s="5">
-        <v>18926000</v>
+        <v>1004550</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E47" s="6">
-        <v>45826</v>
+        <v>46020</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>14</v>
@@ -2226,19 +2378,19 @@
     </row>
     <row r="48" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C48" s="5">
-        <v>1148850</v>
+        <v>1300000</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E48" s="6">
-        <v>45991</v>
+        <v>46017</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>14</v>
@@ -2246,19 +2398,19 @@
     </row>
     <row r="49" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C49" s="5">
-        <v>5121500</v>
+        <v>2200000</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="E49" s="6">
-        <v>45992</v>
+        <v>46032</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>14</v>
@@ -2266,19 +2418,19 @@
     </row>
     <row r="50" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C50" s="5">
-        <v>1298700</v>
+        <v>20525300</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E50" s="6">
-        <v>45995</v>
+        <v>46015</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>14</v>
@@ -2286,19 +2438,19 @@
     </row>
     <row r="51" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C51" s="5">
-        <v>582750</v>
+        <v>836940</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="E51" s="6">
-        <v>45994</v>
+        <v>46003</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>14</v>
@@ -2306,19 +2458,19 @@
     </row>
     <row r="52" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C52" s="5">
-        <v>1781550</v>
+        <v>1831500</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="E52" s="6">
-        <v>45993</v>
+        <v>46013</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>14</v>
@@ -2326,19 +2478,19 @@
     </row>
     <row r="53" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C53" s="5">
-        <v>1798200</v>
+        <v>6646115</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="E53" s="6">
-        <v>45997</v>
+        <v>46024</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>14</v>
@@ -2346,19 +2498,19 @@
     </row>
     <row r="54" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="C54" s="5">
-        <v>22176434</v>
+        <v>8258400</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E54" s="6">
-        <v>46000</v>
+        <v>46030</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>14</v>
@@ -2366,19 +2518,19 @@
     </row>
     <row r="55" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="C55" s="5">
-        <v>1831500</v>
+        <v>2477520</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E55" s="6">
-        <v>45994</v>
+        <v>46033</v>
       </c>
       <c r="F55" s="5" t="s">
         <v>14</v>
@@ -2389,16 +2541,16 @@
         <v>109</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C56" s="5">
-        <v>999000</v>
+        <v>18926000</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="E56" s="6">
-        <v>46000</v>
+        <v>45826</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>14</v>
@@ -2406,19 +2558,19 @@
     </row>
     <row r="57" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C57" s="5">
-        <v>138945800</v>
+        <v>1569540</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E57" s="6">
-        <v>45996</v>
+        <v>46004</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>14</v>
@@ -2426,19 +2578,19 @@
     </row>
     <row r="58" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>113</v>
       </c>
       <c r="C58" s="5">
-        <v>8370607</v>
+        <v>1568430</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="E58" s="6">
-        <v>45996</v>
+        <v>46007</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>14</v>
@@ -2446,19 +2598,19 @@
     </row>
     <row r="59" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>113</v>
       </c>
       <c r="C59" s="5">
-        <v>17629073</v>
+        <v>5557458</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="E59" s="6">
-        <v>46006</v>
+        <v>46013</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>14</v>
@@ -2466,19 +2618,19 @@
     </row>
     <row r="60" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>113</v>
       </c>
       <c r="C60" s="5">
-        <v>42084540</v>
+        <v>1576200</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="E60" s="6">
-        <v>46002</v>
+        <v>46010</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>14</v>
@@ -2486,19 +2638,19 @@
     </row>
     <row r="61" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C61" s="5">
-        <v>3866932</v>
+        <v>17472787</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="E61" s="6">
-        <v>45993</v>
+        <v>46003</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>14</v>
@@ -2506,19 +2658,19 @@
     </row>
     <row r="62" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C62" s="5">
-        <v>5180569</v>
+        <v>10488755</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E62" s="6">
-        <v>45995</v>
+        <v>46009</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>14</v>
@@ -2526,19 +2678,19 @@
     </row>
     <row r="63" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C63" s="5">
-        <v>68413737</v>
+        <v>10186969</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E63" s="6">
-        <v>46006</v>
+        <v>46014</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>14</v>
@@ -2546,19 +2698,19 @@
     </row>
     <row r="64" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C64" s="5">
-        <v>6200000</v>
+        <v>22945392</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>53</v>
+        <v>125</v>
       </c>
       <c r="E64" s="6">
-        <v>45990</v>
+        <v>46000</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>14</v>
@@ -2566,19 +2718,19 @@
     </row>
     <row r="65" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C65" s="5">
-        <v>3181300</v>
+        <v>14043400</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E65" s="6">
-        <v>45999</v>
+        <v>46006</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>14</v>
@@ -2586,19 +2738,19 @@
     </row>
     <row r="66" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C66" s="5">
-        <v>3181300</v>
+        <v>38073821</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E66" s="6">
-        <v>45994</v>
+        <v>46006</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>14</v>
@@ -2606,19 +2758,19 @@
     </row>
     <row r="67" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="C67" s="5">
-        <v>3115215</v>
+        <v>42150082</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="E67" s="6">
-        <v>45993</v>
+        <v>46011</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>14</v>
@@ -2626,19 +2778,19 @@
     </row>
     <row r="68" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="C68" s="5">
-        <v>1143300</v>
+        <v>1998000</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="E68" s="6">
-        <v>45996</v>
+        <v>46009</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>14</v>
@@ -2646,19 +2798,19 @@
     </row>
     <row r="69" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="C69" s="5">
-        <v>18502159</v>
+        <v>10334400</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="E69" s="6">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>14</v>
@@ -2666,19 +2818,19 @@
     </row>
     <row r="70" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C70" s="5">
-        <v>3539000</v>
+        <v>4555440</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>133</v>
+        <v>36</v>
       </c>
       <c r="E70" s="6">
-        <v>45979</v>
+        <v>46003</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>14</v>
@@ -2686,19 +2838,19 @@
     </row>
     <row r="71" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C71" s="5">
-        <v>7490260</v>
+        <v>1443987</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>133</v>
+        <v>24</v>
       </c>
       <c r="E71" s="6">
-        <v>45996</v>
+        <v>46009</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>14</v>
@@ -2706,19 +2858,19 @@
     </row>
     <row r="72" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C72" s="5">
-        <v>22012300</v>
+        <v>5672100</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>138</v>
+        <v>13</v>
       </c>
       <c r="E72" s="6">
-        <v>45992</v>
+        <v>46002</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>14</v>
@@ -2726,19 +2878,19 @@
     </row>
     <row r="73" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C73" s="5">
-        <v>16547600</v>
+        <v>31409800</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>138</v>
+        <v>62</v>
       </c>
       <c r="E73" s="6">
-        <v>45997</v>
+        <v>46008</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>14</v>
@@ -2746,19 +2898,19 @@
     </row>
     <row r="74" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C74" s="5">
-        <v>18511500</v>
+        <v>17629073</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>138</v>
+        <v>53</v>
       </c>
       <c r="E74" s="6">
-        <v>46004</v>
+        <v>46006</v>
       </c>
       <c r="F74" s="5" t="s">
         <v>14</v>
@@ -2766,19 +2918,19 @@
     </row>
     <row r="75" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C75" s="5">
-        <v>20091000</v>
+        <v>56217539</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="E75" s="6">
-        <v>46001</v>
+        <v>46013</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>14</v>
@@ -2786,19 +2938,19 @@
     </row>
     <row r="76" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="C76" s="5">
-        <v>15591000</v>
+        <v>30165713</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E76" s="6">
-        <v>46009</v>
+        <v>46003</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>14</v>
@@ -2806,19 +2958,19 @@
     </row>
     <row r="77" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C77" s="5">
-        <v>59272200</v>
+        <v>16182000</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E77" s="6">
-        <v>46000</v>
+        <v>46004</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>14</v>
@@ -2826,19 +2978,19 @@
     </row>
     <row r="78" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C78" s="5">
-        <v>43448000</v>
+        <v>2416742</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E78" s="6">
-        <v>45993</v>
+        <v>46007</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>14</v>
@@ -2846,19 +2998,19 @@
     </row>
     <row r="79" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C79" s="5">
-        <v>48291300</v>
+        <v>6237756</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="E79" s="6">
-        <v>46009</v>
+        <v>46020</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>14</v>
@@ -2866,19 +3018,19 @@
     </row>
     <row r="80" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C80" s="5">
-        <v>34893000</v>
+        <v>632700</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="E80" s="6">
-        <v>45996</v>
+        <v>46021</v>
       </c>
       <c r="F80" s="5" t="s">
         <v>14</v>
@@ -2886,19 +3038,19 @@
     </row>
     <row r="81" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C81" s="5">
-        <v>15086000</v>
+        <v>68413737</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="E81" s="6">
-        <v>45997</v>
+        <v>46006</v>
       </c>
       <c r="F81" s="5" t="s">
         <v>14</v>
@@ -2906,19 +3058,19 @@
     </row>
     <row r="82" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C82" s="5">
-        <v>19505000</v>
+        <v>5673210</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E82" s="6">
-        <v>46022</v>
+        <v>46017</v>
       </c>
       <c r="F82" s="5" t="s">
         <v>14</v>
@@ -2926,19 +3078,19 @@
     </row>
     <row r="83" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C83" s="5">
-        <v>7795000</v>
+        <v>6401600</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>42</v>
+        <v>163</v>
       </c>
       <c r="E83" s="6">
-        <v>46005</v>
+        <v>46007</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>14</v>
@@ -2946,19 +3098,19 @@
     </row>
     <row r="84" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C84" s="5">
-        <v>23160869</v>
+        <v>7244500</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
       <c r="E84" s="6">
-        <v>46015</v>
+        <v>46009</v>
       </c>
       <c r="F84" s="5" t="s">
         <v>14</v>
@@ -2966,19 +3118,19 @@
     </row>
     <row r="85" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C85" s="5">
-        <v>109871000</v>
+        <v>6864800</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>37</v>
+        <v>163</v>
       </c>
       <c r="E85" s="6">
-        <v>46014</v>
+        <v>46010</v>
       </c>
       <c r="F85" s="5" t="s">
         <v>14</v>
@@ -2986,19 +3138,19 @@
     </row>
     <row r="86" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B86" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B86" s="5" t="s">
-        <v>161</v>
-      </c>
       <c r="C86" s="5">
-        <v>60913000</v>
+        <v>8045300</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>37</v>
+        <v>163</v>
       </c>
       <c r="E86" s="6">
-        <v>46017</v>
+        <v>46011</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>14</v>
@@ -3006,19 +3158,19 @@
     </row>
     <row r="87" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C87" s="5">
+        <v>8045300</v>
+      </c>
+      <c r="D87" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="B87" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="C87" s="5">
-        <v>10399000</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>13</v>
-      </c>
       <c r="E87" s="6">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>14</v>
@@ -3026,19 +3178,19 @@
     </row>
     <row r="88" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C88" s="5">
-        <v>7839000</v>
+        <v>8045300</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
       <c r="E88" s="6">
-        <v>46015</v>
+        <v>46016</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>14</v>
@@ -3046,19 +3198,19 @@
     </row>
     <row r="89" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C89" s="5">
-        <v>3653800</v>
+        <v>18502159</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E89" s="6">
-        <v>46026</v>
+        <v>46008</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>14</v>
@@ -3066,19 +3218,19 @@
     </row>
     <row r="90" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C90" s="5">
-        <v>39757000</v>
+        <v>85479182</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>170</v>
+        <v>13</v>
       </c>
       <c r="E90" s="6">
-        <v>45994</v>
+        <v>46063</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>14</v>
@@ -3086,19 +3238,19 @@
     </row>
     <row r="91" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C91" s="5">
-        <v>8268100</v>
+        <v>4100000</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>42</v>
+        <v>174</v>
       </c>
       <c r="E91" s="6">
-        <v>45988</v>
+        <v>46011</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>14</v>
@@ -3106,19 +3258,19 @@
     </row>
     <row r="92" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C92" s="5">
-        <v>9996000</v>
+        <v>85479182</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>170</v>
+        <v>13</v>
       </c>
       <c r="E92" s="6">
-        <v>45994</v>
+        <v>46077</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>14</v>
@@ -3126,19 +3278,19 @@
     </row>
     <row r="93" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C93" s="5">
-        <v>34215750</v>
+        <v>11509000</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="E93" s="6">
-        <v>46013</v>
+        <v>46008</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>14</v>
@@ -3146,19 +3298,19 @@
     </row>
     <row r="94" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C94" s="5">
-        <v>27139500</v>
+        <v>18511500</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="E94" s="6">
-        <v>46009</v>
+        <v>46004</v>
       </c>
       <c r="F94" s="5" t="s">
         <v>14</v>
@@ -3166,19 +3318,19 @@
     </row>
     <row r="95" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C95" s="5">
-        <v>20646000</v>
+        <v>20360500</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="E95" s="6">
-        <v>46008</v>
+        <v>46011</v>
       </c>
       <c r="F95" s="5" t="s">
         <v>14</v>
@@ -3186,19 +3338,19 @@
     </row>
     <row r="96" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C96" s="5">
-        <v>19980000</v>
+        <v>25459900</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>170</v>
+        <v>62</v>
       </c>
       <c r="E96" s="6">
-        <v>46010</v>
+        <v>46018</v>
       </c>
       <c r="F96" s="5" t="s">
         <v>14</v>
@@ -3206,19 +3358,19 @@
     </row>
     <row r="97" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="C97" s="5">
-        <v>19980000</v>
+        <v>15591000</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>170</v>
+        <v>62</v>
       </c>
       <c r="E97" s="6">
-        <v>46017</v>
+        <v>46009</v>
       </c>
       <c r="F97" s="5" t="s">
         <v>14</v>
@@ -3226,19 +3378,19 @@
     </row>
     <row r="98" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="C98" s="5">
-        <v>19980000</v>
+        <v>22733000</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>170</v>
+        <v>62</v>
       </c>
       <c r="E98" s="6">
-        <v>46014</v>
+        <v>46018</v>
       </c>
       <c r="F98" s="5" t="s">
         <v>14</v>
@@ -3246,19 +3398,19 @@
     </row>
     <row r="99" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="C99" s="5">
-        <v>19547100</v>
+        <v>48291300</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>170</v>
+        <v>62</v>
       </c>
       <c r="E99" s="6">
-        <v>46015</v>
+        <v>46009</v>
       </c>
       <c r="F99" s="5" t="s">
         <v>14</v>
@@ -3266,19 +3418,19 @@
     </row>
     <row r="100" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C100" s="5">
-        <v>31087000</v>
+        <v>32761000</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="E100" s="6">
-        <v>45990</v>
+        <v>46004</v>
       </c>
       <c r="F100" s="5" t="s">
         <v>14</v>
@@ -3286,19 +3438,19 @@
     </row>
     <row r="101" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C101" s="5">
-        <v>113935950</v>
+        <v>54050300</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="E101" s="6">
-        <v>46000</v>
+        <v>46006</v>
       </c>
       <c r="F101" s="5" t="s">
         <v>14</v>
@@ -3306,19 +3458,19 @@
     </row>
     <row r="102" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C102" s="5">
-        <v>11151878</v>
+        <v>18528700</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>188</v>
+        <v>62</v>
       </c>
       <c r="E102" s="6">
-        <v>45989</v>
+        <v>46012</v>
       </c>
       <c r="F102" s="5" t="s">
         <v>14</v>
@@ -3326,19 +3478,19 @@
     </row>
     <row r="103" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="C103" s="5">
-        <v>9632000</v>
+        <v>63849000</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="E103" s="6">
-        <v>46001</v>
+        <v>46015</v>
       </c>
       <c r="F103" s="5" t="s">
         <v>14</v>
@@ -3346,19 +3498,19 @@
     </row>
     <row r="104" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C104" s="5">
-        <v>5497495</v>
+        <v>8800000</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>192</v>
+        <v>131</v>
       </c>
       <c r="E104" s="6">
-        <v>46013</v>
+        <v>46011</v>
       </c>
       <c r="F104" s="5" t="s">
         <v>14</v>
@@ -3366,19 +3518,19 @@
     </row>
     <row r="105" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C105" s="5">
-        <v>2582415</v>
+        <v>36010000</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>192</v>
+        <v>13</v>
       </c>
       <c r="E105" s="6">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="F105" s="5" t="s">
         <v>14</v>
@@ -3386,19 +3538,19 @@
     </row>
     <row r="106" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="C106" s="5">
-        <v>771450</v>
+        <v>19505000</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="E106" s="6">
-        <v>46002</v>
+        <v>46022</v>
       </c>
       <c r="F106" s="5" t="s">
         <v>14</v>
@@ -3406,19 +3558,19 @@
     </row>
     <row r="107" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C107" s="5">
-        <v>7448500</v>
+        <v>7795000</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E107" s="6">
-        <v>46002</v>
+        <v>46005</v>
       </c>
       <c r="F107" s="5" t="s">
         <v>14</v>
@@ -3426,19 +3578,19 @@
     </row>
     <row r="108" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C108" s="5">
-        <v>3714600</v>
+        <v>52700000</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="E108" s="6">
-        <v>46026</v>
+        <v>46011</v>
       </c>
       <c r="F108" s="5" t="s">
         <v>14</v>
@@ -3446,19 +3598,19 @@
     </row>
     <row r="109" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="C109" s="5">
-        <v>7732800</v>
+        <v>23160869</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="E109" s="6">
-        <v>46041</v>
+        <v>46015</v>
       </c>
       <c r="F109" s="5" t="s">
         <v>14</v>
@@ -3466,19 +3618,19 @@
     </row>
     <row r="110" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="C110" s="5">
-        <v>17489300</v>
+        <v>51121301</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="E110" s="6">
-        <v>46008</v>
+        <v>46043</v>
       </c>
       <c r="F110" s="5" t="s">
         <v>14</v>
@@ -3486,19 +3638,19 @@
     </row>
     <row r="111" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="C111" s="5">
-        <v>40181000</v>
+        <v>109871000</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E111" s="6">
-        <v>45998</v>
+        <v>46014</v>
       </c>
       <c r="F111" s="5" t="s">
         <v>14</v>
@@ -3506,19 +3658,19 @@
     </row>
     <row r="112" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="C112" s="5">
-        <v>1122300</v>
+        <v>60913000</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E112" s="6">
-        <v>46000</v>
+        <v>46017</v>
       </c>
       <c r="F112" s="5" t="s">
         <v>14</v>
@@ -3526,19 +3678,19 @@
     </row>
     <row r="113" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="C113" s="5">
-        <v>41306100</v>
+        <v>144775000</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E113" s="6">
-        <v>46006</v>
+        <v>46028</v>
       </c>
       <c r="F113" s="5" t="s">
         <v>14</v>
@@ -3546,19 +3698,19 @@
     </row>
     <row r="114" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="C114" s="5">
-        <v>27795200</v>
+        <v>41630000</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E114" s="6">
-        <v>46021</v>
+        <v>46042</v>
       </c>
       <c r="F114" s="5" t="s">
         <v>14</v>
@@ -3566,19 +3718,19 @@
     </row>
     <row r="115" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="C115" s="5">
-        <v>54567000</v>
+        <v>10399000</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="E115" s="6">
-        <v>46012</v>
+        <v>46008</v>
       </c>
       <c r="F115" s="5" t="s">
         <v>14</v>
@@ -3586,19 +3738,19 @@
     </row>
     <row r="116" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="C116" s="5">
-        <v>1359900</v>
+        <v>7839000</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="E116" s="6">
-        <v>46025</v>
+        <v>46015</v>
       </c>
       <c r="F116" s="5" t="s">
         <v>14</v>
@@ -3606,19 +3758,19 @@
     </row>
     <row r="117" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C117" s="5">
-        <v>13990000</v>
+        <v>3051000</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>210</v>
+        <v>62</v>
       </c>
       <c r="E117" s="6">
-        <v>46007</v>
+        <v>46022</v>
       </c>
       <c r="F117" s="5" t="s">
         <v>14</v>
@@ -3626,19 +3778,19 @@
     </row>
     <row r="118" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C118" s="5">
-        <v>11190000</v>
+        <v>4080000</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>210</v>
+        <v>62</v>
       </c>
       <c r="E118" s="6">
-        <v>46011</v>
+        <v>46039</v>
       </c>
       <c r="F118" s="5" t="s">
         <v>14</v>
@@ -3646,19 +3798,19 @@
     </row>
     <row r="119" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="C119" s="5">
-        <v>190353643</v>
+        <v>3653800</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>210</v>
+        <v>13</v>
       </c>
       <c r="E119" s="6">
-        <v>46047</v>
+        <v>46026</v>
       </c>
       <c r="F119" s="5" t="s">
         <v>14</v>
@@ -3666,19 +3818,19 @@
     </row>
     <row r="120" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="C120" s="5">
-        <v>45771500</v>
+        <v>38000000</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="E120" s="6">
-        <v>45996</v>
+        <v>46013</v>
       </c>
       <c r="F120" s="5" t="s">
         <v>14</v>
@@ -3686,19 +3838,19 @@
     </row>
     <row r="121" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="C121" s="5">
-        <v>1471000</v>
+        <v>17897000</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>30</v>
+        <v>226</v>
       </c>
       <c r="E121" s="6">
-        <v>45994</v>
+        <v>46027</v>
       </c>
       <c r="F121" s="5" t="s">
         <v>14</v>
@@ -3706,19 +3858,19 @@
     </row>
     <row r="122" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C122" s="5">
-        <v>835000</v>
+        <v>8495400</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E122" s="6">
-        <v>46004</v>
+        <v>46006</v>
       </c>
       <c r="F122" s="5" t="s">
         <v>14</v>
@@ -3726,19 +3878,19 @@
     </row>
     <row r="123" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="C123" s="5">
-        <v>1176000</v>
+        <v>63742000</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>30</v>
+        <v>226</v>
       </c>
       <c r="E123" s="6">
-        <v>46003</v>
+        <v>46004</v>
       </c>
       <c r="F123" s="5" t="s">
         <v>14</v>
@@ -3746,19 +3898,19 @@
     </row>
     <row r="124" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="C124" s="5">
-        <v>246383600</v>
+        <v>63742000</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>53</v>
+        <v>226</v>
       </c>
       <c r="E124" s="6">
-        <v>46003</v>
+        <v>46011</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>14</v>
@@ -3766,19 +3918,19 @@
     </row>
     <row r="125" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A125" s="5" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="C125" s="5">
-        <v>18181000</v>
+        <v>63742000</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>68</v>
+        <v>226</v>
       </c>
       <c r="E125" s="6">
-        <v>46002</v>
+        <v>46015</v>
       </c>
       <c r="F125" s="5" t="s">
         <v>14</v>
@@ -3786,19 +3938,19 @@
     </row>
     <row r="126" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C126" s="5">
-        <v>4195800</v>
+        <v>63742000</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="E126" s="6">
-        <v>45993</v>
+        <v>46018</v>
       </c>
       <c r="F126" s="5" t="s">
         <v>14</v>
@@ -3806,19 +3958,19 @@
     </row>
     <row r="127" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C127" s="5">
-        <v>3624308</v>
+        <v>63742000</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>21</v>
+        <v>226</v>
       </c>
       <c r="E127" s="6">
-        <v>45993</v>
+        <v>46025</v>
       </c>
       <c r="F127" s="5" t="s">
         <v>14</v>
@@ -3826,19 +3978,19 @@
     </row>
     <row r="128" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C128" s="5">
+        <v>42205000</v>
+      </c>
+      <c r="D128" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="B128" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="C128" s="5">
-        <v>12788410</v>
-      </c>
-      <c r="D128" s="5" t="s">
-        <v>37</v>
-      </c>
       <c r="E128" s="6">
-        <v>45991</v>
+        <v>46014</v>
       </c>
       <c r="F128" s="5" t="s">
         <v>14</v>
@@ -3846,19 +3998,19 @@
     </row>
     <row r="129" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C129" s="5">
-        <v>14962170</v>
+        <v>41068000</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>37</v>
+        <v>226</v>
       </c>
       <c r="E129" s="6">
-        <v>46011</v>
+        <v>46022</v>
       </c>
       <c r="F129" s="5" t="s">
         <v>14</v>
@@ -3866,19 +4018,19 @@
     </row>
     <row r="130" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C130" s="5">
-        <v>41692951</v>
+        <v>15466700</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E130" s="6">
-        <v>45996</v>
+        <v>46002</v>
       </c>
       <c r="F130" s="5" t="s">
         <v>14</v>
@@ -3886,19 +4038,19 @@
     </row>
     <row r="131" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C131" s="5">
-        <v>18983775</v>
+        <v>34215750</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>42</v>
+        <v>226</v>
       </c>
       <c r="E131" s="6">
-        <v>45994</v>
+        <v>46013</v>
       </c>
       <c r="F131" s="5" t="s">
         <v>14</v>
@@ -3906,19 +4058,19 @@
     </row>
     <row r="132" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C132" s="5">
-        <v>5818600</v>
+        <v>27139500</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>53</v>
+        <v>226</v>
       </c>
       <c r="E132" s="6">
-        <v>45997</v>
+        <v>46009</v>
       </c>
       <c r="F132" s="5" t="s">
         <v>14</v>
@@ -3926,19 +4078,19 @@
     </row>
     <row r="133" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A133" s="5" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C133" s="5">
-        <v>3968200</v>
+        <v>20646000</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>53</v>
+        <v>226</v>
       </c>
       <c r="E133" s="6">
-        <v>46001</v>
+        <v>46008</v>
       </c>
       <c r="F133" s="5" t="s">
         <v>14</v>
@@ -3946,19 +4098,19 @@
     </row>
     <row r="134" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A134" s="5" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C134" s="5">
-        <v>391900</v>
+        <v>19980000</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>53</v>
+        <v>226</v>
       </c>
       <c r="E134" s="6">
-        <v>46002</v>
+        <v>46010</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>14</v>
@@ -3966,19 +4118,19 @@
     </row>
     <row r="135" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A135" s="5" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C135" s="5">
-        <v>2418100</v>
+        <v>19980000</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>53</v>
+        <v>226</v>
       </c>
       <c r="E135" s="6">
-        <v>46003</v>
+        <v>46017</v>
       </c>
       <c r="F135" s="5" t="s">
         <v>14</v>
@@ -3986,19 +4138,19 @@
     </row>
     <row r="136" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A136" s="5" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C136" s="5">
-        <v>13478400</v>
+        <v>19980000</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>13</v>
+        <v>226</v>
       </c>
       <c r="E136" s="6">
-        <v>45999</v>
+        <v>46014</v>
       </c>
       <c r="F136" s="5" t="s">
         <v>14</v>
@@ -4006,19 +4158,19 @@
     </row>
     <row r="137" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A137" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B137" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="B137" s="5" t="s">
-        <v>240</v>
-      </c>
       <c r="C137" s="5">
-        <v>5216100</v>
+        <v>19547100</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>13</v>
+        <v>226</v>
       </c>
       <c r="E137" s="6">
-        <v>46002</v>
+        <v>46015</v>
       </c>
       <c r="F137" s="5" t="s">
         <v>14</v>
@@ -4026,19 +4178,19 @@
     </row>
     <row r="138" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A138" s="5" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C138" s="5">
-        <v>5241400</v>
+        <v>115534350</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="E138" s="6">
-        <v>46014</v>
+        <v>46030</v>
       </c>
       <c r="F138" s="5" t="s">
         <v>14</v>
@@ -4046,19 +4198,19 @@
     </row>
     <row r="139" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A139" s="5" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="C139" s="5">
-        <v>2077900</v>
+        <v>75054000</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E139" s="6">
-        <v>45995</v>
+        <v>46011</v>
       </c>
       <c r="F139" s="5" t="s">
         <v>14</v>
@@ -4066,19 +4218,19 @@
     </row>
     <row r="140" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A140" s="5" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C140" s="5">
-        <v>1122900</v>
+        <v>14947490</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>13</v>
+        <v>254</v>
       </c>
       <c r="E140" s="6">
-        <v>45999</v>
+        <v>46004</v>
       </c>
       <c r="F140" s="5" t="s">
         <v>14</v>
@@ -4086,19 +4238,19 @@
     </row>
     <row r="141" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A141" s="5" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="C141" s="5">
-        <v>4409400</v>
+        <v>49047281</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="E141" s="6">
-        <v>45997</v>
+        <v>46020</v>
       </c>
       <c r="F141" s="5" t="s">
         <v>14</v>
@@ -4106,19 +4258,19 @@
     </row>
     <row r="142" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A142" s="5" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C142" s="5">
-        <v>4415400</v>
+        <v>5497495</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>13</v>
+        <v>259</v>
       </c>
       <c r="E142" s="6">
-        <v>46008</v>
+        <v>46013</v>
       </c>
       <c r="F142" s="5" t="s">
         <v>14</v>
@@ -4126,16 +4278,16 @@
     </row>
     <row r="143" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A143" s="5" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C143" s="5">
-        <v>5737925</v>
+        <v>2582415</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="E143" s="6">
         <v>46013</v>
@@ -4146,19 +4298,19 @@
     </row>
     <row r="144" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A144" s="5" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C144" s="5">
-        <v>3639347</v>
+        <v>2989091</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="E144" s="6">
-        <v>45996</v>
+        <v>46028</v>
       </c>
       <c r="F144" s="5" t="s">
         <v>14</v>
@@ -4166,19 +4318,19 @@
     </row>
     <row r="145" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A145" s="5" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="C145" s="5">
-        <v>3570194</v>
+        <v>3714600</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>250</v>
+        <v>45</v>
       </c>
       <c r="E145" s="6">
-        <v>46004</v>
+        <v>46026</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>14</v>
@@ -4186,19 +4338,19 @@
     </row>
     <row r="146" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A146" s="5" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="C146" s="5">
-        <v>10003310</v>
+        <v>7732800</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>188</v>
+        <v>45</v>
       </c>
       <c r="E146" s="6">
-        <v>46002</v>
+        <v>46041</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>14</v>
@@ -4206,19 +4358,19 @@
     </row>
     <row r="147" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A147" s="5" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="C147" s="5">
-        <v>3153500</v>
+        <v>17489300</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="E147" s="6">
-        <v>45994</v>
+        <v>46008</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>14</v>
@@ -4226,19 +4378,19 @@
     </row>
     <row r="148" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A148" s="5" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C148" s="5">
-        <v>1660000</v>
+        <v>41306100</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="E148" s="6">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="F148" s="5" t="s">
         <v>14</v>
@@ -4246,19 +4398,19 @@
     </row>
     <row r="149" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A149" s="5" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C149" s="5">
-        <v>472850</v>
+        <v>27795200</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E149" s="6">
-        <v>45981</v>
+        <v>46021</v>
       </c>
       <c r="F149" s="5" t="s">
         <v>14</v>
@@ -4266,19 +4418,19 @@
     </row>
     <row r="150" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A150" s="5" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C150" s="5">
-        <v>952700</v>
+        <v>54567000</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E150" s="6">
-        <v>46004</v>
+        <v>46012</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>14</v>
@@ -4286,19 +4438,19 @@
     </row>
     <row r="151" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A151" s="5" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C151" s="5">
-        <v>1059800</v>
+        <v>1359900</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E151" s="6">
-        <v>46010</v>
+        <v>46025</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>14</v>
@@ -4306,19 +4458,19 @@
     </row>
     <row r="152" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A152" s="5" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C152" s="5">
-        <v>1332000</v>
+        <v>13990000</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>53</v>
+        <v>128</v>
       </c>
       <c r="E152" s="6">
-        <v>45995</v>
+        <v>46007</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>14</v>
@@ -4326,19 +4478,19 @@
     </row>
     <row r="153" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A153" s="5" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C153" s="5">
-        <v>41923100</v>
+        <v>11190000</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>13</v>
+        <v>128</v>
       </c>
       <c r="E153" s="6">
-        <v>46004</v>
+        <v>46011</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>14</v>
@@ -4346,19 +4498,19 @@
     </row>
     <row r="154" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A154" s="5" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C154" s="5">
-        <v>1044500</v>
+        <v>190353643</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>21</v>
+        <v>128</v>
       </c>
       <c r="E154" s="6">
-        <v>45993</v>
+        <v>46047</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>14</v>
@@ -4366,19 +4518,19 @@
     </row>
     <row r="155" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A155" s="5" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C155" s="5">
-        <v>9915100</v>
+        <v>21731600</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="E155" s="6">
-        <v>46004</v>
+        <v>46009</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>14</v>
@@ -4386,19 +4538,19 @@
     </row>
     <row r="156" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A156" s="5" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C156" s="5">
-        <v>4544000</v>
+        <v>6501100</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="E156" s="6">
-        <v>45994</v>
+        <v>46013</v>
       </c>
       <c r="F156" s="5" t="s">
         <v>14</v>
@@ -4406,19 +4558,19 @@
     </row>
     <row r="157" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A157" s="5" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C157" s="5">
-        <v>11569000</v>
+        <v>10229500</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="E157" s="6">
-        <v>45994</v>
+        <v>46020</v>
       </c>
       <c r="F157" s="5" t="s">
         <v>14</v>
@@ -4426,19 +4578,19 @@
     </row>
     <row r="158" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A158" s="5" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="C158" s="5">
-        <v>11074000</v>
+        <v>1348727</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="E158" s="6">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="F158" s="5" t="s">
         <v>14</v>
@@ -4446,19 +4598,19 @@
     </row>
     <row r="159" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A159" s="5" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="C159" s="5">
-        <v>10000000</v>
+        <v>835000</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E159" s="6">
-        <v>46007</v>
+        <v>46004</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>14</v>
@@ -4466,19 +4618,19 @@
     </row>
     <row r="160" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A160" s="5" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="C160" s="5">
-        <v>12949000</v>
+        <v>760000</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E160" s="6">
-        <v>45999</v>
+        <v>46004</v>
       </c>
       <c r="F160" s="5" t="s">
         <v>14</v>
@@ -4486,19 +4638,19 @@
     </row>
     <row r="161" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A161" s="5" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="C161" s="5">
-        <v>7951000</v>
+        <v>50200850</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E161" s="6">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="F161" s="5" t="s">
         <v>14</v>
@@ -4506,19 +4658,19 @@
     </row>
     <row r="162" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A162" s="5" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="C162" s="5">
-        <v>7951000</v>
+        <v>53050651</v>
       </c>
       <c r="D162" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E162" s="6">
-        <v>46011</v>
+        <v>46006</v>
       </c>
       <c r="F162" s="5" t="s">
         <v>14</v>
@@ -4526,19 +4678,19 @@
     </row>
     <row r="163" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A163" s="5" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="C163" s="5">
-        <v>6242000</v>
+        <v>1607561</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>13</v>
+        <v>259</v>
       </c>
       <c r="E163" s="6">
-        <v>46007</v>
+        <v>45993</v>
       </c>
       <c r="F163" s="5" t="s">
         <v>14</v>
@@ -4546,19 +4698,19 @@
     </row>
     <row r="164" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A164" s="5" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="C164" s="5">
-        <v>9341000</v>
+        <v>6729453</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="E164" s="6">
-        <v>46016</v>
+        <v>46006</v>
       </c>
       <c r="F164" s="5" t="s">
         <v>14</v>
@@ -4566,19 +4718,19 @@
     </row>
     <row r="165" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A165" s="5" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="C165" s="5">
-        <v>9341000</v>
+        <v>63854100</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>13</v>
+        <v>128</v>
       </c>
       <c r="E165" s="6">
-        <v>46021</v>
+        <v>46006</v>
       </c>
       <c r="F165" s="5" t="s">
         <v>14</v>
@@ -4586,19 +4738,19 @@
     </row>
     <row r="166" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A166" s="5" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C166" s="5">
-        <v>2140000</v>
+        <v>14962170</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="E166" s="6">
-        <v>45995</v>
+        <v>46011</v>
       </c>
       <c r="F166" s="5" t="s">
         <v>14</v>
@@ -4606,19 +4758,19 @@
     </row>
     <row r="167" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A167" s="5" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="C167" s="5">
-        <v>15564800</v>
+        <v>11488818</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="E167" s="6">
-        <v>46004</v>
+        <v>46006</v>
       </c>
       <c r="F167" s="5" t="s">
         <v>14</v>
@@ -4626,13 +4778,13 @@
     </row>
     <row r="168" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A168" s="5" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C168" s="5">
-        <v>49116000</v>
+        <v>4210638</v>
       </c>
       <c r="D168" s="5" t="s">
         <v>13</v>
@@ -4646,19 +4798,19 @@
     </row>
     <row r="169" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A169" s="5" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="C169" s="5">
-        <v>786000</v>
+        <v>2721900</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="E169" s="6">
-        <v>45997</v>
+        <v>46021</v>
       </c>
       <c r="F169" s="5" t="s">
         <v>14</v>
@@ -4666,19 +4818,19 @@
     </row>
     <row r="170" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A170" s="5" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="C170" s="5">
-        <v>40787500</v>
+        <v>8003500</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="E170" s="6">
-        <v>46009</v>
+        <v>46022</v>
       </c>
       <c r="F170" s="5" t="s">
         <v>14</v>
@@ -4686,19 +4838,19 @@
     </row>
     <row r="171" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A171" s="5" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="C171" s="5">
-        <v>5644616</v>
+        <v>16987440</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E171" s="6">
-        <v>46010</v>
+        <v>46004</v>
       </c>
       <c r="F171" s="5" t="s">
         <v>14</v>
@@ -4706,19 +4858,19 @@
     </row>
     <row r="172" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A172" s="5" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="C172" s="5">
-        <v>87468710</v>
+        <v>5241400</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>295</v>
+        <v>62</v>
       </c>
       <c r="E172" s="6">
-        <v>45997</v>
+        <v>46014</v>
       </c>
       <c r="F172" s="5" t="s">
         <v>14</v>
@@ -4726,19 +4878,19 @@
     </row>
     <row r="173" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A173" s="5" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="C173" s="5">
-        <v>25870770</v>
+        <v>13001700</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>295</v>
+        <v>62</v>
       </c>
       <c r="E173" s="6">
-        <v>46004</v>
+        <v>46017</v>
       </c>
       <c r="F173" s="5" t="s">
         <v>14</v>
@@ -4746,19 +4898,19 @@
     </row>
     <row r="174" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A174" s="5" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="C174" s="5">
-        <v>437000</v>
+        <v>4691200</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="E174" s="6">
-        <v>45997</v>
+        <v>46021</v>
       </c>
       <c r="F174" s="5" t="s">
         <v>14</v>
@@ -4766,19 +4918,19 @@
     </row>
     <row r="175" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A175" s="5" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="C175" s="5">
-        <v>3225000</v>
+        <v>4415400</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="E175" s="6">
-        <v>46004</v>
+        <v>46008</v>
       </c>
       <c r="F175" s="5" t="s">
         <v>14</v>
@@ -4786,19 +4938,19 @@
     </row>
     <row r="176" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A176" s="5" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="C176" s="5">
-        <v>2481000</v>
+        <v>1560700</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="E176" s="6">
-        <v>46018</v>
+        <v>46008</v>
       </c>
       <c r="F176" s="5" t="s">
         <v>14</v>
@@ -4806,19 +4958,19 @@
     </row>
     <row r="177" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A177" s="5" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="C177" s="5">
-        <v>1354200</v>
+        <v>3682200</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="E177" s="6">
-        <v>46004</v>
+        <v>46016</v>
       </c>
       <c r="F177" s="5" t="s">
         <v>14</v>
@@ -4826,19 +4978,19 @@
     </row>
     <row r="178" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A178" s="5" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="C178" s="5">
-        <v>1495500</v>
+        <v>5737925</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>37</v>
+        <v>314</v>
       </c>
       <c r="E178" s="6">
-        <v>45995</v>
+        <v>46013</v>
       </c>
       <c r="F178" s="5" t="s">
         <v>14</v>
@@ -4846,19 +4998,19 @@
     </row>
     <row r="179" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A179" s="5" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="C179" s="5">
-        <v>36419100</v>
+        <v>3570194</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>30</v>
+        <v>314</v>
       </c>
       <c r="E179" s="6">
-        <v>45995</v>
+        <v>46004</v>
       </c>
       <c r="F179" s="5" t="s">
         <v>14</v>
@@ -4866,19 +5018,19 @@
     </row>
     <row r="180" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A180" s="5" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="C180" s="5">
-        <v>54381600</v>
+        <v>472850</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E180" s="6">
-        <v>46015</v>
+        <v>45981</v>
       </c>
       <c r="F180" s="5" t="s">
         <v>14</v>
@@ -4886,19 +5038,19 @@
     </row>
     <row r="181" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A181" s="5" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="C181" s="5">
-        <v>1030000</v>
+        <v>952700</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E181" s="6">
-        <v>45991</v>
+        <v>46004</v>
       </c>
       <c r="F181" s="5" t="s">
         <v>14</v>
@@ -4906,19 +5058,19 @@
     </row>
     <row r="182" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A182" s="5" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C182" s="5">
-        <v>19490000</v>
+        <v>1059800</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E182" s="6">
-        <v>45996</v>
+        <v>46010</v>
       </c>
       <c r="F182" s="5" t="s">
         <v>14</v>
@@ -4926,19 +5078,19 @@
     </row>
     <row r="183" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A183" s="5" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C183" s="5">
-        <v>26014000</v>
+        <v>638250</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E183" s="6">
-        <v>45995</v>
+        <v>46016</v>
       </c>
       <c r="F183" s="5" t="s">
         <v>14</v>
@@ -4946,19 +5098,19 @@
     </row>
     <row r="184" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A184" s="5" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="C184" s="5">
-        <v>10937000</v>
+        <v>1665000</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="E184" s="6">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="F184" s="5" t="s">
         <v>14</v>
@@ -4966,19 +5118,19 @@
     </row>
     <row r="185" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A185" s="5" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C185" s="5">
-        <v>4824000</v>
+        <v>7214000</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="E185" s="6">
-        <v>45992</v>
+        <v>46017</v>
       </c>
       <c r="F185" s="5" t="s">
         <v>14</v>
@@ -4986,19 +5138,19 @@
     </row>
     <row r="186" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A186" s="5" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C186" s="5">
-        <v>13081000</v>
+        <v>1371000</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E186" s="6">
-        <v>45997</v>
+        <v>45995</v>
       </c>
       <c r="F186" s="5" t="s">
         <v>14</v>
@@ -5006,19 +5158,19 @@
     </row>
     <row r="187" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A187" s="5" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="C187" s="5">
-        <v>18641000</v>
+        <v>14331300</v>
       </c>
       <c r="D187" s="5" t="s">
         <v>13</v>
       </c>
       <c r="E187" s="6">
-        <v>46007</v>
+        <v>46014</v>
       </c>
       <c r="F187" s="5" t="s">
         <v>14</v>
@@ -5026,19 +5178,19 @@
     </row>
     <row r="188" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A188" s="5" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="C188" s="5">
-        <v>1212952</v>
+        <v>8802200</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E188" s="6">
-        <v>45995</v>
+        <v>46036</v>
       </c>
       <c r="F188" s="5" t="s">
         <v>14</v>
@@ -5046,19 +5198,19 @@
     </row>
     <row r="189" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A189" s="5" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="C189" s="5">
-        <v>2484000</v>
+        <v>9491800</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="E189" s="6">
-        <v>45993</v>
+        <v>46038</v>
       </c>
       <c r="F189" s="5" t="s">
         <v>14</v>
@@ -5066,19 +5218,19 @@
     </row>
     <row r="190" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A190" s="5" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C190" s="5">
-        <v>1082100</v>
+        <v>10000000</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>326</v>
+        <v>62</v>
       </c>
       <c r="E190" s="6">
-        <v>45989</v>
+        <v>46007</v>
       </c>
       <c r="F190" s="5" t="s">
         <v>14</v>
@@ -5086,21 +5238,641 @@
     </row>
     <row r="191" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A191" s="5" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C191" s="5">
-        <v>3666663</v>
+        <v>7951000</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E191" s="6">
-        <v>45994</v>
+        <v>46009</v>
       </c>
       <c r="F191" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A192" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C192" s="5">
+        <v>7951000</v>
+      </c>
+      <c r="D192" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E192" s="6">
+        <v>46011</v>
+      </c>
+      <c r="F192" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A193" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C193" s="5">
+        <v>6242000</v>
+      </c>
+      <c r="D193" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E193" s="6">
+        <v>46007</v>
+      </c>
+      <c r="F193" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A194" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C194" s="5">
+        <v>9341000</v>
+      </c>
+      <c r="D194" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E194" s="6">
+        <v>46016</v>
+      </c>
+      <c r="F194" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A195" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C195" s="5">
+        <v>9341000</v>
+      </c>
+      <c r="D195" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E195" s="6">
+        <v>46021</v>
+      </c>
+      <c r="F195" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A196" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C196" s="5">
+        <v>9501000</v>
+      </c>
+      <c r="D196" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E196" s="6">
+        <v>46011</v>
+      </c>
+      <c r="F196" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A197" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C197" s="5">
+        <v>7295000</v>
+      </c>
+      <c r="D197" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E197" s="6">
+        <v>46025</v>
+      </c>
+      <c r="F197" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A198" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C198" s="5">
+        <v>7295000</v>
+      </c>
+      <c r="D198" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E198" s="6">
+        <v>46028</v>
+      </c>
+      <c r="F198" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A199" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C199" s="5">
+        <v>10000000</v>
+      </c>
+      <c r="D199" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E199" s="6">
+        <v>46035</v>
+      </c>
+      <c r="F199" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A200" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C200" s="5">
+        <v>11947000</v>
+      </c>
+      <c r="D200" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E200" s="6">
+        <v>46018</v>
+      </c>
+      <c r="F200" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A201" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="C201" s="5">
+        <v>49116000</v>
+      </c>
+      <c r="D201" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E201" s="6">
+        <v>46011</v>
+      </c>
+      <c r="F201" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A202" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="C202" s="5">
+        <v>55043235</v>
+      </c>
+      <c r="D202" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="E202" s="6">
+        <v>46003</v>
+      </c>
+      <c r="F202" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A203" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="C203" s="5">
+        <v>9338000</v>
+      </c>
+      <c r="D203" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E203" s="6">
+        <v>46016</v>
+      </c>
+      <c r="F203" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A204" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="C204" s="5">
+        <v>40787500</v>
+      </c>
+      <c r="D204" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E204" s="6">
+        <v>46009</v>
+      </c>
+      <c r="F204" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A205" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="C205" s="5">
+        <v>5644616</v>
+      </c>
+      <c r="D205" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E205" s="6">
+        <v>46010</v>
+      </c>
+      <c r="F205" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A206" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="C206" s="5">
+        <v>101327200</v>
+      </c>
+      <c r="D206" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E206" s="6">
+        <v>46007</v>
+      </c>
+      <c r="F206" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A207" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="C207" s="5">
+        <v>63454500</v>
+      </c>
+      <c r="D207" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E207" s="6">
+        <v>46018</v>
+      </c>
+      <c r="F207" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A208" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="C208" s="5">
+        <v>13670000</v>
+      </c>
+      <c r="D208" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E208" s="6">
+        <v>46025</v>
+      </c>
+      <c r="F208" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A209" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="C209" s="5">
+        <v>38687000</v>
+      </c>
+      <c r="D209" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E209" s="6">
+        <v>46035</v>
+      </c>
+      <c r="F209" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A210" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="C210" s="5">
+        <v>30000000</v>
+      </c>
+      <c r="D210" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E210" s="6">
+        <v>46022</v>
+      </c>
+      <c r="F210" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A211" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="C211" s="5">
+        <v>32186000</v>
+      </c>
+      <c r="D211" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E211" s="6">
+        <v>46015</v>
+      </c>
+      <c r="F211" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A212" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="C212" s="5">
+        <v>52444000</v>
+      </c>
+      <c r="D212" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E212" s="6">
+        <v>46035</v>
+      </c>
+      <c r="F212" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A213" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="C213" s="5">
+        <v>120390253</v>
+      </c>
+      <c r="D213" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="E213" s="6">
+        <v>46018</v>
+      </c>
+      <c r="F213" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A214" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="C214" s="5">
+        <v>25870770</v>
+      </c>
+      <c r="D214" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="E214" s="6">
+        <v>46004</v>
+      </c>
+      <c r="F214" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A215" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C215" s="5">
+        <v>58436534</v>
+      </c>
+      <c r="D215" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E215" s="6">
+        <v>46010</v>
+      </c>
+      <c r="F215" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A216" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="C216" s="5">
+        <v>3225000</v>
+      </c>
+      <c r="D216" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E216" s="6">
+        <v>46004</v>
+      </c>
+      <c r="F216" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A217" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="C217" s="5">
+        <v>2481000</v>
+      </c>
+      <c r="D217" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E217" s="6">
+        <v>46018</v>
+      </c>
+      <c r="F217" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A218" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="C218" s="5">
+        <v>54381600</v>
+      </c>
+      <c r="D218" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E218" s="6">
+        <v>46015</v>
+      </c>
+      <c r="F218" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A219" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="C219" s="5">
+        <v>48951000</v>
+      </c>
+      <c r="D219" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E219" s="6">
+        <v>46024</v>
+      </c>
+      <c r="F219" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A220" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C220" s="5">
+        <v>15877000</v>
+      </c>
+      <c r="D220" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E220" s="6">
+        <v>46010</v>
+      </c>
+      <c r="F220" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A221" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="C221" s="5">
+        <v>18641000</v>
+      </c>
+      <c r="D221" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E221" s="6">
+        <v>46007</v>
+      </c>
+      <c r="F221" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" s="5" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A222" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C222" s="5">
+        <v>5720000</v>
+      </c>
+      <c r="D222" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E222" s="6">
+        <v>46007</v>
+      </c>
+      <c r="F222" s="5" t="s">
         <v>14</v>
       </c>
     </row>
